--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -586,6 +586,81 @@
       <c r="C11" t="inlineStr">
         <is>
           <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BCCMA.SW</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.03691437376361972</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TELE.PA</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.03452904661767775</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Amundi STOXX Europe 600 Telecommunications UCITS ETF Acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ABBA.SW</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.02807797708419013</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>21shares Bitcoin Ethereum Core ETP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FBTC.MI</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.02677895973065669</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Fidelity Physical Bitcoin ETP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>INDO.PA</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.02462910956296205</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -600,7 +675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -767,6 +842,81 @@
       <c r="C11" t="inlineStr">
         <is>
           <t>BNP Paribas Easy ESG Enhanced US UCITS ETF EUR Hedged Acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FBT.MI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.1045520414775176</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>First Trust NYSE Arca Biotechnology UCITS ETF Acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BTEC.SW</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.08783161148811036</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BSOL.PA</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.08534640049685427</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Bitwise Solana Staking ETP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ARKK.MI</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.07998883393049838</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SETH.AS</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.07784429950385774</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AMINA Ethereum ETP</t>
         </is>
       </c>
     </row>
@@ -781,7 +931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -948,6 +1098,81 @@
       <c r="C11" t="inlineStr">
         <is>
           <t>Amundi MSCI Korea UCITS ETF Acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>IKRA.AS</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.2685487917573555</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>GOAI.AS</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.2558051926830418</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Amundi MSCI Robotics &amp; AI UCITS ETF Acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FBT.MI</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.2375407799057305</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>First Trust NYSE Arca Biotechnology UCITS ETF Acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>WITS.AS</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.2352438044925331</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>GLIT.PA</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.232112574980101</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Amundi S&amp;P Global Information Technology ESG UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
@@ -962,7 +1187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,6 +1354,81 @@
       <c r="C11" t="inlineStr">
         <is>
           <t>Amundi Core S&amp;P 500 Swap UCITS ETF Acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NRGW.PA</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.2642900387483433</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EXCD.AS</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.2564886970946796</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SXLE.AS</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.2498896474626309</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FTAI.MI</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.2482117355335969</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>First Trust Bloomberg Artificial Intelligence UCITS ETF Class A Accumulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FEME.MI</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.245093498057402</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Fidelity Emerging Markets Quality Income UCITS ETF INC-USD</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1310,6 +1610,81 @@
       <c r="C11" t="inlineStr">
         <is>
           <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMXC.PA</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.5742624509571184</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BRES.PA</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.5643582343116078</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TPHG.PA</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.5324881080680428</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Amundi Japan Topix UCITS ETF Daily Hedged GBP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BNK.PA</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.5322475923100316</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EXCD.AS</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.5299646630586388</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1491,6 +1866,81 @@
       <c r="C11" t="inlineStr">
         <is>
           <t>Amundi Japan Topix UCITS ETF Daily Hedged USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>GRE.PA</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.157711829953367</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>JPHU.PA</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.153712096333823</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Amundi JPX Nikkei 400 UCITS ETF Daily Hedged USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>JPHG.PA</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.130249633900089</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Amundi JPX Nikkei 400 UCITS ETF Daily Hedged GBP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TPHG.PA</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.123865672814606</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Amundi Japan Topix UCITS ETF Daily Hedged GBP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MIB.PA</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.106605816728025</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1675,6 +2125,81 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SXLE.AS</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.2957373514562294</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FEMI.MI</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.294412338744366</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NRGW.PA</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.2908254029383845</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SP5C.PA</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.2888175993127151</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Amundi Core S&amp;P 500 Swap UCITS ETF Acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>STN.PA</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.2870218647235494</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,225 +442,120 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TIAB.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1244270225218909</v>
+        <v>0.07088469158115274</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bitwise Celestia Staking ETP</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AUNI.AS</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1234758013921327</v>
+        <v>0.05913640588672275</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>21shares Uniswap ETP</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ET32.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08659070370634114</v>
+        <v>0.05750153606847408</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bitwise Ethereum Staking ETP</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07088469158115274</v>
+        <v>0.0489349675918187</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SDOT.AS</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.06692913047073046</v>
+        <v>0.04206313555654373</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AMINA Polkadot ETP</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ADOT.AS</t>
+          <t>TELE.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.06675130324650169</v>
+        <v>0.03452904661767775</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>21shares Polkadot ETP</t>
+          <t>Amundi STOXX Europe 600 Telecommunications UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>INDO.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.05913640588672275</v>
+        <v>0.02462910956296205</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>BSX.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05750153606847408</v>
+        <v>0.02166618866541903</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>NRGW.PA</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.0489349675918187</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>BXX.PA</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.04206313555654373</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>BCCMA.SW</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.03691437376361972</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TELE.PA</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0.03452904661767775</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Amundi STOXX Europe 600 Telecommunications UCITS ETF Acc</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>ABBA.SW</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.02807797708419013</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>21shares Bitcoin Ethereum Core ETP</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>FBTC.MI</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0.02677895973065669</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Fidelity Physical Bitcoin ETP</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>INDO.PA</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.02462910956296205</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -675,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -698,225 +593,120 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AUNI.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4497998976697066</v>
+        <v>0.2302223837755073</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21shares Uniswap ETP</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TIAB.PA</t>
+          <t>SP5C.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3909591383710396</v>
+        <v>0.1703637705238301</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bitwise Celestia Staking ETP</t>
+          <t>Amundi Core S&amp;P 500 Swap UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2302223837755073</v>
+        <v>0.08783161148811036</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JSOL.AS</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1841651948457452</v>
+        <v>0.07998883393049838</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21shares Jito Staked SOL ETP</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CSOL.MI</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.175791442448135</v>
+        <v>0.07761454350890928</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>21shares Solana Core Staking ETP</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SP5C.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1703637705238301</v>
+        <v>0.07619972786979612</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Core S&amp;P 500 Swap UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ASOL.AS</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1492440483785455</v>
+        <v>0.07408527478270366</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>21shares Solana Staking ETP</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>QUSAE.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1397838360603161</v>
+        <v>0.06616888992604664</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Alpha Enhanced US UCITS ETF EUR Acc</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>SLNC.PA</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.1377138068537653</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>CoinShares Physical Staked Solana</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>AUSSH.PA</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.1307394352806199</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>BNP Paribas Easy ESG Enhanced US UCITS ETF EUR Hedged Acc</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>FBT.MI</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.1045520414775176</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>First Trust NYSE Arca Biotechnology UCITS ETF Acc</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>BTEC.SW</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0.08783161148811036</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>BSOL.PA</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.08534640049685427</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Bitwise Solana Staking ETP</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ARKK.MI</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0.07998883393049838</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>SETH.AS</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.07784429950385774</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AMINA Ethereum ETP</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
@@ -931,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -984,195 +774,90 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NEAR.AS</t>
+          <t>SP5C.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.368990242986162</v>
+        <v>0.2932447794350908</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21shares NEAR Protocol Staking ETP</t>
+          <t>Amundi Core S&amp;P 500 Swap UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EJAPU.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3451283397940894</v>
+        <v>0.2878198938069461</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF USD</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ONDO.AS</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.324706994489665</v>
+        <v>0.2686936913329221</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>21Shares Ondo ETP</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FTAI.MI</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3104534904029543</v>
+        <v>0.2686860651842049</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>First Trust Bloomberg Artificial Intelligence UCITS ETF Class A Accumulation</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SP5C.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2932447794350908</v>
+        <v>0.2685487917573555</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Core S&amp;P 500 Swap UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2878198938069461</v>
+        <v>0.2352438044925331</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>LEVMIB.MI</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.2686936913329221</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>KRW.PA</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.2686860651842049</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>IKRA.AS</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.2685487917573555</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>GOAI.AS</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0.2558051926830418</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Amundi MSCI Robotics &amp; AI UCITS ETF Acc</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>FBT.MI</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.2375407799057305</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>First Trust NYSE Arca Biotechnology UCITS ETF Acc</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>WITS.AS</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0.2352438044925331</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
           <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>GLIT.PA</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.232112574980101</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Amundi S&amp;P Global Information Technology ESG UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
@@ -1187,7 +872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1270,165 +955,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EJAPU.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3451283397940894</v>
+        <v>0.3332675507779312</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF USD</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3332675507779312</v>
+        <v>0.3009325716984608</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3009325716984608</v>
+        <v>0.2918728490319493</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2918728490319493</v>
+        <v>0.2812062625950971</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>EMXC.PA</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.2812062625950971</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
           <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>SP5C.PA</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.2656893720769995</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Amundi Core S&amp;P 500 Swap UCITS ETF Acc</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>NRGW.PA</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.2642900387483433</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>EXCD.AS</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0.2564886970946796</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>SXLE.AS</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.2498896474626309</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>FTAI.MI</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0.2482117355335969</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>First Trust Bloomberg Artificial Intelligence UCITS ETF Class A Accumulation</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>FEME.MI</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.245093498057402</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Fidelity Emerging Markets Quality Income UCITS ETF INC-USD</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1496,195 +1076,90 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MINR.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.019933503870999</v>
+        <v>0.8904155813543404</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>First Trust Indxx Future Economy Metals UCITS ETF Class A Accumulation</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8904155813543404</v>
+        <v>0.7765479014724228</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7765479014724228</v>
+        <v>0.7714090452057252</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7714090452057252</v>
+        <v>0.7222165004178984</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7222165004178984</v>
+        <v>0.6523443122821793</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6523443122821793</v>
+        <v>0.5769297947462435</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>GOAI.AS</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.5891469573527659</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Amundi MSCI Robotics &amp; AI UCITS ETF Acc</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>VAPU.SW</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.5769297947462435</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
           <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>EMXC.PA</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.5742624509571184</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>BRES.PA</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0.5643582343116078</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TPHG.PA</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.5324881080680428</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Amundi Japan Topix UCITS ETF Daily Hedged GBP</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>BNK.PA</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0.5322475923100316</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>EXCD.AS</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.5299646630586388</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1699,7 +1174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1836,111 +1311,6 @@
       <c r="C9" t="inlineStr">
         <is>
           <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CEC.PA</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1.207374345089354</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TPHU.PA</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.159602887961937</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Amundi Japan Topix UCITS ETF Daily Hedged USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>GRE.PA</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.157711829953367</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>JPHU.PA</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.153712096333823</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Amundi JPX Nikkei 400 UCITS ETF Daily Hedged USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>JPHG.PA</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.130249633900089</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Amundi JPX Nikkei 400 UCITS ETF Daily Hedged GBP</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TPHG.PA</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1.123865672814606</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Amundi Japan Topix UCITS ETF Daily Hedged GBP</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>MIB.PA</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1.106605816728025</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2095,111 +1465,6 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>EJAPU.PA</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.3451283397940894</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>FEME.MI</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.302805170236357</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Fidelity Emerging Markets Quality Income UCITS ETF INC-USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>SXLE.AS</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.2957373514562294</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>FEMI.MI</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0.294412338744366</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>NRGW.PA</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.2908254029383845</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>SP5C.PA</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0.2888175993127151</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Amundi Core S&amp;P 500 Swap UCITS ETF Acc</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>STN.PA</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.2870218647235494</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,6 +556,111 @@
       <c r="C9" t="inlineStr">
         <is>
           <t>Amundi EURO STOXX 50 Daily (-1x) Inverse UCITS ETF Acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TELW.PA</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01849568468831286</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Amundi S&amp;P Global Communication Services ESG UCITS ETF DR EUR (A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>XUCM.L</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.01603207097720105</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Xtrackers MSCI USA Communication Services UCITS ETF 1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SHC.PA</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.01598176924731054</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>HMXJ.MI</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.01511266926963617</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>HSBC MSCI Pacific ex Japan UCITS ETF USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ALAU.PA</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.01314671191456318</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>UINC.L</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.01287699085055904</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>First Trust US Equity Income UCITS ETF Dist</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DSP5.PA</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.01256439247301921</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -570,7 +675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -707,6 +812,111 @@
       <c r="C9" t="inlineStr">
         <is>
           <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CL2.PA</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.06231000592109037</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HLTW.PA</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.05811565509750327</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>JPXH.PA</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.05501646945378802</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - EUR Hedged (C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>JPXX.L</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.05379021814921803</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LEVMIB.MI</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.0530940374550628</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>GRE.PA</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.0465809568105664</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DJE.PA</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.04065946251940367</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Amundi Dow Jones Industrial Average UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -721,7 +931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -858,6 +1068,111 @@
       <c r="C9" t="inlineStr">
         <is>
           <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ARKK.MI</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.2019230854559046</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LWLD.PA</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.198128997009505</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CU2.PA</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.1873370007490154</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EQQQ.L</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.1792481905781347</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BCHN.MI</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.1789838547338414</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ARKI.MI</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.1689173115421989</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BNKE.PA</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.1655937885200118</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -872,7 +1187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1009,6 +1324,111 @@
       <c r="C9" t="inlineStr">
         <is>
           <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SP5C.PA</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.2656893720769995</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Amundi Core S&amp;P 500 Swap UCITS ETF Acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NRGW.PA</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.2642900387483433</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EXCD.AS</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.2564886970946796</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SXLE.AS</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.2498896474626309</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CL2.PA</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.2137757596936585</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AASI.PA</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.1882681635304022</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MIB.PA</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.1849819604889646</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1160,6 +1580,111 @@
       <c r="C9" t="inlineStr">
         <is>
           <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMXC.PA</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.5742624509571184</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BRES.PA</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.5643582343116078</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BNK.PA</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.5322475923100316</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EXCD.AS</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.5299646630586388</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BNKE.PA</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.5288415217328559</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>XMK9.MI</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.4967853816720769</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Xtrackers MSCI Japan UCITS ETF 4C - EUR Hedged</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EJAH.PA</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.494426249416881</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1197,120 +1722,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JPXX.L</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>156.7614924936782</v>
+        <v>2.598523336888218</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.598523336888218</v>
+        <v>2.200655946783614</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.200655946783614</v>
+        <v>1.674788056299872</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.674788056299872</v>
+        <v>1.655239699187534</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.655239699187534</v>
+        <v>1.395963490476427</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.395963490476427</v>
+        <v>1.362783604857835</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.362783604857835</v>
+        <v>1.313317512091593</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.313317512091593</v>
+        <v>1.207374345089354</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>GRE.PA</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.157711829953367</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MIB.PA</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.106605816728025</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EJAH.PA</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.045943445248393</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>GOLD.AS</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.042878384243142</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Amundi Physical Gold ETC (C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>WITS.AS</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.04205227546404</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>XMK9.MI</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.031548871431515</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Xtrackers MSCI Japan UCITS ETF 4C - EUR Hedged</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TPXH.PA</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.017982473482495</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Amundi Japan Topix UCITS ETF Daily Hedged EUR (C)</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1465,6 +2095,111 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SXLE.AS</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.2957373514562294</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NRGW.PA</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.2908254029383845</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SP5C.PA</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.2888175993127151</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Amundi Core S&amp;P 500 Swap UCITS ETF Acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>STN.PA</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.2870218647235494</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AASI.PA</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.2594285566956194</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CL2.PA</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.2561900468701963</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AJEUAS.MI</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.2513509183857769</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.07088469158115274</v>
+        <v>0.06325474262573771</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -457,15 +457,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05913640588672275</v>
+        <v>0.05155242016883599</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05750153606847408</v>
+        <v>0.04262592576738311</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -487,180 +487,180 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0489349675918187</v>
+        <v>0.03498320896102247</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04206313555654373</v>
+        <v>0.03430679138069848</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TELE.PA</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03452904661767775</v>
+        <v>0.02938039637115653</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Telecommunications UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>INDO.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02462910956296205</v>
+        <v>0.02773730527176332</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BSX.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02166618866541903</v>
+        <v>0.02768682051060156</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TELW.PA</t>
+          <t>HMXJ.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01849568468831286</v>
+        <v>0.02694284829819305</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Communication Services ESG UCITS ETF DR EUR (A)</t>
+          <t>HSBC MSCI Pacific ex Japan UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XUCM.L</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01603207097720105</v>
+        <v>0.02640864809471388</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Communication Services UCITS ETF 1D</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SHC.PA</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.01598176924731054</v>
+        <v>0.02608690394045321</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HMXJ.MI</t>
+          <t>AIPO.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.01511266926963617</v>
+        <v>0.02550953451195226</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HSBC MSCI Pacific ex Japan UCITS ETF USD</t>
+          <t>Defiance AI &amp; Power Infrastructure UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>TELE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01314671191456318</v>
+        <v>0.02521172818269912</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi STOXX Europe 600 Telecommunications UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UINC.L</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01287699085055904</v>
+        <v>0.0242348530686769</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>First Trust US Equity Income UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DSP5.PA</t>
+          <t>JPXX.L</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01256439247301921</v>
+        <v>0.02251263951159022</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2302223837755073</v>
+        <v>0.2211082404691673</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -713,210 +713,210 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SP5C.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1703637705238301</v>
+        <v>0.08920399064256213</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi Core S&amp;P 500 Swap UCITS ETF Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08783161148811036</v>
+        <v>0.08366758755392589</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07998883393049838</v>
+        <v>0.08290750385680368</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.07761454350890928</v>
+        <v>0.08046144225549301</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07619972786979612</v>
+        <v>0.07543770066078537</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.07408527478270366</v>
+        <v>0.06995538555865211</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>JPXX.L</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.06616888992604664</v>
+        <v>0.06773583026197838</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>JPXH.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.06231000592109037</v>
+        <v>0.0668460352317759</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - EUR Hedged (C)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.05811565509750327</v>
+        <v>0.05471120900005721</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>JPXH.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05501646945378802</v>
+        <v>0.05458960697921977</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - EUR Hedged (C)</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JPXX.L</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05379021814921803</v>
+        <v>0.04993480915630388</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>AJASE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0530940374550628</v>
+        <v>0.04448668948061085</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>BNP Paribas Easy ESG Enhanced Japan UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>XDWU.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0465809568105664</v>
+        <v>0.04353594657583537</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DJE.PA</t>
+          <t>JPNK.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04065946251940367</v>
+        <v>0.0417576909789914</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Dow Jones Industrial Average UCITS ETF Dist</t>
+          <t>Amundi JPX Nikkei 400 UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5298651496078619</v>
+        <v>0.425167506740695</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3783342994485948</v>
+        <v>0.3465686423464129</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -984,195 +984,195 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SP5C.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2932447794350908</v>
+        <v>0.2507008570694615</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi Core S&amp;P 500 Swap UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2878198938069461</v>
+        <v>0.2461208602696037</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2686936913329221</v>
+        <v>0.2436193598177105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2686860651842049</v>
+        <v>0.2381474571351039</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2685487917573555</v>
+        <v>0.215923622478059</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2352438044925331</v>
+        <v>0.1688577756637313</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2019230854559046</v>
+        <v>0.1656747222440376</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>CU2.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.198128997009505</v>
+        <v>0.1643479238369989</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CU2.PA</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1873370007490154</v>
+        <v>0.1491154553086109</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1792481905781347</v>
+        <v>0.1441433666887577</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1789838547338414</v>
+        <v>0.1437221785324871</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>AUSSE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1689173115421989</v>
+        <v>0.1436047939601968</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>BNP Paribas Easy ESG Enhanced US UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1655937885200118</v>
+        <v>0.1421288307065587</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6064168029276249</v>
+        <v>0.6477228408044433</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6029489275337985</v>
+        <v>0.6443947946814828</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4321404875825956</v>
+        <v>0.4246078272391671</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3570225032226428</v>
+        <v>0.3705053463686743</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1270,75 +1270,75 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3332675507779312</v>
+        <v>0.3301954296116842</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3009325716984608</v>
+        <v>0.3078874653182906</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2918728490319493</v>
+        <v>0.2860006815297782</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2812062625950971</v>
+        <v>0.2775218715160799</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SP5C.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2656893720769995</v>
+        <v>0.266986275771683</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Core S&amp;P 500 Swap UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2642900387483433</v>
+        <v>0.2452636537460811</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1360,45 +1360,45 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2564886970946796</v>
+        <v>0.2278410327166482</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2498896474626309</v>
+        <v>0.1988483860608468</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>MIB.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2137757596936585</v>
+        <v>0.1920618123976403</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1882681635304022</v>
+        <v>0.1915037200401066</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1420,15 +1420,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MIB.PA</t>
+          <t>AJEUAS.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1849819604889646</v>
+        <v>0.1870206678004969</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.542956978805963</v>
+        <v>1.585393775639258</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.525736226669062</v>
+        <v>1.572328722520088</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8904155813543404</v>
+        <v>0.8944826818504767</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1511,30 +1511,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7765479014724228</v>
+        <v>0.8381975877753114</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7714090452057252</v>
+        <v>0.7709796707693994</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7222165004178984</v>
+        <v>0.7331392006931017</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6523443122821793</v>
+        <v>0.6459458474690551</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5769297947462435</v>
+        <v>0.6199294045540218</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1586,60 +1586,60 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5742624509571184</v>
+        <v>0.6189073732457309</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5643582343116078</v>
+        <v>0.5864478507284048</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5322475923100316</v>
+        <v>0.5464940222633361</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5299646630586388</v>
+        <v>0.5341007240623272</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5288415217328559</v>
+        <v>0.5320165293462102</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4967853816720769</v>
+        <v>0.5103703251591436</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.494426249416881</v>
+        <v>0.5071088163025894</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.598523336888218</v>
+        <v>2.603633841404627</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.200655946783614</v>
+        <v>2.216376730356573</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.674788056299872</v>
+        <v>1.731148103111878</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.655239699187534</v>
+        <v>1.7123839952674</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.395963490476427</v>
+        <v>1.378824952862302</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.362783604857835</v>
+        <v>1.377912198247917</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.313317512091593</v>
+        <v>1.329369858266531</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.207374345089354</v>
+        <v>1.231378334803925</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.157711829953367</v>
+        <v>1.164626390012216</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.106605816728025</v>
+        <v>1.110118783944252</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1872,45 +1872,45 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EJAH.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.045943445248393</v>
+        <v>1.077540391619742</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>EJAH.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.042878384243142</v>
+        <v>1.060699939538897</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.04205227546404</v>
+        <v>1.058879642913425</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.031548871431515</v>
+        <v>1.053028965004586</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1932,15 +1932,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TPXH.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.017982473482495</v>
+        <v>1.051134806269113</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Japan Topix UCITS ETF Daily Hedged EUR (C)</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7995595529573973</v>
+        <v>0.8374777948931615</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7934956160810336</v>
+        <v>0.8320940313332001</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5023203991529144</v>
+        <v>0.4998634446725718</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4575100542052806</v>
+        <v>0.4467120426590347</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2038,165 +2038,165 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3988080752602723</v>
+        <v>0.4035757189398312</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3641502645571733</v>
+        <v>0.4007946164931517</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3511199676777448</v>
+        <v>0.3610816774407746</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3498044739950943</v>
+        <v>0.3569965666570933</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2957373514562294</v>
+        <v>0.3018070975391487</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2908254029383845</v>
+        <v>0.2959007049807312</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SP5C.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2888175993127151</v>
+        <v>0.2922423170603994</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Core S&amp;P 500 Swap UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>AASI.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2870218647235494</v>
+        <v>0.2653921884756707</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AASI.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2594285566956194</v>
+        <v>0.2644689165742453</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>AJEUAS.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2561900468701963</v>
+        <v>0.2585559473233707</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AJEUAS.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2513509183857769</v>
+        <v>0.2472044089611258</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,225 +442,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.06325474262573771</v>
+        <v>0.08014724996671596</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05155242016883599</v>
+        <v>0.06003909040634037</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04262592576738311</v>
+        <v>0.04171169842406908</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03498320896102247</v>
+        <v>0.03811170694719523</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03430679138069848</v>
+        <v>0.03742239562991445</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>HMXJ.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02938039637115653</v>
+        <v>0.03642790953795538</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>HSBC MSCI Pacific ex Japan UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>TELW.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02773730527176332</v>
+        <v>0.03455078221533925</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi S&amp;P Global Communication Services ESG UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02768682051060156</v>
+        <v>0.03392105173939108</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HMXJ.MI</t>
+          <t>TRV.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02694284829819305</v>
+        <v>0.0333269887476908</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>HSBC MSCI Pacific ex Japan UCITS ETF USD</t>
+          <t>Amundi STOXX Europe 600 Consumer Discretionary UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>XUCM.L</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02640864809471388</v>
+        <v>0.03143032247507449</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Xtrackers MSCI USA Communication Services UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02608690394045321</v>
+        <v>0.03014704816756608</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AIPO.MI</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02550953451195226</v>
+        <v>0.02899066464144573</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Defiance AI &amp; Power Infrastructure UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TELE.PA</t>
+          <t>SEL.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02521172818269912</v>
+        <v>0.02882340512387094</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Telecommunications UCITS ETF Acc</t>
+          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>MATW.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0242348530686769</v>
+        <v>0.02810691637919893</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JPXX.L</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02251263951159022</v>
+        <v>0.02785060185847743</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2211082404691673</v>
+        <v>0.1745754199669611</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08920399064256213</v>
+        <v>0.09495335393725823</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -728,195 +728,195 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08366758755392589</v>
+        <v>0.07493607211046438</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08290750385680368</v>
+        <v>0.0740625005706439</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08046144225549301</v>
+        <v>0.06951067579670611</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07543770066078537</v>
+        <v>0.05610246940250874</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>JPXX.L</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06995538555865211</v>
+        <v>0.05122583217061982</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JPXX.L</t>
+          <t>DSP5.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.06773583026197838</v>
+        <v>0.05098168134574044</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JPXH.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0668460352317759</v>
+        <v>0.04934422987529596</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - EUR Hedged (C)</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>JPXH.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.05471120900005721</v>
+        <v>0.04635018260662838</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - EUR Hedged (C)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>XSMC.SW</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05458960697921977</v>
+        <v>0.04184821686304363</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Xtrackers Swiss Large Cap UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>HMXJ.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04993480915630388</v>
+        <v>0.03713271962819165</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>HSBC MSCI Pacific ex Japan UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AJASE.PA</t>
+          <t>XDWU.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.04448668948061085</v>
+        <v>0.03706826292938636</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy ESG Enhanced Japan UCITS ETF EUR Acc</t>
+          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>XDWU.MI</t>
+          <t>CD9.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.04353594657583537</v>
+        <v>0.03678353606703211</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
+          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JPNK.PA</t>
+          <t>UTI.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0417576909789914</v>
+        <v>0.03668294767054125</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi JPX Nikkei 400 UCITS ETF EUR (C)</t>
+          <t>Amundi STOXX Europe 600 Utilities UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.425167506740695</v>
+        <v>0.4077650306531748</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3465686423464129</v>
+        <v>0.3046317616563878</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2507008570694615</v>
+        <v>0.2396759715832568</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -999,45 +999,45 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2461208602696037</v>
+        <v>0.217906525601834</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2436193598177105</v>
+        <v>0.1958000346931188</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2381474571351039</v>
+        <v>0.1953749370954068</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.215923622478059</v>
+        <v>0.1806977503029152</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1059,90 +1059,90 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1688577756637313</v>
+        <v>0.1577253557041596</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>CU2.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1656747222440376</v>
+        <v>0.1512424719623873</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CU2.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1643479238369989</v>
+        <v>0.1477018557720302</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1491154553086109</v>
+        <v>0.1406751345810116</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1441433666887577</v>
+        <v>0.1402617957829566</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1437221785324871</v>
+        <v>0.1385472818394888</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1436047939601968</v>
+        <v>0.1374723968508647</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1164,15 +1164,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1421288307065587</v>
+        <v>0.1300801514781544</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6477228408044433</v>
+        <v>0.5756853396901074</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6443947946814828</v>
+        <v>0.5723460518362817</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4246078272391671</v>
+        <v>0.4138925222810439</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3705053463686743</v>
+        <v>0.3402559817557795</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3301954296116842</v>
+        <v>0.3289701359452377</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3078874653182906</v>
+        <v>0.2857964679500902</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2860006815297782</v>
+        <v>0.2675720837715398</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2775218715160799</v>
+        <v>0.2558086282299972</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.266986275771683</v>
+        <v>0.2444105951136442</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1345,75 +1345,75 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2452636537460811</v>
+        <v>0.227068264576892</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2278410327166482</v>
+        <v>0.211189916329914</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1988483860608468</v>
+        <v>0.198873992231569</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MIB.PA</t>
+          <t>AASI.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1920618123976403</v>
+        <v>0.1876296534716124</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AASI.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1915037200401066</v>
+        <v>0.1871880720877757</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1870206678004969</v>
+        <v>0.1824498493619942</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.585393775639258</v>
+        <v>1.473246934996625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.572328722520088</v>
+        <v>1.462503806976721</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8944826818504767</v>
+        <v>0.8375064640229155</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8381975877753114</v>
+        <v>0.818901762516216</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7709796707693994</v>
+        <v>0.7660955713268904</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7331392006931017</v>
+        <v>0.6880069211266067</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6459458474690551</v>
+        <v>0.6877595377780827</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6199294045540218</v>
+        <v>0.6260119656083758</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6189073732457309</v>
+        <v>0.6111482326424766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5864478507284048</v>
+        <v>0.5681925056294939</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1616,45 +1616,45 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5464940222633361</v>
+        <v>0.5591749020915062</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5341007240623272</v>
+        <v>0.5432249338222876</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5320165293462102</v>
+        <v>0.5238056231380146</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5103703251591436</v>
+        <v>0.4972219451122559</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5071088163025894</v>
+        <v>0.4955727744471143</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.603633841404627</v>
+        <v>2.545500420828882</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.216376730356573</v>
+        <v>2.206179395247355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.731148103111878</v>
+        <v>1.638385540047988</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.7123839952674</v>
+        <v>1.620263301580029</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.378824952862302</v>
+        <v>1.389489012536056</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.377912198247917</v>
+        <v>1.368986383550332</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.329369858266531</v>
+        <v>1.33263979323524</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.231378334803925</v>
+        <v>1.214550809247295</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.164626390012216</v>
+        <v>1.133510961333397</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.110118783944252</v>
+        <v>1.092553947863117</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.077540391619742</v>
+        <v>1.059439053627902</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.060699939538897</v>
+        <v>1.044926479456288</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1902,45 +1902,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>XMK9.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.058879642913425</v>
+        <v>1.034905216071968</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Xtrackers MSCI Japan UCITS ETF 4C - EUR Hedged</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>XMK9.MI</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.053028965004586</v>
+        <v>1.030951361705928</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI Japan UCITS ETF 4C - EUR Hedged</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>TPXH.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.051134806269113</v>
+        <v>1.021148070857033</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi Japan Topix UCITS ETF Daily Hedged EUR (C)</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8374777948931615</v>
+        <v>0.7750684551605176</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8320940313332001</v>
+        <v>0.7698706244109554</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4998634446725718</v>
+        <v>0.4725634442039359</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4467120426590347</v>
+        <v>0.4486557424047422</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4035757189398312</v>
+        <v>0.4118275663631386</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4007946164931517</v>
+        <v>0.3781971534420514</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3610816774407746</v>
+        <v>0.3459398729401948</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3569965666570933</v>
+        <v>0.3413815304546817</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3018070975391487</v>
+        <v>0.2938276927858983</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2113,30 +2113,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2959007049807312</v>
+        <v>0.284449162705692</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2922423170603994</v>
+        <v>0.2821165832049775</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2653921884756707</v>
+        <v>0.2594285566956194</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2644689165742453</v>
+        <v>0.2534799332246307</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2173,30 +2173,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AJEUAS.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2585559473233707</v>
+        <v>0.2527955148668071</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>AJEUAS.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2472044089611258</v>
+        <v>0.2524317002112406</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,150 +442,150 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>XUCM.L</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.08014724996671596</v>
+        <v>0.04989276785573948</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Xtrackers MSCI USA Communication Services UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>TELW.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.06003909040634037</v>
+        <v>0.04375928065927681</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Communication Services ESG UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04171169842406908</v>
+        <v>0.02761602957757092</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03811170694719523</v>
+        <v>0.02469549394200565</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03742239562991445</v>
+        <v>0.02198873480319308</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HMXJ.MI</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03642790953795538</v>
+        <v>0.02057258482745672</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HSBC MSCI Pacific ex Japan UCITS ETF USD</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TELW.PA</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03455078221533925</v>
+        <v>0.01952451127756327</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Communication Services ESG UCITS ETF DR EUR (A)</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>VMIG.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03392105173939108</v>
+        <v>0.01947419726806743</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TRV.PA</t>
+          <t>INDO.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0333269887476908</v>
+        <v>0.01944524682410376</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Consumer Discretionary UCITS ETF Acc</t>
+          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XUCM.L</t>
+          <t>SEL.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03143032247507449</v>
+        <v>0.0181507247680146</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Communication Services UCITS ETF 1D</t>
+          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03014704816756608</v>
+        <v>0.01798740129911125</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -607,60 +607,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02899066464144573</v>
+        <v>0.01629117659470003</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SEL.PA</t>
+          <t>TRV.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02882340512387094</v>
+        <v>0.01527570212672225</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Consumer Discretionary UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MATW.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02810691637919893</v>
+        <v>0.01524309764110865</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>HMXJ.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02785060185847743</v>
+        <v>0.01519020219202782</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>HSBC MSCI Pacific ex Japan UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1745754199669611</v>
+        <v>0.1903248697263886</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09495335393725823</v>
+        <v>0.09659218981786322</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07493607211046438</v>
+        <v>0.06159696471941767</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -743,15 +743,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>SRIJC.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0740625005706439</v>
+        <v>0.05945836069221611</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.06951067579670611</v>
+        <v>0.05155741359849375</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -773,150 +773,150 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05610246940250874</v>
+        <v>0.04950876575329577</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JPXX.L</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.05122583217061982</v>
+        <v>0.04566066290299853</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DSP5.PA</t>
+          <t>JPXH.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05098168134574044</v>
+        <v>0.04520504704001316</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - EUR Hedged (C)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>DSP5.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.04934422987529596</v>
+        <v>0.04505197809821682</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JPXH.PA</t>
+          <t>JPXX.L</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.04635018260662838</v>
+        <v>0.04332344213649852</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - EUR Hedged (C)</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XSMC.SW</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04184821686304363</v>
+        <v>0.04112583439285999</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Xtrackers Swiss Large Cap UCITS ETF 1C</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HMXJ.MI</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03713271962819165</v>
+        <v>0.03996222376737313</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HSBC MSCI Pacific ex Japan UCITS ETF USD</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>XDWU.MI</t>
+          <t>XSMC.SW</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.03706826292938636</v>
+        <v>0.03678319838961741</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
+          <t>Xtrackers Swiss Large Cap UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CD9.PA</t>
+          <t>VMIG.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.03678353606703211</v>
+        <v>0.0311207012430863</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
+          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UTI.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.03668294767054125</v>
+        <v>0.03019300442054229</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Utilities UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4077650306531748</v>
+        <v>0.4053152507278786</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3046317616563878</v>
+        <v>0.2787626991582364</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -984,195 +984,195 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2396759715832568</v>
+        <v>0.2178807747928169</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.217906525601834</v>
+        <v>0.2131338089339956</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1958000346931188</v>
+        <v>0.162785634951</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1953749370954068</v>
+        <v>0.1575849190475112</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1806977503029152</v>
+        <v>0.1483427287948529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1577253557041596</v>
+        <v>0.1454224656628695</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CU2.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1512424719623873</v>
+        <v>0.1445603357372138</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1477018557720302</v>
+        <v>0.1444953297481932</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>CU2.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1406751345810116</v>
+        <v>0.1334962748531587</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>AUSSE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1402617957829566</v>
+        <v>0.1261019986157619</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>BNP Paribas Easy ESG Enhanced US UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1385472818394888</v>
+        <v>0.1255039531992712</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AUSSE.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1374723968508647</v>
+        <v>0.1254523593858936</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy ESG Enhanced US UCITS ETF EUR Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1300801514781544</v>
+        <v>0.1220629838189076</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5756853396901074</v>
+        <v>0.4983678058182117</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5723460518362817</v>
+        <v>0.4964879981791765</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4138925222810439</v>
+        <v>0.3740731409187912</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3402559817557795</v>
+        <v>0.3236563763195164</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1270,165 +1270,165 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3289701359452377</v>
+        <v>0.2883623845904595</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2857964679500902</v>
+        <v>0.2658584714023544</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2675720837715398</v>
+        <v>0.2554509632193502</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2558086282299972</v>
+        <v>0.2372057804148724</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2444105951136442</v>
+        <v>0.2271353823487843</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.227068264576892</v>
+        <v>0.2094459434026452</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.211189916329914</v>
+        <v>0.1937149044045556</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.198873992231569</v>
+        <v>0.1884278176374348</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AASI.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1876296534716124</v>
+        <v>0.1747750339425604</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>MIB.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1871880720877757</v>
+        <v>0.1692408455832792</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AJEUAS.MI</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1824498493619942</v>
+        <v>0.1543494143217929</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.473246934996625</v>
+        <v>1.450726870307217</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.462503806976721</v>
+        <v>1.444607270949144</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8375064640229155</v>
+        <v>0.8454670953288708</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.818901762516216</v>
+        <v>0.8182447651584031</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7660955713268904</v>
+        <v>0.7706639620726727</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1541,105 +1541,105 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6880069211266067</v>
+        <v>0.7146490938668881</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6877595377780827</v>
+        <v>0.7055679839325364</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6260119656083758</v>
+        <v>0.6057036274010006</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6111482326424766</v>
+        <v>0.5809859904569437</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5681925056294939</v>
+        <v>0.5594107560226222</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5591749020915062</v>
+        <v>0.5514734070031626</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5432249338222876</v>
+        <v>0.5333099794590372</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5238056231380146</v>
+        <v>0.5120182766659234</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1661,15 +1661,15 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>XMK9.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4972219451122559</v>
+        <v>0.4948527158826841</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI Japan UCITS ETF 4C - EUR Hedged</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4955727744471143</v>
+        <v>0.4940017680601687</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.545500420828882</v>
+        <v>2.539759745195758</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.206179395247355</v>
+        <v>2.20690805100688</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.638385540047988</v>
+        <v>1.58014187430276</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.620263301580029</v>
+        <v>1.572416565162146</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1782,30 +1782,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.389489012536056</v>
+        <v>1.39024392527477</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.368986383550332</v>
+        <v>1.367244376766853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.33263979323524</v>
+        <v>1.326106443541798</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.214550809247295</v>
+        <v>1.202866291989947</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.133510961333397</v>
+        <v>1.159560050085224</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.092553947863117</v>
+        <v>1.087553202997646</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.059439053627902</v>
+        <v>1.057690530905431</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1887,60 +1887,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EJAH.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.044926479456288</v>
+        <v>1.041197100355598</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>XMK9.MI</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.034905216071968</v>
+        <v>1.038232851827249</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI Japan UCITS ETF 4C - EUR Hedged</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>EJAH.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.030951361705928</v>
+        <v>1.021849694579522</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TPXH.PA</t>
+          <t>XMK9.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.021148070857033</v>
+        <v>1.010749065834857</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Japan Topix UCITS ETF Daily Hedged EUR (C)</t>
+          <t>Xtrackers MSCI Japan UCITS ETF 4C - EUR Hedged</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7750684551605176</v>
+        <v>0.7403727605991994</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7698706244109554</v>
+        <v>0.7384262317971371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4725634442039359</v>
+        <v>0.4671034441102087</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4486557424047422</v>
+        <v>0.4559983449461027</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4118275663631386</v>
+        <v>0.372249384192231</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3781971534420514</v>
+        <v>0.3700024221953806</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3459398729401948</v>
+        <v>0.3381472300470052</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3413815304546817</v>
+        <v>0.3224084742927136</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2098,90 +2098,90 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2938276927858983</v>
+        <v>0.2916217397748451</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.284449162705692</v>
+        <v>0.2837361937683551</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2821165832049775</v>
+        <v>0.2835636441642766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AASI.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2594285566956194</v>
+        <v>0.2597069725541608</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2534799332246307</v>
+        <v>0.2468050388127152</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>AASI.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2527955148668071</v>
+        <v>0.243746460676084</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2524317002112406</v>
+        <v>0.2394112750602704</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -833,30 +833,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JPXX.L</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.04332344213649852</v>
+        <v>0.04112583439285999</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>JPXX.L</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04112583439285999</v>
+        <v>0.04075173095944606</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
         </is>
       </c>
     </row>
@@ -2173,30 +2173,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AASI.PA</t>
+          <t>AJEUAS.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.243746460676084</v>
+        <v>0.2394112750602704</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AJEUAS.MI</t>
+          <t>AASI.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2394112750602704</v>
+        <v>0.2311565994483351</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -472,195 +472,195 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02761602957757092</v>
+        <v>0.02996775690895981</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02469549394200565</v>
+        <v>0.02761602957757092</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02198873480319308</v>
+        <v>0.02469549394200565</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02057258482745672</v>
+        <v>0.0222329789704212</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01952451127756327</v>
+        <v>0.02184514837675122</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VMIG.MI</t>
+          <t>INDO.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01947419726806743</v>
+        <v>0.02016007983265511</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
+          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>INDO.PA</t>
+          <t>VMIG.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01944524682410376</v>
+        <v>0.01947419726806743</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
+          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SEL.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0181507247680146</v>
+        <v>0.01870955102899607</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>SEL.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.01798740129911125</v>
+        <v>0.0181507247680146</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.01629117659470003</v>
+        <v>0.01798740129911125</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TRV.PA</t>
+          <t>HMXJ.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01527570212672225</v>
+        <v>0.01559345296631931</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Consumer Discretionary UCITS ETF Acc</t>
+          <t>HSBC MSCI Pacific ex Japan UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>TRV.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01524309764110865</v>
+        <v>0.01527570212672225</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi STOXX Europe 600 Consumer Discretionary UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HMXJ.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01519020219202782</v>
+        <v>0.01476772770401946</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HSBC MSCI Pacific ex Japan UCITS ETF USD</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1903248697263886</v>
+        <v>0.1908544923506952</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09659218981786322</v>
+        <v>0.1039603835382592</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -758,75 +758,75 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05155741359849375</v>
+        <v>0.05183273004833389</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04950876575329577</v>
+        <v>0.05155741359849375</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>DSP5.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04566066290299853</v>
+        <v>0.04593756294313556</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JPXH.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04520504704001316</v>
+        <v>0.04319349713672183</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - EUR Hedged (C)</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DSP5.PA</t>
+          <t>JPXH.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.04505197809821682</v>
+        <v>0.04219775661414982</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - EUR Hedged (C)</t>
         </is>
       </c>
     </row>
@@ -863,30 +863,30 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>XSMC.SW</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03996222376737313</v>
+        <v>0.03678319838961741</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Xtrackers Swiss Large Cap UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>XSMC.SW</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.03678319838961741</v>
+        <v>0.03158874913734588</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Xtrackers Swiss Large Cap UCITS ETF 1C</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -908,15 +908,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>FUSR.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.03019300442054229</v>
+        <v>0.0298685283742921</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Fidelity US Equity Research Enhanced UCITS ETF ACC-USD</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4053152507278786</v>
+        <v>0.405940531077805</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2787626991582364</v>
+        <v>0.2642475600176597</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2131338089339956</v>
+        <v>0.2065280163456105</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1575849190475112</v>
+        <v>0.1482643805411865</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1044,120 +1044,120 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1483427287948529</v>
+        <v>0.1454224656628695</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1454224656628695</v>
+        <v>0.1445603357372138</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1445603357372138</v>
+        <v>0.1376084930931545</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>CU2.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1444953297481932</v>
+        <v>0.1334962748531587</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CU2.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1334962748531587</v>
+        <v>0.1303191723508559</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AUSSE.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1261019986157619</v>
+        <v>0.1255039531992712</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy ESG Enhanced US UCITS ETF EUR Acc</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1255039531992712</v>
+        <v>0.1254523593858936</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>AUSSE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1254523593858936</v>
+        <v>0.1230435145515605</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>BNP Paribas Easy ESG Enhanced US UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4964879981791765</v>
+        <v>0.4730002055310245</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3740731409187912</v>
+        <v>0.3584761401281877</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2883623845904595</v>
+        <v>0.2889356279835356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1315,30 +1315,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2372057804148724</v>
+        <v>0.2195007573881751</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2271353823487843</v>
+        <v>0.2168507474244603</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1884278176374348</v>
+        <v>0.1819565548535886</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1420,15 +1420,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1543494143217929</v>
+        <v>0.1540387790218127</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.444607270949144</v>
+        <v>1.40623848432601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8454670953288708</v>
+        <v>0.8245193372454613</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8182447651584031</v>
+        <v>0.8040505521009922</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7146490938668881</v>
+        <v>0.7154120090810072</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7055679839325364</v>
+        <v>0.6968335791946993</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6057036274010006</v>
+        <v>0.5858648370246895</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5594107560226222</v>
+        <v>0.5500272252421157</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5514734070031626</v>
+        <v>0.5389813924705182</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5333099794590372</v>
+        <v>0.5237704886987573</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1646,30 +1646,30 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>XMK9.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5120182766659234</v>
+        <v>0.4929542034642149</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Xtrackers MSCI Japan UCITS ETF 4C - EUR Hedged</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4948527158826841</v>
+        <v>0.4924512783762631</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4940017680601687</v>
+        <v>0.4886813900933988</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.20690805100688</v>
+        <v>2.181086956170705</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.572416565162146</v>
+        <v>1.532041776349462</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.39024392527477</v>
+        <v>1.364472980779404</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.367244376766853</v>
+        <v>1.354354186712152</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.202866291989947</v>
+        <v>1.207314038462553</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.159560050085224</v>
+        <v>1.155668861969416</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.057690530905431</v>
+        <v>1.048028197532126</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1887,30 +1887,30 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.041197100355598</v>
+        <v>1.038232851827249</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.038232851827249</v>
+        <v>1.025262399434244</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.021849694579522</v>
+        <v>1.014649566174635</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7384262317971371</v>
+        <v>0.71114115171882</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2008,30 +2008,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4671034441102087</v>
+        <v>0.4566461762096918</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4559983449461027</v>
+        <v>0.4504504633508413</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3381472300470052</v>
+        <v>0.3161314656165304</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3224084742927136</v>
+        <v>0.3141811076213756</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2597069725541608</v>
+        <v>0.2664835798238001</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2468050388127152</v>
+        <v>0.2400158986338692</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2394112750602704</v>
+        <v>0.2365292948964608</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,225 +442,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>XUCM.L</t>
+          <t>INDO.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04989276785573948</v>
+        <v>0.06054068203977581</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Communication Services UCITS ETF 1D</t>
+          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TELW.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04375928065927681</v>
+        <v>0.05701916898927206</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Communication Services ESG UCITS ETF DR EUR (A)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02996775690895981</v>
+        <v>0.05541497635731574</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>DSP5.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02761602957757092</v>
+        <v>0.04065658464473798</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02469549394200565</v>
+        <v>0.03897023564665103</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>EPRU.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0222329789704212</v>
+        <v>0.03302058114475126</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi FTSE EPRA NAREIT Global UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>HPRA.L</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02184514837675122</v>
+        <v>0.03233261190539216</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>HSBC FTSE EPRA NAREIT Developed UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>INDO.PA</t>
+          <t>UINC.L</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02016007983265511</v>
+        <v>0.03053306342780027</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
+          <t>First Trust US Equity Income UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VMIG.MI</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01947419726806743</v>
+        <v>0.02953295402920331</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01870955102899607</v>
+        <v>0.0265283656259232</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SEL.PA</t>
+          <t>XDWS.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0181507247680146</v>
+        <v>0.02437758119972178</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
+          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.01798740129911125</v>
+        <v>0.02322807435273977</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HMXJ.MI</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01559345296631931</v>
+        <v>0.02149892925412589</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>HSBC MSCI Pacific ex Japan UCITS ETF USD</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TRV.PA</t>
+          <t>CD9.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01527570212672225</v>
+        <v>0.02032349138299305</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Consumer Discretionary UCITS ETF Acc</t>
+          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>SEL.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01476772770401946</v>
+        <v>0.01998729461630444</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1908544923506952</v>
+        <v>0.08911232647218092</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1039603835382592</v>
+        <v>0.07575582007510828</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -728,195 +728,195 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.06159696471941767</v>
+        <v>0.06972261432295568</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SRIJC.PA</t>
+          <t>DSP5.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05945836069221611</v>
+        <v>0.06721672725838257</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05183273004833389</v>
+        <v>0.06693915701380093</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>CD9.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05155741359849375</v>
+        <v>0.05195635484014516</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DSP5.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04593756294313556</v>
+        <v>0.0512820981472295</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04319349713672183</v>
+        <v>0.04701015617161808</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JPXH.PA</t>
+          <t>UINC.L</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.04219775661414982</v>
+        <v>0.04435230489480047</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - EUR Hedged (C)</t>
+          <t>First Trust US Equity Income UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>SRIJC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.04112583439285999</v>
+        <v>0.04083913873336265</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>JPXX.L</t>
+          <t>HPRA.L</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04075173095944606</v>
+        <v>0.04022609690459755</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
+          <t>HSBC FTSE EPRA NAREIT Developed UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>XSMC.SW</t>
+          <t>STU.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03678319838961741</v>
+        <v>0.03989150776921724</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Xtrackers Swiss Large Cap UCITS ETF 1C</t>
+          <t>State Street SPDR MSCI Europe Utilities UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>XDWS.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.03158874913734588</v>
+        <v>0.03888008711938173</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VMIG.MI</t>
+          <t>UTI.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0311207012430863</v>
+        <v>0.03884198234473613</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
+          <t>Amundi STOXX Europe 600 Utilities UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FUSR.MI</t>
+          <t>XDWU.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0298685283742921</v>
+        <v>0.03877089727030492</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fidelity US Equity Research Enhanced UCITS ETF ACC-USD</t>
+          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.405940531077805</v>
+        <v>0.2876712144544282</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2642475600176597</v>
+        <v>0.2083916226935365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -984,30 +984,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2178807747928169</v>
+        <v>0.1659372283026295</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2065280163456105</v>
+        <v>0.1621102136279369</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.162785634951</v>
+        <v>0.1120966045138083</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1029,150 +1029,150 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1482643805411865</v>
+        <v>0.1063716917013025</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>CU2.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1454224656628695</v>
+        <v>0.1063306735974654</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1445603357372138</v>
+        <v>0.1021140189452283</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>AUSSE.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1376084930931545</v>
+        <v>0.1014156196638942</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>BNP Paribas Easy ESG Enhanced US UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CU2.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1334962748531587</v>
+        <v>0.1012630247453243</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1303191723508559</v>
+        <v>0.09866918659091417</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>DJE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1255039531992712</v>
+        <v>0.09597927927992767</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>Amundi Dow Jones Industrial Average UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1254523593858936</v>
+        <v>0.09501119284342274</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AUSSE.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1230435145515605</v>
+        <v>0.094813228728587</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy ESG Enhanced US UCITS ETF EUR Acc</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>UINC.L</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1220629838189076</v>
+        <v>0.09390527433378248</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>First Trust US Equity Income UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1210,30 +1210,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4983678058182117</v>
+        <v>0.4750222581304133</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4730002055310245</v>
+        <v>0.4737991898250267</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3584761401281877</v>
+        <v>0.3340195894672486</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3236563763195164</v>
+        <v>0.3095066389046062</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1270,15 +1270,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2889356279835356</v>
+        <v>0.2856489358068428</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2658584714023544</v>
+        <v>0.2329946654533137</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,75 +1300,75 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2554509632193502</v>
+        <v>0.2276341201474525</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2195007573881751</v>
+        <v>0.2267442279535092</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2168507474244603</v>
+        <v>0.226165436064532</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2094459434026452</v>
+        <v>0.2100793276989026</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1937149044045556</v>
+        <v>0.2014307122439045</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1819565548535886</v>
+        <v>0.1717345455155606</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1390,45 +1390,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>MIB.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1747750339425604</v>
+        <v>0.1656967609295246</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MIB.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1692408455832792</v>
+        <v>0.1647457834017478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1540387790218127</v>
+        <v>0.1533776872048123</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.450726870307217</v>
+        <v>1.383481786996342</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.40623848432601</v>
+        <v>1.379753282127959</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8245193372454613</v>
+        <v>0.7513513339358235</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8040505521009922</v>
+        <v>0.7400033901082925</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7706639620726727</v>
+        <v>0.7141871478403197</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7154120090810072</v>
+        <v>0.6058284702751238</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6968335791946993</v>
+        <v>0.6007363529609315</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5858648370246895</v>
+        <v>0.572953003919441</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5809859904569437</v>
+        <v>0.535500885827656</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5500272252421157</v>
+        <v>0.5208732862114545</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5389813924705182</v>
+        <v>0.5125613893168215</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5237704886987573</v>
+        <v>0.5033290410625424</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1646,45 +1646,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>XMK9.MI</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4929542034642149</v>
+        <v>0.4597418792791612</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI Japan UCITS ETF 4C - EUR Hedged</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4924512783762631</v>
+        <v>0.4569944934423382</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EJAH.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4886813900933988</v>
+        <v>0.4528541718634862</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.539759745195758</v>
+        <v>2.469066683789146</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.181086956170705</v>
+        <v>2.128385607521404</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.58014187430276</v>
+        <v>1.538564600980179</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.532041776349462</v>
+        <v>1.529618854888041</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1782,45 +1782,45 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.364472980779404</v>
+        <v>1.309170251810208</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.354354186712152</v>
+        <v>1.302298248419975</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.326106443541798</v>
+        <v>1.278439952379164</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.207314038462553</v>
+        <v>1.151021382436306</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.155668861969416</v>
+        <v>1.084669971907137</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.087553202997646</v>
+        <v>1.069701775226965</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.048028197532126</v>
+        <v>1.01588548803332</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.038232851827249</v>
+        <v>0.9818439708091804</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1902,15 +1902,15 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.025262399434244</v>
+        <v>0.9716647699768992</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.014649566174635</v>
+        <v>0.9557807180865427</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1932,15 +1932,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XMK9.MI</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.010749065834857</v>
+        <v>0.9442939102454133</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI Japan UCITS ETF 4C - EUR Hedged</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7403727605991994</v>
+        <v>0.7111552818405416</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2008,135 +2008,135 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4566461762096918</v>
+        <v>0.415233378131465</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4504504633508413</v>
+        <v>0.3804125730547916</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.372249384192231</v>
+        <v>0.3511298542069516</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3700024221953806</v>
+        <v>0.3351161290803968</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3161314656165304</v>
+        <v>0.3213457265204074</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3141811076213756</v>
+        <v>0.3182351658323452</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2916217397748451</v>
+        <v>0.3080057294780973</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2837361937683551</v>
+        <v>0.2994533368114995</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2835636441642766</v>
+        <v>0.2965513106833302</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2664835798238001</v>
+        <v>0.2586081161389506</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2400158986338692</v>
+        <v>0.2234424564211985</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2173,30 +2173,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AJEUAS.MI</t>
+          <t>AASI.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2365292948964608</v>
+        <v>0.2143700616399511</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AASI.PA</t>
+          <t>AJEUAS.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2311565994483351</v>
+        <v>0.2085327815427624</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.06054068203977581</v>
+        <v>0.05201007843669703</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -457,15 +457,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05701916898927206</v>
+        <v>0.03381648473674725</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05541497635731574</v>
+        <v>0.03377953051209781</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -487,15 +487,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DSP5.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04065658464473798</v>
+        <v>0.0302698301366302</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03897023564665103</v>
+        <v>0.02236554671001989</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -517,60 +517,60 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EPRU.AS</t>
+          <t>DSP5.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03302058114475126</v>
+        <v>0.02227171920202875</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi FTSE EPRA NAREIT Global UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HPRA.L</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03233261190539216</v>
+        <v>0.01948182387575992</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HSBC FTSE EPRA NAREIT Developed UCITS ETF USD (Acc)</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UINC.L</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03053306342780027</v>
+        <v>0.01885401076453741</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>First Trust US Equity Income UCITS ETF Dist</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>HPRA.L</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02953295402920331</v>
+        <v>0.01878281619028632</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>HSBC FTSE EPRA NAREIT Developed UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0265283656259232</v>
+        <v>0.01678784817110368</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -592,75 +592,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XDWS.MI</t>
+          <t>BERMIB.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02437758119972178</v>
+        <v>0.01492899432521755</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
+          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>UINC.L</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02322807435273977</v>
+        <v>0.01472064235530279</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>First Trust US Equity Income UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>IPRP.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02149892925412589</v>
+        <v>0.01193431765545294</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>iShares European Property Yield UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CD9.PA</t>
+          <t>SEL.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02032349138299305</v>
+        <v>0.01119794546361352</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
+          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SEL.PA</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01998729461630444</v>
+        <v>0.00985102061494314</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -698,15 +698,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.08911232647218092</v>
+        <v>0.09561844874414627</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07575582007510828</v>
+        <v>0.07895031912824879</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.06972261432295568</v>
+        <v>0.07677548966772885</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -743,180 +743,180 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DSP5.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06721672725838257</v>
+        <v>0.07312440645773988</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>DSP5.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.06693915701380093</v>
+        <v>0.0606293599668144</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CD9.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05195635484014516</v>
+        <v>0.05493416400078721</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>CD9.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0512820981472295</v>
+        <v>0.05469421668887042</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>HPRA.L</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04701015617161808</v>
+        <v>0.05013527533290563</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>HSBC FTSE EPRA NAREIT Developed UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UINC.L</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.04435230489480047</v>
+        <v>0.04781071039086449</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>First Trust US Equity Income UCITS ETF Dist</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SRIJC.PA</t>
+          <t>STU.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.04083913873336265</v>
+        <v>0.0401552128167435</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
+          <t>State Street SPDR MSCI Europe Utilities UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HPRA.L</t>
+          <t>UINC.L</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04022609690459755</v>
+        <v>0.03948900305290848</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HSBC FTSE EPRA NAREIT Developed UCITS ETF USD (Acc)</t>
+          <t>First Trust US Equity Income UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STU.PA</t>
+          <t>VMIG.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03989150776921724</v>
+        <v>0.03739807143417062</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Utilities UCITS ETF EUR</t>
+          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>XDWS.MI</t>
+          <t>UTI.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.03888008711938173</v>
+        <v>0.03729011717867925</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
+          <t>Amundi STOXX Europe 600 Utilities UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UTI.PA</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.03884198234473613</v>
+        <v>0.03596126192839977</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Utilities UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XDWU.MI</t>
+          <t>XDEB.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.03877089727030492</v>
+        <v>0.03583171198247825</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
+          <t>Xtrackers MSCI World Minimum Volatility UCITS ETF 1C</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2876712144544282</v>
+        <v>0.2521496050146375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2083916226935365</v>
+        <v>0.2402826874969812</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -984,75 +984,75 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1659372283026295</v>
+        <v>0.183040522988287</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1621102136279369</v>
+        <v>0.1788104477034851</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1120966045138083</v>
+        <v>0.1267923768566139</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1063716917013025</v>
+        <v>0.1264329144233358</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CU2.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1063306735974654</v>
+        <v>0.1248384977810628</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1021140189452283</v>
+        <v>0.1233886343725135</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1074,105 +1074,105 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AUSSE.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1014156196638942</v>
+        <v>0.1222343237038015</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy ESG Enhanced US UCITS ETF EUR Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>CU2.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1012630247453243</v>
+        <v>0.1134510076889341</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.09866918659091417</v>
+        <v>0.1074468372201651</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DJE.PA</t>
+          <t>AUSSE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.09597927927992767</v>
+        <v>0.1065664125913828</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Dow Jones Industrial Average UCITS ETF Dist</t>
+          <t>BNP Paribas Easy ESG Enhanced US UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.09501119284342274</v>
+        <v>0.1062048103623094</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.094813228728587</v>
+        <v>0.1035411522093419</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UINC.L</t>
+          <t>MIB.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.09390527433378248</v>
+        <v>0.09848100381611657</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>First Trust US Equity Income UCITS ETF Dist</t>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1210,30 +1210,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4750222581304133</v>
+        <v>0.4793382742584864</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4737991898250267</v>
+        <v>0.4716455277537484</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3340195894672486</v>
+        <v>0.3714508686627873</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3095066389046062</v>
+        <v>0.3389788166330157</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2856489358068428</v>
+        <v>0.3048498845265588</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1285,30 +1285,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2329946654533137</v>
+        <v>0.2528718324824308</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2276341201474525</v>
+        <v>0.2434472525382159</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2267442279535092</v>
+        <v>0.2425581913888291</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1330,15 +1330,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.226165436064532</v>
+        <v>0.2407747486361096</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2100793276989026</v>
+        <v>0.2192411365342659</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1360,75 +1360,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2014307122439045</v>
+        <v>0.2177005272677384</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1717345455155606</v>
+        <v>0.2093824032560903</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MIB.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1656967609295246</v>
+        <v>0.1842699356857034</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>MIB.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1647457834017478</v>
+        <v>0.1774479894669059</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1533776872048123</v>
+        <v>0.1615264133897674</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.383481786996342</v>
+        <v>1.426113844915488</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.379753282127959</v>
+        <v>1.411072713326597</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7513513339358235</v>
+        <v>0.7790166359691173</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7400033901082925</v>
+        <v>0.7557515583608745</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7141871478403197</v>
+        <v>0.7030521529802971</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1541,45 +1541,45 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6058284702751238</v>
+        <v>0.5698564422875954</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6007363529609315</v>
+        <v>0.5585153765901885</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.572953003919441</v>
+        <v>0.5563564402526651</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.535500885827656</v>
+        <v>0.5401895900539366</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5208732862114545</v>
+        <v>0.522408012152797</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5125613893168215</v>
+        <v>0.5165951193751319</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5033290410625424</v>
+        <v>0.5163726526775623</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1646,45 +1646,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4597418792791612</v>
+        <v>0.4715031013261297</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4569944934423382</v>
+        <v>0.4648364964854219</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>EJAH.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4528541718634862</v>
+        <v>0.4569376565065963</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.469066683789146</v>
+        <v>2.442538791275087</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.128385607521404</v>
+        <v>2.113191702393801</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.538564600980179</v>
+        <v>1.600132307048423</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.529618854888041</v>
+        <v>1.576548277721933</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1782,45 +1782,45 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.309170251810208</v>
+        <v>1.406787655534381</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.302298248419975</v>
+        <v>1.267843955024186</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.278439952379164</v>
+        <v>1.265154895339548</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.151021382436306</v>
+        <v>1.179499752671411</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1842,30 +1842,30 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>MIB.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.084669971907137</v>
+        <v>1.061302538015793</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MIB.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.069701775226965</v>
+        <v>1.06085254299206</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.01588548803332</v>
+        <v>1.039712244175045</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9818439708091804</v>
+        <v>1.022692770912323</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1902,45 +1902,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9716647699768992</v>
+        <v>0.9704912309727063</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EJAH.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9557807180865427</v>
+        <v>0.9534067453423805</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>EJAH.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9442939102454133</v>
+        <v>0.9512990695868226</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7111552818405416</v>
+        <v>0.7300606417820863</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.71114115171882</v>
+        <v>0.7214562925024355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.415233378131465</v>
+        <v>0.4373463589845594</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2023,30 +2023,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3804125730547916</v>
+        <v>0.3546063724105031</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3511298542069516</v>
+        <v>0.3523378254165284</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3351161290803968</v>
+        <v>0.3410757772328803</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3213457265204074</v>
+        <v>0.3395067508554099</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3182351658323452</v>
+        <v>0.3259797979508603</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3080057294780973</v>
+        <v>0.3196954187822831</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2994533368114995</v>
+        <v>0.3080537923465341</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2965513106833302</v>
+        <v>0.3078008184581187</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2586081161389506</v>
+        <v>0.2668498187180353</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2158,30 +2158,30 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>AASI.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2234424564211985</v>
+        <v>0.2311565994483351</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AASI.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2143700616399511</v>
+        <v>0.2308306137366269</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2085327815427624</v>
+        <v>0.2257217907541051</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05201007843669703</v>
+        <v>0.06239367179991939</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -457,60 +457,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03381648473674725</v>
+        <v>0.03863993936329346</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03377953051209781</v>
+        <v>0.02830360890846984</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0302698301366302</v>
+        <v>0.02506681909276698</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02236554671001989</v>
+        <v>0.02325188184652704</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02227171920202875</v>
+        <v>0.02121049313492418</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -532,15 +532,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01948182387575992</v>
+        <v>0.02001095235347172</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01885401076453741</v>
+        <v>0.01984360846487054</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -562,105 +562,105 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HPRA.L</t>
+          <t>EPRU.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01878281619028632</v>
+        <v>0.01942099614858228</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>HSBC FTSE EPRA NAREIT Developed UCITS ETF USD (Acc)</t>
+          <t>Amundi FTSE EPRA NAREIT Global UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>UINC.L</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01678784817110368</v>
+        <v>0.01917900403768513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>First Trust US Equity Income UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BERMIB.MI</t>
+          <t>HPRA.L</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.01492899432521755</v>
+        <v>0.01880931529864571</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>HSBC FTSE EPRA NAREIT Developed UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UINC.L</t>
+          <t>VMIG.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.01472064235530279</v>
+        <v>0.01782596702315842</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>First Trust US Equity Income UCITS ETF Dist</t>
+          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IPRP.AS</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01193431765545294</v>
+        <v>0.01658601126000492</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares European Property Yield UCITS ETF</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEL.PA</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01119794546361352</v>
+        <v>0.01351904582534158</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>HLT.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.00985102061494314</v>
+        <v>0.01202118492463833</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.09561844874414627</v>
+        <v>0.1009083728680551</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -713,105 +713,105 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07895031912824879</v>
+        <v>0.0833808630846391</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07677548966772885</v>
+        <v>0.07701913686141171</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07312440645773988</v>
+        <v>0.07460141471310733</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DSP5.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0606293599668144</v>
+        <v>0.05365987529861393</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>EPRU.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05493416400078721</v>
+        <v>0.05360931431041771</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi FTSE EPRA NAREIT Global UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CD9.PA</t>
+          <t>HPRA.L</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.05469421668887042</v>
+        <v>0.05326346902922463</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
+          <t>HSBC FTSE EPRA NAREIT Developed UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HPRA.L</t>
+          <t>CD9.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05013527533290563</v>
+        <v>0.05103361868758771</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HSBC FTSE EPRA NAREIT Developed UCITS ETF USD (Acc)</t>
+          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.04781071039086449</v>
+        <v>0.04919471398554931</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -833,30 +833,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STU.PA</t>
+          <t>DSP5.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0401552128167435</v>
+        <v>0.04896563383083974</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Utilities UCITS ETF EUR</t>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UINC.L</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03948900305290848</v>
+        <v>0.04704921045536614</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>First Trust US Equity Income UCITS ETF Dist</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03739807143417062</v>
+        <v>0.04495719715443469</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -878,45 +878,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>UTI.PA</t>
+          <t>SRIJC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.03729011717867925</v>
+        <v>0.0430981866917286</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Utilities UCITS ETF Acc</t>
+          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.03596126192839977</v>
+        <v>0.04184380415724975</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XDEB.MI</t>
+          <t>JPXX.L</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.03583171198247825</v>
+        <v>0.04042282470392489</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Minimum Volatility UCITS ETF 1C</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2521496050146375</v>
+        <v>0.2761238637127978</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2402826874969812</v>
+        <v>0.2546453032627429</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.183040522988287</v>
+        <v>0.2173912497179185</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1788104477034851</v>
+        <v>0.180121839337765</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,45 +1014,45 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1267923768566139</v>
+        <v>0.1756423454542362</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1264329144233358</v>
+        <v>0.1741879475769921</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1248384977810628</v>
+        <v>0.1587366972627957</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1233886343725135</v>
+        <v>0.147724358374518</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1074,105 +1074,105 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1222343237038015</v>
+        <v>0.1364548086721362</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CU2.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1134510076889341</v>
+        <v>0.1358982852655304</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1074468372201651</v>
+        <v>0.1228808938369763</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AUSSE.PA</t>
+          <t>SRIJC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1065664125913828</v>
+        <v>0.1205463350973313</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy ESG Enhanced US UCITS ETF EUR Acc</t>
+          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1062048103623094</v>
+        <v>0.1191219959093686</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1035411522093419</v>
+        <v>0.1189091510950377</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MIB.PA</t>
+          <t>AJASE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.09848100381611657</v>
+        <v>0.117248868800802</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+          <t>BNP Paribas Easy ESG Enhanced Japan UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4793382742584864</v>
+        <v>0.5763306255286258</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4716455277537484</v>
+        <v>0.5708089378347665</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3714508686627873</v>
+        <v>0.3966437288158093</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3389788166330157</v>
+        <v>0.3911471687992003</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3048498845265588</v>
+        <v>0.3164090479656332</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1285,75 +1285,75 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2528718324824308</v>
+        <v>0.3163859321227671</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2434472525382159</v>
+        <v>0.2725743885339453</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2425581913888291</v>
+        <v>0.2593441486175527</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2407747486361096</v>
+        <v>0.2580263750956704</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2192411365342659</v>
+        <v>0.2447938529679354</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2177005272677384</v>
+        <v>0.2433300188446816</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2093824032560903</v>
+        <v>0.2336813125687132</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1842699356857034</v>
+        <v>0.2051295991829638</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1405,30 +1405,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MIB.PA</t>
+          <t>AASI.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1774479894669059</v>
+        <v>0.2024245654460752</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>MIB.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1615264133897674</v>
+        <v>0.1993280494295895</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.426113844915488</v>
+        <v>1.500110988017252</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.411072713326597</v>
+        <v>1.49523869441843</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1496,30 +1496,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7790166359691173</v>
+        <v>0.8058844124785625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7557515583608745</v>
+        <v>0.7962187780172734</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7030521529802971</v>
+        <v>0.732646296012488</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1541,75 +1541,75 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5698564422875954</v>
+        <v>0.5820531542911882</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5585153765901885</v>
+        <v>0.5747672875177021</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5563564402526651</v>
+        <v>0.5611494116464935</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5401895900539366</v>
+        <v>0.5542037208035138</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.522408012152797</v>
+        <v>0.542360785706018</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5165951193751319</v>
+        <v>0.5414995557168634</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1631,15 +1631,15 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5163726526775623</v>
+        <v>0.5392858296238732</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4715031013261297</v>
+        <v>0.5022046406575238</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1661,30 +1661,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>EJAH.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4648364964854219</v>
+        <v>0.4877294741247062</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EJAH.PA</t>
+          <t>XMK9.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4569376565065963</v>
+        <v>0.4851533854665933</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
+          <t>Xtrackers MSCI Japan UCITS ETF 4C - EUR Hedged</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.442538791275087</v>
+        <v>2.498704830980443</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.113191702393801</v>
+        <v>2.167290744569843</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.600132307048423</v>
+        <v>1.723148548101963</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.576548277721933</v>
+        <v>1.705039422346403</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.406787655534381</v>
+        <v>1.519862348728368</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.267843955024186</v>
+        <v>1.280353158437372</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.265154895339548</v>
+        <v>1.280273274061623</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.179499752671411</v>
+        <v>1.229524298443663</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1842,105 +1842,105 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MIB.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.061302538015793</v>
+        <v>1.105374818297953</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>MIB.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.06085254299206</v>
+        <v>1.076815544104001</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.039712244175045</v>
+        <v>1.073383935776818</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.022692770912323</v>
+        <v>1.070605369671253</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9704912309727063</v>
+        <v>1.054890262892628</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>EJAH.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9534067453423805</v>
+        <v>1.001895495325661</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EJAH.PA</t>
+          <t>XMK9.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9512990695868226</v>
+        <v>0.9907895137233422</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
+          <t>Xtrackers MSCI Japan UCITS ETF 4C - EUR Hedged</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7300606417820863</v>
+        <v>0.8119124600029437</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7214562925024355</v>
+        <v>0.8073044372304676</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4373463589845594</v>
+        <v>0.4654654310644233</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2023,15 +2023,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3546063724105031</v>
+        <v>0.3847799414084907</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3523378254165284</v>
+        <v>0.3793327513046731</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2053,90 +2053,90 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3410757772328803</v>
+        <v>0.3767071764713794</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3395067508554099</v>
+        <v>0.3464186884942662</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3259797979508603</v>
+        <v>0.3459742296420358</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3196954187822831</v>
+        <v>0.3458924434021358</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3080537923465341</v>
+        <v>0.3386529365021671</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3078008184581187</v>
+        <v>0.318101316496235</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2668498187180353</v>
+        <v>0.2895605426707437</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2311565994483351</v>
+        <v>0.2640669088832996</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2173,30 +2173,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>AJEUAS.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2308306137366269</v>
+        <v>0.2557254030453187</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AJEUAS.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2257217907541051</v>
+        <v>0.2376197539154727</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,30 +442,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>INDO.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.06239367179991939</v>
+        <v>0.06644251966728598</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>INDO.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03863993936329346</v>
+        <v>0.05678903704035099</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02830360890846984</v>
+        <v>0.05387268794604894</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -487,90 +487,90 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02506681909276698</v>
+        <v>0.04441848052431019</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02325188184652704</v>
+        <v>0.04302265318459764</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DSP5.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02121049313492418</v>
+        <v>0.04277869095595466</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02001095235347172</v>
+        <v>0.03629047453736334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01984360846487054</v>
+        <v>0.0304617433042671</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EPRU.AS</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01942099614858228</v>
+        <v>0.02667995778674315</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi FTSE EPRA NAREIT Global UCITS ETF Acc</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01917900403768513</v>
+        <v>0.01979201610197912</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -592,75 +592,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HPRA.L</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.01880931529864571</v>
+        <v>0.0193480480962871</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HSBC FTSE EPRA NAREIT Developed UCITS ETF USD (Acc)</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VMIG.MI</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.01782596702315842</v>
+        <v>0.01833584737849847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>SEL.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01658601126000492</v>
+        <v>0.0179802793797077</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>ISF.L</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01351904582534158</v>
+        <v>0.017554124801475</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>iShares Core FTSE 100 UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HLT.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01202118492463833</v>
+        <v>0.01732040550629343</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1009083728680551</v>
+        <v>0.1129131354879329</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0833808630846391</v>
+        <v>0.09933774834437092</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -728,90 +728,90 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07701913686141171</v>
+        <v>0.07078142565397361</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07460141471310733</v>
+        <v>0.06591210306857564</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05365987529861393</v>
+        <v>0.06266831341070933</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EPRU.AS</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05360931431041771</v>
+        <v>0.06162090137232012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi FTSE EPRA NAREIT Global UCITS ETF Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HPRA.L</t>
+          <t>CD9.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.05326346902922463</v>
+        <v>0.0546038543897216</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HSBC FTSE EPRA NAREIT Developed UCITS ETF USD (Acc)</t>
+          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CD9.PA</t>
+          <t>VMIG.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05103361868758771</v>
+        <v>0.04531066232774417</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
+          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.04919471398554931</v>
+        <v>0.04491576301416189</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -833,90 +833,90 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DSP5.PA</t>
+          <t>UTI.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.04896563383083974</v>
+        <v>0.04385798932210472</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Utilities UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>STU.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04704921045536614</v>
+        <v>0.04313503743618963</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR MSCI Europe Utilities UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VMIG.MI</t>
+          <t>DSP5.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04495719715443469</v>
+        <v>0.04169408384799356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SRIJC.PA</t>
+          <t>EPRU.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0430981866917286</v>
+        <v>0.04165630474196558</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
+          <t>Amundi FTSE EPRA NAREIT Global UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>INDO.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.04184380415724975</v>
+        <v>0.04152053649122545</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JPXX.L</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04042282470392489</v>
+        <v>0.04105462972868112</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2761238637127978</v>
+        <v>0.2784987082843629</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -969,210 +969,210 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2546453032627429</v>
+        <v>0.2483414250129405</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2173912497179185</v>
+        <v>0.2347946453713687</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.180121839337765</v>
+        <v>0.184291958203781</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1756423454542362</v>
+        <v>0.1731166610874437</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1741879475769921</v>
+        <v>0.1687359150949996</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1587366972627957</v>
+        <v>0.1580083522875726</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.147724358374518</v>
+        <v>0.1421907176534891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1364548086721362</v>
+        <v>0.1358221441690233</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1358982852655304</v>
+        <v>0.135804319779075</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1228808938369763</v>
+        <v>0.1318753681071301</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SRIJC.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1205463350973313</v>
+        <v>0.1280699580460354</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>MIB.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1191219959093686</v>
+        <v>0.1274244111185496</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1189091510950377</v>
+        <v>0.1254594158194677</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AJASE.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.117248868800802</v>
+        <v>0.1207011406112766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy ESG Enhanced Japan UCITS ETF EUR Acc</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5763306255286258</v>
+        <v>0.5130371959389286</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5708089378347665</v>
+        <v>0.5007052773350988</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1240,30 +1240,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3966437288158093</v>
+        <v>0.4307075965416352</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3911471687992003</v>
+        <v>0.3864192774181514</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3164090479656332</v>
+        <v>0.3264840182648401</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3163859321227671</v>
+        <v>0.3007646139577294</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,30 +1300,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2725743885339453</v>
+        <v>0.2545704967257927</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2593441486175527</v>
+        <v>0.2516017227241552</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2580263750956704</v>
+        <v>0.2490735296497484</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1345,30 +1345,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2447938529679354</v>
+        <v>0.2455894093360507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2433300188446816</v>
+        <v>0.2451029411002874</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2336813125687132</v>
+        <v>0.2307339990345461</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1390,45 +1390,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>MIB.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2051295991829638</v>
+        <v>0.2174305339356439</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AASI.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2024245654460752</v>
+        <v>0.208013045185631</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MIB.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1993280494295895</v>
+        <v>0.2015310142402953</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.500110988017252</v>
+        <v>1.552171900208311</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.49523869441843</v>
+        <v>1.528848117233958</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8058844124785625</v>
+        <v>0.8458703776192493</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7962187780172734</v>
+        <v>0.833674194431244</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.732646296012488</v>
+        <v>0.7631881400748834</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5820531542911882</v>
+        <v>0.6161154180814905</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5747672875177021</v>
+        <v>0.5823545033861168</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1571,75 +1571,75 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5611494116464935</v>
+        <v>0.5742379689455686</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5542037208035138</v>
+        <v>0.5636839980732691</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.542360785706018</v>
+        <v>0.5633256411086578</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5414995557168634</v>
+        <v>0.5629755948562558</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5392858296238732</v>
+        <v>0.5510823685040953</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5022046406575238</v>
+        <v>0.5159608431680196</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1661,15 +1661,15 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EJAH.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4877294741247062</v>
+        <v>0.5137013081223922</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4851533854665933</v>
+        <v>0.4840380328104412</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.498704830980443</v>
+        <v>2.562443998384168</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.167290744569843</v>
+        <v>2.200998761707691</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.723148548101963</v>
+        <v>1.716691097036295</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.705039422346403</v>
+        <v>1.684620278860309</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.519862348728368</v>
+        <v>1.523615953644208</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1797,30 +1797,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.280353158437372</v>
+        <v>1.307602898393524</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.280273274061623</v>
+        <v>1.285871978312085</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.229524298443663</v>
+        <v>1.2324669848138</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1842,60 +1842,60 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.105374818297953</v>
+        <v>1.139002211132207</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MIB.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.076815544104001</v>
+        <v>1.124617536250228</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.073383935776818</v>
+        <v>1.11124064039539</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>MIB.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.070605369671253</v>
+        <v>1.096594822892798</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.054890262892628</v>
+        <v>1.060017156140831</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1917,30 +1917,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EJAH.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.001895495325661</v>
+        <v>1.009365524103332</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XMK9.MI</t>
+          <t>EJAH.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9907895137233422</v>
+        <v>0.9905766250434573</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI Japan UCITS ETF 4C - EUR Hedged</t>
+          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8119124600029437</v>
+        <v>0.807615839440728</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8073044372304676</v>
+        <v>0.793661897191309</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4654654310644233</v>
+        <v>0.4687414571559938</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3847799414084907</v>
+        <v>0.4037285633141789</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2038,90 +2038,90 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3793327513046731</v>
+        <v>0.4017879344735997</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3767071764713794</v>
+        <v>0.3830040010866183</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3464186884942662</v>
+        <v>0.3673036395003275</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3459742296420358</v>
+        <v>0.3635296683353095</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3458924434021358</v>
+        <v>0.3447395504142379</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3386529365021671</v>
+        <v>0.342677053030604</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.318101316496235</v>
+        <v>0.3397095735660258</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2895605426707437</v>
+        <v>0.3091576072261826</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2640669088832996</v>
+        <v>0.2561153998432313</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2557254030453187</v>
+        <v>0.2509907101293358</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2376197539154727</v>
+        <v>0.2406149919425187</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,225 +442,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.06644251966728598</v>
+        <v>0.08793414183900827</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>INDO.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05678903704035099</v>
+        <v>0.08019122203828677</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05387268794604894</v>
+        <v>0.0644404572399071</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04441848052431019</v>
+        <v>0.0469616130550552</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04302265318459764</v>
+        <v>0.043858580404458</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04277869095595466</v>
+        <v>0.0425161930171678</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>DSP5.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03629047453736334</v>
+        <v>0.04106249548975338</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0304617433042671</v>
+        <v>0.03718892177161393</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02667995778674315</v>
+        <v>0.03700411603121689</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UINC.L</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01979201610197912</v>
+        <v>0.03269750425645368</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>First Trust US Equity Income UCITS ETF Dist</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0193480480962871</v>
+        <v>0.03114423466797089</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.01833584737849847</v>
+        <v>0.03006678013903841</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SEL.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0179802793797077</v>
+        <v>0.02974475568807877</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ISF.L</t>
+          <t>XDWU.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.017554124801475</v>
+        <v>0.02441594250558654</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares Core FTSE 100 UCITS ETF (Dist)</t>
+          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>AIPO.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01732040550629343</v>
+        <v>0.02244550814798507</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Defiance AI &amp; Power Infrastructure UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -698,30 +698,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1129131354879329</v>
+        <v>0.1270832870945786</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09933774834437092</v>
+        <v>0.1152480823177822</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07078142565397361</v>
+        <v>0.07557170927506784</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06591210306857564</v>
+        <v>0.0700467127063189</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -758,165 +758,165 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.06266831341070933</v>
+        <v>0.06594705405295942</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.06162090137232012</v>
+        <v>0.06102006770963508</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CD9.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0546038543897216</v>
+        <v>0.05465805215347008</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VMIG.MI</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04531066232774417</v>
+        <v>0.05375941581990307</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.04491576301416189</v>
+        <v>0.05206399480803459</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UTI.PA</t>
+          <t>VMIG.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.04385798932210472</v>
+        <v>0.04424422523957938</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Utilities UCITS ETF Acc</t>
+          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STU.PA</t>
+          <t>DSP5.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04313503743618963</v>
+        <v>0.04349208077025568</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Utilities UCITS ETF EUR</t>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DSP5.PA</t>
+          <t>CD9.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04169408384799356</v>
+        <v>0.04143646355098141</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EPRU.AS</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.04165630474196558</v>
+        <v>0.04110595422269814</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi FTSE EPRA NAREIT Global UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INDO.PA</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.04152053649122545</v>
+        <v>0.03971658225414032</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04105462972868112</v>
+        <v>0.03616403302398408</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2784987082843629</v>
+        <v>0.3147540448590409</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -969,30 +969,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2483414250129405</v>
+        <v>0.2082280331600748</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2347946453713687</v>
+        <v>0.1700635139137798</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.184291958203781</v>
+        <v>0.1667852629776787</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1731166610874437</v>
+        <v>0.1582778750980491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1687359150949996</v>
+        <v>0.1257697641215871</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1044,135 +1044,135 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1580083522875726</v>
+        <v>0.1256533157318651</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1421907176534891</v>
+        <v>0.1254665265917716</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1358221441690233</v>
+        <v>0.1231414295087196</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.135804319779075</v>
+        <v>0.1208925329322648</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1318753681071301</v>
+        <v>0.1186358358804629</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1280699580460354</v>
+        <v>0.1184546414579999</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MIB.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1274244111185496</v>
+        <v>0.1089951622666459</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1254594158194677</v>
+        <v>0.1073579305705012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1207011406112766</v>
+        <v>0.1041770144555152</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1210,45 +1210,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5130371959389286</v>
+        <v>0.5075371876568477</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5007052773350988</v>
+        <v>0.5071261132164704</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4307075965416352</v>
+        <v>0.3797820367006259</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3864192774181514</v>
+        <v>0.3445012414534412</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1270,15 +1270,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3264840182648401</v>
+        <v>0.3199010725004656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3007646139577294</v>
+        <v>0.3011676011396549</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2545704967257927</v>
+        <v>0.2875746360692082</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1315,30 +1315,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2516017227241552</v>
+        <v>0.2691675119974204</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2490735296497484</v>
+        <v>0.2251994345052253</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2455894093360507</v>
+        <v>0.1946535016050432</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1360,45 +1360,45 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2451029411002874</v>
+        <v>0.1844790116576804</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2307339990345461</v>
+        <v>0.178672996512061</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MIB.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2174305339356439</v>
+        <v>0.1757376121511081</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.208013045185631</v>
+        <v>0.1746547365965538</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1420,15 +1420,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>MIB.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2015310142402953</v>
+        <v>0.1680372810968827</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.552171900208311</v>
+        <v>1.512141140064982</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.528848117233958</v>
+        <v>1.501203388307649</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1496,30 +1496,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8458703776192493</v>
+        <v>0.7902264054923065</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.833674194431244</v>
+        <v>0.77770418409172</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7631881400748834</v>
+        <v>0.6255524009238187</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6161154180814905</v>
+        <v>0.6148743360908195</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1556,135 +1556,135 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5823545033861168</v>
+        <v>0.5277188428730002</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5742379689455686</v>
+        <v>0.5268534009500876</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5636839980732691</v>
+        <v>0.5221825995509246</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5633256411086578</v>
+        <v>0.5201778198060585</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5629755948562558</v>
+        <v>0.5127448849966143</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5510823685040953</v>
+        <v>0.5059947208637268</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5159608431680196</v>
+        <v>0.4985394412344495</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5137013081223922</v>
+        <v>0.4932376479204539</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XMK9.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4840380328104412</v>
+        <v>0.4813248502894989</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI Japan UCITS ETF 4C - EUR Hedged</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.562443998384168</v>
+        <v>2.339715783831541</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.200998761707691</v>
+        <v>2.103602960703321</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.716691097036295</v>
+        <v>1.63408483410367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.684620278860309</v>
+        <v>1.618658412433005</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.523615953644208</v>
+        <v>1.49811659802766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.307602898393524</v>
+        <v>1.251157406257626</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.285871978312085</v>
+        <v>1.198615184288174</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.2324669848138</v>
+        <v>1.185707328706738</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1842,30 +1842,30 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.139002211132207</v>
+        <v>1.080583718510488</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.124617536250228</v>
+        <v>1.058304582875214</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.11124064039539</v>
+        <v>1.057223393833366</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.096594822892798</v>
+        <v>1.028195633738119</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.060017156140831</v>
+        <v>1.028059814789687</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1917,30 +1917,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>EJAH.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.009365524103332</v>
+        <v>0.9727493355145007</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EJAH.PA</t>
+          <t>XMK9.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9905766250434573</v>
+        <v>0.9608553078407402</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
+          <t>Xtrackers MSCI Japan UCITS ETF 4C - EUR Hedged</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.807615839440728</v>
+        <v>0.7947258138485125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.793661897191309</v>
+        <v>0.7914991003684206</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4687414571559938</v>
+        <v>0.4351623849824027</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4037285633141789</v>
+        <v>0.4135085047226696</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2038,105 +2038,105 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4017879344735997</v>
+        <v>0.3966204343150501</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3830040010866183</v>
+        <v>0.395198465498608</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3673036395003275</v>
+        <v>0.3855955320959148</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3635296683353095</v>
+        <v>0.366277072290744</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3447395504142379</v>
+        <v>0.3258008140736277</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.342677053030604</v>
+        <v>0.3250948646403087</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3397095735660258</v>
+        <v>0.3208038793132746</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3091576072261826</v>
+        <v>0.3203296401566624</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2561153998432313</v>
+        <v>0.2433047008119602</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2509907101293358</v>
+        <v>0.2358087998555083</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,15 +2188,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2406149919425187</v>
+        <v>0.2294587788414224</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,120 +442,120 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.08793414183900827</v>
+        <v>0.0775965311604081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08019122203828677</v>
+        <v>0.06908496505073036</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0644404572399071</v>
+        <v>0.04659733956615253</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0469616130550552</v>
+        <v>0.04644548740956234</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.043858580404458</v>
+        <v>0.0461099569450607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0425161930171678</v>
+        <v>0.03763837515013324</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DSP5.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04106249548975338</v>
+        <v>0.03696159590233128</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>AIPO.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03718892177161393</v>
+        <v>0.03471663676444869</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>Defiance AI &amp; Power Infrastructure UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.03700411603121689</v>
+        <v>0.03392653316056582</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -577,90 +577,90 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03269750425645368</v>
+        <v>0.03148119059387988</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>JPNH.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03114423466797089</v>
+        <v>0.02985068879847619</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi Japan TOPIX II UCITS ETF EUR Hedged Dist</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>LAFRI.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03006678013903841</v>
+        <v>0.02796288628939791</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi Pan Africa UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02974475568807877</v>
+        <v>0.02736015694557858</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>XDWU.MI</t>
+          <t>LJPN.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02441594250558654</v>
+        <v>0.02721184590009851</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
+          <t>Amundi Core MSCI Japan UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AIPO.MI</t>
+          <t>LCJP.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02244550814798507</v>
+        <v>0.02697737414692813</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Defiance AI &amp; Power Infrastructure UCITS ETF Acc</t>
+          <t>Amundi Core MSCI Japan UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1270832870945786</v>
+        <v>0.1409708263804612</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1152480823177822</v>
+        <v>0.1248439469665965</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07557170927506784</v>
+        <v>0.09944520955022984</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -743,15 +743,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0700467127063189</v>
+        <v>0.08097983035600409</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.06594705405295942</v>
+        <v>0.07741159349607374</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -773,15 +773,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.06102006770963508</v>
+        <v>0.06861958230206522</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.05465805215347008</v>
+        <v>0.05745850752817838</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -803,75 +803,75 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05375941581990307</v>
+        <v>0.0571196337180544</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.05206399480803459</v>
+        <v>0.05331200939728298</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VMIG.MI</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.04424422523957938</v>
+        <v>0.05216380554169975</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DSP5.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04349208077025568</v>
+        <v>0.04924578759160436</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CD9.PA</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04143646355098141</v>
+        <v>0.04826838756299723</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.04110595422269814</v>
+        <v>0.04777145032138885</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -893,30 +893,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>INDO.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.03971658225414032</v>
+        <v>0.04613376310890582</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>JPXH.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.03616403302398408</v>
+        <v>0.04569809443820838</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - EUR Hedged (C)</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3147540448590409</v>
+        <v>0.3079627366803652</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -969,210 +969,210 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2082280331600748</v>
+        <v>0.2045706963197946</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1700635139137798</v>
+        <v>0.2013950443249024</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1667852629776787</v>
+        <v>0.1900523651713457</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1582778750980491</v>
+        <v>0.172290184690624</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1257697641215871</v>
+        <v>0.1524871016783216</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1256533157318651</v>
+        <v>0.1520408241570215</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1254665265917716</v>
+        <v>0.1512793877118337</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1231414295087196</v>
+        <v>0.1441643572491467</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1208925329322648</v>
+        <v>0.1419268269605629</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1186358358804629</v>
+        <v>0.1312285471638421</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>SRIJC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1184546414579999</v>
+        <v>0.1249473419227474</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>CS1.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1089951622666459</v>
+        <v>0.1208061560961828</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi IBEX 35 UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>AJASE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1073579305705012</v>
+        <v>0.1100339088366027</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>BNP Paribas Easy ESG Enhanced Japan UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1041770144555152</v>
+        <v>0.109565182008605</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -1210,105 +1210,105 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5075371876568477</v>
+        <v>0.4624378204935853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5071261132164704</v>
+        <v>0.4611874006025558</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3797820367006259</v>
+        <v>0.3558940977564742</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3445012414534412</v>
+        <v>0.3443147274785896</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3199010725004656</v>
+        <v>0.3371691664086669</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3011676011396549</v>
+        <v>0.2588232385195848</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2875746360692082</v>
+        <v>0.2581144192665961</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2691675119974204</v>
+        <v>0.2502831051764178</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1330,105 +1330,105 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2251994345052253</v>
+        <v>0.2197889909643391</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1946535016050432</v>
+        <v>0.2197398770104966</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>MIB.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1844790116576804</v>
+        <v>0.1868352677701346</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.178672996512061</v>
+        <v>0.1847133934343506</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1757376121511081</v>
+        <v>0.1797684572623017</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1746547365965538</v>
+        <v>0.176441802344367</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MIB.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1680372810968827</v>
+        <v>0.1741455703152719</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.512141140064982</v>
+        <v>1.449019697128591</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.501203388307649</v>
+        <v>1.434552162916777</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1496,30 +1496,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7902264054923065</v>
+        <v>0.8208101637023839</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.77770418409172</v>
+        <v>0.7603097475114735</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6255524009238187</v>
+        <v>0.6574535692124794</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1541,30 +1541,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6148743360908195</v>
+        <v>0.5543168647169545</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5277188428730002</v>
+        <v>0.5531656295851635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5268534009500876</v>
+        <v>0.5247579182901894</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1586,105 +1586,105 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5221825995509246</v>
+        <v>0.5221942878301344</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5201778198060585</v>
+        <v>0.5200095676878962</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5127448849966143</v>
+        <v>0.5089962618310977</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5059947208637268</v>
+        <v>0.4997848822927273</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4985394412344495</v>
+        <v>0.4913827132715642</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4932376479204539</v>
+        <v>0.4904626373306531</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4813248502894989</v>
+        <v>0.4725835392848345</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.339715783831541</v>
+        <v>2.389164450275177</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.103602960703321</v>
+        <v>2.152331131792349</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.63408483410367</v>
+        <v>1.548463139439693</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.618658412433005</v>
+        <v>1.529437736519125</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.49811659802766</v>
+        <v>1.444548176405166</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.251157406257626</v>
+        <v>1.27195627787753</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.198615184288174</v>
+        <v>1.214578838711208</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.185707328706738</v>
+        <v>1.191222572263077</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.080583718510488</v>
+        <v>1.119930346894108</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1857,90 +1857,90 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.058304582875214</v>
+        <v>1.067905605751668</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>MIB.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.057223393833366</v>
+        <v>1.042428564436669</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MIB.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.028195633738119</v>
+        <v>1.020666334092876</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>EJAH.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.028059814789687</v>
+        <v>0.9926699288631113</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EJAH.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9727493355145007</v>
+        <v>0.9860652342597578</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XMK9.MI</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9608553078407402</v>
+        <v>0.984786567122335</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI Japan UCITS ETF 4C - EUR Hedged</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7947258138485125</v>
+        <v>0.7454213799078655</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7914991003684206</v>
+        <v>0.739424553119516</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4351623849824027</v>
+        <v>0.4275184108865187</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2023,15 +2023,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4135085047226696</v>
+        <v>0.3829169220233632</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3966204343150501</v>
+        <v>0.3790189325723397</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2053,45 +2053,45 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.395198465498608</v>
+        <v>0.3687566931182076</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3855955320959148</v>
+        <v>0.3682762465618761</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.366277072290744</v>
+        <v>0.3657272649946008</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3258008140736277</v>
+        <v>0.3481499949936244</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3250948646403087</v>
+        <v>0.3163639358853123</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3208038793132746</v>
+        <v>0.3144366904030862</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3203296401566624</v>
+        <v>0.305128280727073</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2158,45 +2158,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AASI.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2433047008119602</v>
+        <v>0.2326370217294922</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AJEUAS.MI</t>
+          <t>AASI.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2358087998555083</v>
+        <v>0.230935677387734</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>AJEUAS.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2294587788414224</v>
+        <v>0.2300962754136466</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,225 +442,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0775965311604081</v>
+        <v>0.04469937862083118</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.06908496505073036</v>
+        <v>0.04315268229968439</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04659733956615253</v>
+        <v>0.03817226974220977</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>DSP5.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04644548740956234</v>
+        <v>0.03620707327748951</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0461099569450607</v>
+        <v>0.03570124047504231</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03763837515013324</v>
+        <v>0.03328435399902263</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>ESIH.L</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03696159590233128</v>
+        <v>0.03025856778508151</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AIPO.MI</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03471663676444869</v>
+        <v>0.02925381051909737</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Defiance AI &amp; Power Infrastructure UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>CS1.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.03392653316056582</v>
+        <v>0.0291926709153294</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>Amundi IBEX 35 UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>XASX.L</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03148119059387988</v>
+        <v>0.02658735002790169</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Xtrackers MSCI UK ESG UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>JPNH.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02985068879847619</v>
+        <v>0.02543655094698249</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Japan TOPIX II UCITS ETF EUR Hedged Dist</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LAFRI.MI</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02796288628939791</v>
+        <v>0.02464379513152415</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Pan Africa UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>HLT.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02736015694557858</v>
+        <v>0.02435512038049259</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LJPN.AS</t>
+          <t>ISF.L</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02721184590009851</v>
+        <v>0.02418561163189348</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Core MSCI Japan UCITS ETF Dist</t>
+          <t>iShares Core FTSE 100 UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LCJP.AS</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02697737414692813</v>
+        <v>0.02348832854563887</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Core MSCI Japan UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1409708263804612</v>
+        <v>0.1377813214954529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1248439469665965</v>
+        <v>0.09727603679483354</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09944520955022984</v>
+        <v>0.07691221326535325</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -743,180 +743,180 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08097983035600409</v>
+        <v>0.06352217086567435</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.07741159349607374</v>
+        <v>0.06344028865434637</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.06861958230206522</v>
+        <v>0.06269966603118848</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.05745850752817838</v>
+        <v>0.06072018400668844</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0571196337180544</v>
+        <v>0.05702911585336556</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.05331200939728298</v>
+        <v>0.05644388014754198</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.05216380554169975</v>
+        <v>0.0557665902354727</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>JPXY.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04924578759160436</v>
+        <v>0.05475287906265791</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR (C)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>DSP5.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04826838756299723</v>
+        <v>0.05314210239730821</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>JPXX.L</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.04777145032138885</v>
+        <v>0.05258987818163807</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INDO.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.04613376310890582</v>
+        <v>0.0525459712724281</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JPXH.PA</t>
+          <t>HMXJ.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04569809443820838</v>
+        <v>0.05035479729540682</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - EUR Hedged (C)</t>
+          <t>HSBC MSCI Pacific ex Japan UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3079627366803652</v>
+        <v>0.2836158942590175</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2045706963197946</v>
+        <v>0.2169183006032203</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2013950443249024</v>
+        <v>0.2094035837591131</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1900523651713457</v>
+        <v>0.1968972867245098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,165 +1014,165 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.172290184690624</v>
+        <v>0.1630167541760128</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1524871016783216</v>
+        <v>0.1621778860635659</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1520408241570215</v>
+        <v>0.1592212975794065</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1512793877118337</v>
+        <v>0.1486999444947055</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1441643572491467</v>
+        <v>0.1438066599207701</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1419268269605629</v>
+        <v>0.1383478910817255</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1312285471638421</v>
+        <v>0.1366530007857905</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SRIJC.PA</t>
+          <t>CS1.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1249473419227474</v>
+        <v>0.1310985693100468</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
+          <t>Amundi IBEX 35 UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CS1.PA</t>
+          <t>MIB.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1208061560961828</v>
+        <v>0.1146650092051953</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi IBEX 35 UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AJASE.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1100339088366027</v>
+        <v>0.1120470432355816</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy ESG Enhanced Japan UCITS ETF EUR Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>JPXX.L</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.109565182008605</v>
+        <v>0.104896558893856</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
         </is>
       </c>
     </row>
@@ -1210,30 +1210,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4624378204935853</v>
+        <v>0.3941511543076932</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4611874006025558</v>
+        <v>0.3936651857624069</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3558940977564742</v>
+        <v>0.3614009850560698</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3443147274785896</v>
+        <v>0.3138819429575213</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3371691664086669</v>
+        <v>0.3033448815964384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1285,30 +1285,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2588232385195848</v>
+        <v>0.2798145453828393</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2581144192665961</v>
+        <v>0.259786314115986</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2502831051764178</v>
+        <v>0.2437428870294518</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2197889909643391</v>
+        <v>0.2209933999523335</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1345,60 +1345,60 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2197398770104966</v>
+        <v>0.2068765867707303</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MIB.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1868352677701346</v>
+        <v>0.1959869076791059</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>MIB.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1847133934343506</v>
+        <v>0.1884542003798797</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>UINC.L</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1797684572623017</v>
+        <v>0.1831568497220699</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>First Trust US Equity Income UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.176441802344367</v>
+        <v>0.1749427573862141</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1420,15 +1420,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>AVSG.L</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1741455703152719</v>
+        <v>0.1670994640108923</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Avantis Global Small Cap Value UCITS ETF USD Acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.449019697128591</v>
+        <v>1.336941902543255</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.434552162916777</v>
+        <v>1.336298233661663</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8208101637023839</v>
+        <v>0.8034406217768211</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7603097475114735</v>
+        <v>0.7135636351044385</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6574535692124794</v>
+        <v>0.6640819628044472</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1541,120 +1541,120 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5543168647169545</v>
+        <v>0.5931107326133278</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5531656295851635</v>
+        <v>0.5355309498799008</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5247579182901894</v>
+        <v>0.5280019078149862</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5221942878301344</v>
+        <v>0.5230348074869826</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5200095676878962</v>
+        <v>0.5128073445875212</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5089962618310977</v>
+        <v>0.5115842418624159</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4997848822927273</v>
+        <v>0.4990641750006879</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4913827132715642</v>
+        <v>0.4714877885607953</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4904626373306531</v>
+        <v>0.4648775244496222</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1676,15 +1676,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4725835392848345</v>
+        <v>0.4621453446810593</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.389164450275177</v>
+        <v>2.28292111877544</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.152331131792349</v>
+        <v>2.159202468526043</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.548463139439693</v>
+        <v>1.42303122284752</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.529437736519125</v>
+        <v>1.414027837753606</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.444548176405166</v>
+        <v>1.367906910504482</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.27195627787753</v>
+        <v>1.275980045463142</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1812,30 +1812,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.214578838711208</v>
+        <v>1.166546995261889</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.191222572263077</v>
+        <v>1.164192098176926</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.119930346894108</v>
+        <v>1.157631302887805</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.067905605751668</v>
+        <v>1.06971214105624</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.042428564436669</v>
+        <v>1.015526055588505</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.020666334092876</v>
+        <v>0.9674316003337864</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9926699288631113</v>
+        <v>0.944136649191277</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1917,30 +1917,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>JPHE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9860652342597578</v>
+        <v>0.9410102380302339</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi JPX Nikkei 400 UCITS ETF Daily Hedged EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.984786567122335</v>
+        <v>0.9406157365906858</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1978,105 +1978,105 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7454213799078655</v>
+        <v>0.6625604117678792</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.739424553119516</v>
+        <v>0.660347014312562</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4275184108865187</v>
+        <v>0.3922676835461574</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3829169220233632</v>
+        <v>0.3882063581410147</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3790189325723397</v>
+        <v>0.3610628445553983</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3687566931182076</v>
+        <v>0.3592029992753758</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3682762465618761</v>
+        <v>0.3527341378963356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3657272649946008</v>
+        <v>0.3493144068981724</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2098,15 +2098,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3481499949936244</v>
+        <v>0.3466171249235674</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3163639358853123</v>
+        <v>0.2910104624598373</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2128,75 +2128,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3144366904030862</v>
+        <v>0.2893773533573738</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.305128280727073</v>
+        <v>0.2876852225419604</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2326370217294922</v>
+        <v>0.2346137795746763</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AASI.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.230935677387734</v>
+        <v>0.2281605997871388</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AJEUAS.MI</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2300962754136466</v>
+        <v>0.2189938038143782</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,195 +442,195 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>DSP5.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04469937862083118</v>
+        <v>0.04961707470182053</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>ESIH.L</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04315268229968439</v>
+        <v>0.04418450778105898</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>XASX.L</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03817226974220977</v>
+        <v>0.04415839166924496</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Xtrackers MSCI UK ESG UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DSP5.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03620707327748951</v>
+        <v>0.04206996053041356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>UINC.L</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03570124047504231</v>
+        <v>0.04159788709144929</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>First Trust US Equity Income UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>XDWS.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03328435399902263</v>
+        <v>0.03887218775317303</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ESIH.L</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03025856778508151</v>
+        <v>0.0383712550694848</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>HLT.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02925381051909737</v>
+        <v>0.03563497853790887</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CS1.PA</t>
+          <t>XDEB.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0291926709153294</v>
+        <v>0.03277939031881427</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi IBEX 35 UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Minimum Volatility UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XASX.L</t>
+          <t>WELE.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02658735002790169</v>
+        <v>0.028459986803969</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI UK ESG UCITS ETF 1D</t>
+          <t>Amundi S&amp;P 500 Equal Weight ESG UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02543655094698249</v>
+        <v>0.02688173788859238</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>HMXJ.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02464379513152415</v>
+        <v>0.02660346936244307</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>HSBC MSCI Pacific ex Japan UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HLT.PA</t>
+          <t>CD9.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02435512038049259</v>
+        <v>0.02601922050941274</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
+          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02418561163189348</v>
+        <v>0.02557646353702125</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -652,15 +652,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>SPEQ.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02348832854563887</v>
+        <v>0.02494111902573537</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Invesco S&amp;P 500 Equal Weight UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1377813214954529</v>
+        <v>0.1210027982076676</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09727603679483354</v>
+        <v>0.08126996031801514</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -728,195 +728,195 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07691221326535325</v>
+        <v>0.0668254019421477</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>HMXJ.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06352217086567435</v>
+        <v>0.06372816638285062</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>HSBC MSCI Pacific ex Japan UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.06344028865434637</v>
+        <v>0.06016397632523951</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.06269966603118848</v>
+        <v>0.05991499465787031</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06072018400668844</v>
+        <v>0.05804047458651018</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05702911585336556</v>
+        <v>0.05665883561942198</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>XASX.L</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.05644388014754198</v>
+        <v>0.05629001381971865</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Xtrackers MSCI UK ESG UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0557665902354727</v>
+        <v>0.05622116453738002</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>JPXY.AS</t>
+          <t>DSP5.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05475287906265791</v>
+        <v>0.05503999871288157</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR (C)</t>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DSP5.PA</t>
+          <t>UINC.L</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05314210239730821</v>
+        <v>0.05377421509686031</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>First Trust US Equity Income UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JPXX.L</t>
+          <t>JPXY.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05258987818163807</v>
+        <v>0.05365051553796762</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR (C)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0525459712724281</v>
+        <v>0.05289054470601995</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HMXJ.MI</t>
+          <t>CD9.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05035479729540682</v>
+        <v>0.05254308667800567</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HSBC MSCI Pacific ex Japan UCITS ETF USD</t>
+          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2836158942590175</v>
+        <v>0.2760748964067659</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -969,120 +969,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2169183006032203</v>
+        <v>0.1913082732853175</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2094035837591131</v>
+        <v>0.1883036058362415</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1968972867245098</v>
+        <v>0.1856954863755571</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1630167541760128</v>
+        <v>0.1772744986336316</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1621778860635659</v>
+        <v>0.1735593628204064</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1592212975794065</v>
+        <v>0.15755962647871</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1486999444947055</v>
+        <v>0.1492191895368309</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1438066599207701</v>
+        <v>0.1489642198627772</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1383478910817255</v>
+        <v>0.1447081899750793</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1104,15 +1104,15 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1366530007857905</v>
+        <v>0.143068156195552</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1310985693100468</v>
+        <v>0.126863157591127</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1134,45 +1134,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MIB.PA</t>
+          <t>WELE.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1146650092051953</v>
+        <v>0.1242893567261678</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+          <t>Amundi S&amp;P 500 Equal Weight ESG UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>SPEQ.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1120470432355816</v>
+        <v>0.1197943109950497</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Invesco S&amp;P 500 Equal Weight UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JPXX.L</t>
+          <t>UINC.L</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.104896558893856</v>
+        <v>0.1117822569329168</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
+          <t>First Trust US Equity Income UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1210,15 +1210,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3941511543076932</v>
+        <v>0.3192990723573521</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3936651857624069</v>
+        <v>0.3179985983361209</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1240,15 +1240,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3614009850560698</v>
+        <v>0.3126115493209447</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3138819429575213</v>
+        <v>0.2883394740037721</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3033448815964384</v>
+        <v>0.2571464325422836</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1285,30 +1285,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2798145453828393</v>
+        <v>0.2411842062266734</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.259786314115986</v>
+        <v>0.2357707036961458</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2437428870294518</v>
+        <v>0.2189281440028037</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1330,105 +1330,105 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>UINC.L</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2209933999523335</v>
+        <v>0.204854481446719</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>First Trust US Equity Income UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2068765867707303</v>
+        <v>0.1956943935818143</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1959869076791059</v>
+        <v>0.1849621471699061</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MIB.PA</t>
+          <t>AVSG.L</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1884542003798797</v>
+        <v>0.1702616515775635</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+          <t>Avantis Global Small Cap Value UCITS ETF USD Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>UINC.L</t>
+          <t>MIB.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1831568497220699</v>
+        <v>0.1683211326982743</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>First Trust US Equity Income UCITS ETF Dist</t>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1749427573862141</v>
+        <v>0.1657226615600471</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AVSG.L</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1670994640108923</v>
+        <v>0.1632261731093416</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avantis Global Small Cap Value UCITS ETF USD Acc</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.336941902543255</v>
+        <v>1.247844202689928</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.336298233661663</v>
+        <v>1.233323289180507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8034406217768211</v>
+        <v>0.8039821747690572</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7135636351044385</v>
+        <v>0.6721943303980025</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6640819628044472</v>
+        <v>0.6473514250152641</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1541,150 +1541,150 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5931107326133278</v>
+        <v>0.5421657920006697</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5355309498799008</v>
+        <v>0.5123521212845052</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5280019078149862</v>
+        <v>0.5080866090676357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5230348074869826</v>
+        <v>0.500610039057261</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5128073445875212</v>
+        <v>0.472486931899013</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5115842418624159</v>
+        <v>0.4651011603859356</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4990641750006879</v>
+        <v>0.4641306554057734</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4714877885607953</v>
+        <v>0.4606634174818749</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4648775244496222</v>
+        <v>0.4501744220148478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4621453446810593</v>
+        <v>0.4478151754004678</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.28292111877544</v>
+        <v>2.246983148771388</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.159202468526043</v>
+        <v>2.148576531541307</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.42303122284752</v>
+        <v>1.357819226452204</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1767,30 +1767,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.414027837753606</v>
+        <v>1.339999886446221</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.367906910504482</v>
+        <v>1.333825979851439</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.275980045463142</v>
+        <v>1.266001471934759</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1812,15 +1812,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.166546995261889</v>
+        <v>1.18547414972123</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.164192098176926</v>
+        <v>1.174528221719306</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1842,15 +1842,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.157631302887805</v>
+        <v>1.166068309642777</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.06971214105624</v>
+        <v>1.048695939189324</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.015526055588505</v>
+        <v>1.001917829513031</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9674316003337864</v>
+        <v>0.9578809756082436</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1902,45 +1902,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EJAH.PA</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.944136649191277</v>
+        <v>0.9437115762360133</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>JPHE.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9410102380302339</v>
+        <v>0.9263195716408308</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi JPX Nikkei 400 UCITS ETF Daily Hedged EUR (C)</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9406157365906858</v>
+        <v>0.9247116919394316</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1978,105 +1978,105 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6625604117678792</v>
+        <v>0.6156614392810185</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.660347014312562</v>
+        <v>0.6073247463737073</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3922676835461574</v>
+        <v>0.3626807958689215</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3882063581410147</v>
+        <v>0.3461633590327284</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3610628445553983</v>
+        <v>0.339376167717593</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3592029992753758</v>
+        <v>0.3327857692545968</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3527341378963356</v>
+        <v>0.3253630752703429</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3493144068981724</v>
+        <v>0.3171364189914345</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2098,15 +2098,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3466171249235674</v>
+        <v>0.3155561296773177</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2910104624598373</v>
+        <v>0.271533716113961</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2128,30 +2128,30 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2893773533573738</v>
+        <v>0.2710703834708361</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2876852225419604</v>
+        <v>0.2604395900751355</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2346137795746763</v>
+        <v>0.2505456778174968</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2281605997871388</v>
+        <v>0.2278892450376855</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,15 +2188,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>UINC.L</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2189938038143782</v>
+        <v>0.2202296560956198</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>First Trust US Equity Income UCITS ETF Dist</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04961707470182053</v>
+        <v>0.06859962961089106</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -457,45 +457,45 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ESIH.L</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04418450778105898</v>
+        <v>0.04982700731786216</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>XASX.L</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04415839166924496</v>
+        <v>0.04616446023637755</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI UK ESG UCITS ETF 1D</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>ESIH.L</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04206996053041356</v>
+        <v>0.04501786703029054</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04159788709144929</v>
+        <v>0.04374999999999996</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -517,135 +517,135 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XDWS.MI</t>
+          <t>HLT.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03887218775317303</v>
+        <v>0.03979579709146175</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
+          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>XDWS.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0383712550694848</v>
+        <v>0.03517477516729262</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLT.PA</t>
+          <t>XDEB.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03563497853790887</v>
+        <v>0.03420456972989161</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Minimum Volatility UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>XDEB.MI</t>
+          <t>XASX.L</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.03277939031881427</v>
+        <v>0.03227699453441657</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Minimum Volatility UCITS ETF 1C</t>
+          <t>Xtrackers MSCI UK ESG UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WELE.MI</t>
+          <t>BERMIB.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.028459986803969</v>
+        <v>0.02661923408444933</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P 500 Equal Weight ESG UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02688173788859238</v>
+        <v>0.02443790360041476</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HMXJ.MI</t>
+          <t>WELE.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02660346936244307</v>
+        <v>0.02310807758314359</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HSBC MSCI Pacific ex Japan UCITS ETF USD</t>
+          <t>Amundi S&amp;P 500 Equal Weight ESG UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CD9.PA</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02601922050941274</v>
+        <v>0.02064842137200951</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ISF.L</t>
+          <t>INR.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02557646353702125</v>
+        <v>0.01926134251284628</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares Core FTSE 100 UCITS ETF (Dist)</t>
+          <t>Amundi MSCI India Swap UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02494111902573537</v>
+        <v>0.01894477719438115</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1210027982076676</v>
+        <v>0.15313720703125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08126996031801514</v>
+        <v>0.1101299384448862</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -728,195 +728,195 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0668254019421477</v>
+        <v>0.08522154137793914</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HMXJ.MI</t>
+          <t>DSP5.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06372816638285062</v>
+        <v>0.08212769618451121</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HSBC MSCI Pacific ex Japan UCITS ETF USD</t>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>UINC.L</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.06016397632523951</v>
+        <v>0.06979096426163189</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>First Trust US Equity Income UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05991499465787031</v>
+        <v>0.06753882850144133</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>HMXJ.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.05804047458651018</v>
+        <v>0.06373086610963918</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>HSBC MSCI Pacific ex Japan UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>XASX.L</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05665883561942198</v>
+        <v>0.06348246518554523</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Xtrackers MSCI UK ESG UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>XASX.L</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.05629001381971865</v>
+        <v>0.06279828972016266</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI UK ESG UCITS ETF 1D</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.05622116453738002</v>
+        <v>0.06267532670385889</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DSP5.PA</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05503999871288157</v>
+        <v>0.06162186161142369</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UINC.L</t>
+          <t>BITC.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05377421509686031</v>
+        <v>0.05818295592736145</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>First Trust US Equity Income UCITS ETF Dist</t>
+          <t>CoinShares Physical Bitcoin</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JPXY.AS</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05365051553796762</v>
+        <v>0.05690015418585115</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR (C)</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05289054470601995</v>
+        <v>0.05426208736657934</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CD9.PA</t>
+          <t>SEL.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05254308667800567</v>
+        <v>0.05338234701246214</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
+          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2760748964067659</v>
+        <v>0.3238434526034755</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -969,60 +969,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1913082732853175</v>
+        <v>0.1809149450206049</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1883036058362415</v>
+        <v>0.1806138251229605</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1856954863755571</v>
+        <v>0.1779114630391754</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1772744986336316</v>
+        <v>0.1744649361184958</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1735593628204064</v>
+        <v>0.1658102271601563</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1044,15 +1044,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.15755962647871</v>
+        <v>0.1649046366091869</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1492191895368309</v>
+        <v>0.1459333375441343</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1074,60 +1074,60 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1489642198627772</v>
+        <v>0.1430501707673504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1447081899750793</v>
+        <v>0.143027085189418</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.143068156195552</v>
+        <v>0.1251871746505366</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CS1.PA</t>
+          <t>UINC.L</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.126863157591127</v>
+        <v>0.1232705869073536</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi IBEX 35 UCITS ETF Acc</t>
+          <t>First Trust US Equity Income UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1242893567261678</v>
+        <v>0.1208860630084456</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1197943109950497</v>
+        <v>0.1155296822221181</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1164,15 +1164,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UINC.L</t>
+          <t>JPXX.L</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1117822569329168</v>
+        <v>0.1132870077911139</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>First Trust US Equity Income UCITS ETF Dist</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3192990723573521</v>
+        <v>0.3202469437210649</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1225,210 +1225,210 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3179985983361209</v>
+        <v>0.3153656174403554</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3126115493209447</v>
+        <v>0.2470731525497074</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2883394740037721</v>
+        <v>0.2289518098998438</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2571464325422836</v>
+        <v>0.2239813339499555</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2411842062266734</v>
+        <v>0.2235816383573033</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>UINC.L</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2357707036961458</v>
+        <v>0.213582033177721</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>First Trust US Equity Income UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2189281440028037</v>
+        <v>0.2129306428100493</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UINC.L</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.204854481446719</v>
+        <v>0.2105899594276557</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>First Trust US Equity Income UCITS ETF Dist</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1956943935818143</v>
+        <v>0.2089722898600779</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1849621471699061</v>
+        <v>0.1825310155364703</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AVSG.L</t>
+          <t>MIB.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1702616515775635</v>
+        <v>0.1693503551713906</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avantis Global Small Cap Value UCITS ETF USD Acc</t>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MIB.PA</t>
+          <t>AVSG.L</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1683211326982743</v>
+        <v>0.1692979979875153</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+          <t>Avantis Global Small Cap Value UCITS ETF USD Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1657226615600471</v>
+        <v>0.1568011070600632</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>CD8.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1632261731093416</v>
+        <v>0.153413383516779</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>Amundi MSCI EMU High Dividend UCITS ETF UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1466,30 +1466,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.247844202689928</v>
+        <v>1.090992281089076</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.233323289180507</v>
+        <v>1.090256009999031</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8039821747690572</v>
+        <v>0.7847472512931726</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6721943303980025</v>
+        <v>0.6212880347045808</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6473514250152641</v>
+        <v>0.5884652782027484</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5421657920006697</v>
+        <v>0.5591157164564882</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1556,135 +1556,135 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5123521212845052</v>
+        <v>0.5280059020020749</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5080866090676357</v>
+        <v>0.4845450085861978</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.500610039057261</v>
+        <v>0.4761684526412497</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.472486931899013</v>
+        <v>0.4712820083981477</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4651011603859356</v>
+        <v>0.4702798406700979</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4641306554057734</v>
+        <v>0.4611179517663044</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4606634174818749</v>
+        <v>0.4583396711939449</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4501744220148478</v>
+        <v>0.4420314644386893</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4478151754004678</v>
+        <v>0.4310340363747833</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.246983148771388</v>
+        <v>2.202659949465621</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.148576531541307</v>
+        <v>2.0970809729425</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1752,60 +1752,60 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.357819226452204</v>
+        <v>1.254418661428052</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.339999886446221</v>
+        <v>1.245473996381176</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.333825979851439</v>
+        <v>1.230530375196814</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.266001471934759</v>
+        <v>1.223186013041033</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.18547414972123</v>
+        <v>1.175938885849638</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1827,30 +1827,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.174528221719306</v>
+        <v>1.173486476218435</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.166068309642777</v>
+        <v>1.143163217371856</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.048695939189324</v>
+        <v>1.035881177184186</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.001917829513031</v>
+        <v>0.990199746990702</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1887,60 +1887,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9578809756082436</v>
+        <v>0.9382146546105385</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9437115762360133</v>
+        <v>0.9290258141857677</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>EJAH.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9263195716408308</v>
+        <v>0.9094433746486759</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9247116919394316</v>
+        <v>0.9087242809460141</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1978,105 +1978,105 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6156614392810185</v>
+        <v>0.5311261102596079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6073247463737073</v>
+        <v>0.528438599499039</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3626807958689215</v>
+        <v>0.3801923660218536</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3461633590327284</v>
+        <v>0.3674015768536902</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.339376167717593</v>
+        <v>0.3487424538787147</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3327857692545968</v>
+        <v>0.3277874500345237</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3253630752703429</v>
+        <v>0.3265083440642302</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3171364189914345</v>
+        <v>0.3255588432829135</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3155561296773177</v>
+        <v>0.3137224635295368</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2113,60 +2113,60 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.271533716113961</v>
+        <v>0.2853480268582642</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2710703834708361</v>
+        <v>0.2450895240473923</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2604395900751355</v>
+        <v>0.2356022364254087</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2505456778174968</v>
+        <v>0.2337386544844251</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2278892450376855</v>
+        <v>0.2320944157220997</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2202296560956198</v>
+        <v>0.2271913466850717</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,225 +442,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DSP5.PA</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.06859962961089106</v>
+        <v>0.07192945994282063</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04982700731786216</v>
+        <v>0.05937154012130863</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04616446023637755</v>
+        <v>0.04403428100802631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ESIH.L</t>
+          <t>TRV.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04501786703029054</v>
+        <v>0.04045799370516723</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
+          <t>Amundi STOXX Europe 600 Consumer Discretionary UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UINC.L</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04374999999999996</v>
+        <v>0.0389089111325216</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>First Trust US Equity Income UCITS ETF Dist</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HLT.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03979579709146175</v>
+        <v>0.03790337318779047</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>XDWS.MI</t>
+          <t>XASX.L</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03517477516729262</v>
+        <v>0.03561560423782462</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
+          <t>Xtrackers MSCI UK ESG UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XDEB.MI</t>
+          <t>C50U.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03420456972989161</v>
+        <v>0.03447548879440721</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Minimum Volatility UCITS ETF 1C</t>
+          <t>Amundi Core EURO STOXX 50 UCITS ETF USD Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>XASX.L</t>
+          <t>CG1.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.03227699453441657</v>
+        <v>0.03429747294081364</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI UK ESG UCITS ETF 1D</t>
+          <t>Amundi ETF DAX UCITS ETF DR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BERMIB.MI</t>
+          <t>DAX.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02661923408444933</v>
+        <v>0.0337327596173207</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi DAX II UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>CI2.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02443790360041476</v>
+        <v>0.03068208924166416</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI India Swap II UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WELE.MI</t>
+          <t>JPXH.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02310807758314359</v>
+        <v>0.03017876263142183</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P 500 Equal Weight ESG UCITS ETF Acc</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - EUR Hedged (C)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>INR.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02064842137200951</v>
+        <v>0.02916919713628352</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI India Swap UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INR.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01926134251284628</v>
+        <v>0.02869219176592153</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI India Swap UCITS ETF EUR Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SPEQ.MI</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01894477719438115</v>
+        <v>0.02840615678385539</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Invesco S&amp;P 500 Equal Weight UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.15313720703125</v>
+        <v>0.1465938676763023</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -713,210 +713,210 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>INDO.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1101299384448862</v>
+        <v>0.09264059249580492</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08522154137793914</v>
+        <v>0.08523753979808735</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DSP5.PA</t>
+          <t>BITC.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08212769618451121</v>
+        <v>0.07885513079111872</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>CoinShares Physical Bitcoin</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UINC.L</t>
+          <t>DSP5.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.06979096426163189</v>
+        <v>0.07288719346794226</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>First Trust US Equity Income UCITS ETF Dist</t>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.06753882850144133</v>
+        <v>0.07171825531803555</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HMXJ.MI</t>
+          <t>SEL.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06373086610963918</v>
+        <v>0.06818176751435234</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HSBC MSCI Pacific ex Japan UCITS ETF USD</t>
+          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XASX.L</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.06348246518554523</v>
+        <v>0.06598120245503725</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI UK ESG UCITS ETF 1D</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>HMXJ.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.06279828972016266</v>
+        <v>0.06362885470279989</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>HSBC MSCI Pacific ex Japan UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06267532670385889</v>
+        <v>0.06322178060028194</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06162186161142369</v>
+        <v>0.05995239995680479</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BITC.AS</t>
+          <t>XASX.L</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05818295592736145</v>
+        <v>0.05667397359993021</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CoinShares Physical Bitcoin</t>
+          <t>Xtrackers MSCI UK ESG UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>VMIG.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05690015418585115</v>
+        <v>0.05444064701143914</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05426208736657934</v>
+        <v>0.05440340692477053</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SEL.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05338234701246214</v>
+        <v>0.05415020458135578</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3238434526034755</v>
+        <v>0.3060408373746395</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -969,60 +969,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1809149450206049</v>
+        <v>0.2032893368772473</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1806138251229605</v>
+        <v>0.202612972680158</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1779114630391754</v>
+        <v>0.1920444797175866</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1744649361184958</v>
+        <v>0.1904968268654668</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1658102271601563</v>
+        <v>0.1727876384578966</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1044,135 +1044,135 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1649046366091869</v>
+        <v>0.1542123844268339</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1459333375441343</v>
+        <v>0.1309668444587726</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1430501707673504</v>
+        <v>0.1270866375528152</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>JPXX.L</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.143027085189418</v>
+        <v>0.1265271433124402</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1251871746505366</v>
+        <v>0.1241953116877907</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UINC.L</t>
+          <t>JPXH.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1232705869073536</v>
+        <v>0.1211520158259134</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>First Trust US Equity Income UCITS ETF Dist</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - EUR Hedged (C)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WELE.MI</t>
+          <t>CS1.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1208860630084456</v>
+        <v>0.1195175438596492</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P 500 Equal Weight ESG UCITS ETF Acc</t>
+          <t>Amundi IBEX 35 UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SPEQ.MI</t>
+          <t>JPXY.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1155296822221181</v>
+        <v>0.1191642141906604</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Invesco S&amp;P 500 Equal Weight UCITS ETF Acc</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR (C)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JPXX.L</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1132870077911139</v>
+        <v>0.1130059636847576</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3202469437210649</v>
+        <v>0.356489441210518</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1225,150 +1225,150 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3153656174403554</v>
+        <v>0.3251460188189632</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2470731525497074</v>
+        <v>0.3201561704756302</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2289518098998438</v>
+        <v>0.3030768344811456</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2239813339499555</v>
+        <v>0.291556816579017</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2235816383573033</v>
+        <v>0.2645200411049755</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UINC.L</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.213582033177721</v>
+        <v>0.2119464691499418</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>First Trust US Equity Income UCITS ETF Dist</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2129306428100493</v>
+        <v>0.2033058188216326</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2105899594276557</v>
+        <v>0.1944436945323824</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2089722898600779</v>
+        <v>0.1879687507978689</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1825310155364703</v>
+        <v>0.1872117086386251</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1693503551713906</v>
+        <v>0.1869231346775195</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1390,45 +1390,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AVSG.L</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1692979979875153</v>
+        <v>0.1826412986017907</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avantis Global Small Cap Value UCITS ETF USD Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1568011070600632</v>
+        <v>0.1720941743539581</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CD8.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.153413383516779</v>
+        <v>0.1674086621059085</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI EMU High Dividend UCITS ETF UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1466,30 +1466,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.090992281089076</v>
+        <v>1.199252666078826</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.090256009999031</v>
+        <v>1.197342523060042</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7847472512931726</v>
+        <v>0.8295104519574059</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6212880347045808</v>
+        <v>0.691181226358478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1526,30 +1526,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5884652782027484</v>
+        <v>0.6035650462929905</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5591157164564882</v>
+        <v>0.5981354805886723</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5280059020020749</v>
+        <v>0.5174858356981804</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1571,120 +1571,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4845450085861978</v>
+        <v>0.508468016805885</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4761684526412497</v>
+        <v>0.5015469259559266</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4712820083981477</v>
+        <v>0.4754639637906344</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4702798406700979</v>
+        <v>0.4750652778892799</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4611179517663044</v>
+        <v>0.4738669904955386</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4583396711939449</v>
+        <v>0.4659346306946659</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4420314644386893</v>
+        <v>0.4567582047849701</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4310340363747833</v>
+        <v>0.4548611262961326</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.202659949465621</v>
+        <v>2.26315217541724</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.0970809729425</v>
+        <v>2.170005295847507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1752,60 +1752,60 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.254418661428052</v>
+        <v>1.372089300819692</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.245473996381176</v>
+        <v>1.363033614018655</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.230530375196814</v>
+        <v>1.316312276781028</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.223186013041033</v>
+        <v>1.287634185186082</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.175938885849638</v>
+        <v>1.224502484263345</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.173486476218435</v>
+        <v>1.218225379079816</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.143163217371856</v>
+        <v>1.094695615271011</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.035881177184186</v>
+        <v>1.072170909186204</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.990199746990702</v>
+        <v>1.007923840655183</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1887,45 +1887,45 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9382146546105385</v>
+        <v>0.9949913970904412</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9290258141857677</v>
+        <v>0.9637351167439614</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EJAH.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9094433746486759</v>
+        <v>0.9534989256417323</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9087242809460141</v>
+        <v>0.9136974068664006</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5311261102596079</v>
+        <v>0.6267902985761387</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.528438599499039</v>
+        <v>0.6250066791519002</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2008,105 +2008,105 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3801923660218536</v>
+        <v>0.3873872865297867</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3674015768536902</v>
+        <v>0.3785496737856442</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3487424538787147</v>
+        <v>0.3625527267980537</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3277874500345237</v>
+        <v>0.3400281046111047</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3265083440642302</v>
+        <v>0.3349632847060491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3255588432829135</v>
+        <v>0.3341173305691574</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3137224635295368</v>
+        <v>0.3219979359014637</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2853480268582642</v>
+        <v>0.2849817879640288</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2128,15 +2128,15 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2450895240473923</v>
+        <v>0.2813656142193151</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2356022364254087</v>
+        <v>0.2681755680541547</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2158,15 +2158,15 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2337386544844251</v>
+        <v>0.2656045539928089</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2320944157220997</v>
+        <v>0.2547476732002929</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,15 +2188,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UINC.L</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2271913466850717</v>
+        <v>0.2328859782448727</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>First Trust US Equity Income UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.07192945994282063</v>
+        <v>0.04314871177265545</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -457,45 +457,45 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>LYINR.SW</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05937154012130863</v>
+        <v>0.03188149769529813</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI India Swap UCITS ETF USD Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>MSEC.SW</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04403428100802631</v>
+        <v>0.02738095238095228</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 II UCITS ETF CHF Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TRV.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04045799370516723</v>
+        <v>0.02667142486385266</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Consumer Discretionary UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0389089111325216</v>
+        <v>0.02357872599469157</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -517,30 +517,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>SEL.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03790337318779047</v>
+        <v>0.02309276148216011</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>XASX.L</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03561560423782462</v>
+        <v>0.0229952462036116</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI UK ESG UCITS ETF 1D</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03447548879440721</v>
+        <v>0.02199750469797945</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.03429747294081364</v>
+        <v>0.02154780579858762</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0337327596173207</v>
+        <v>0.02102498023475552</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -592,75 +592,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CI2.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03068208924166416</v>
+        <v>0.02035730839690908</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI India Swap II UCITS ETF EUR Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JPXH.PA</t>
+          <t>INR.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03017876263142183</v>
+        <v>0.019611760844777</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - EUR Hedged (C)</t>
+          <t>Amundi MSCI India Swap UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>INR.PA</t>
+          <t>CEU2.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02916919713628352</v>
+        <v>0.01957165241254311</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI India Swap UCITS ETF EUR Acc</t>
+          <t>Amundi Core MSCI Europe UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>CAC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02869219176592153</v>
+        <v>0.01776619678524449</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi CAC 40 UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02840615678385539</v>
+        <v>0.01770187217637886</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1465938676763023</v>
+        <v>0.1822698878492666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -713,60 +713,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>INDO.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09264059249580492</v>
+        <v>0.1087783958204438</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08523753979808735</v>
+        <v>0.09272971047797607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BITC.AS</t>
+          <t>INDO.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07885513079111872</v>
+        <v>0.08687112536504449</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CoinShares Physical Bitcoin</t>
+          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DSP5.PA</t>
+          <t>SEL.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.07288719346794226</v>
+        <v>0.07170625808923869</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07171825531803555</v>
+        <v>0.06351393867761379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -788,135 +788,135 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SEL.PA</t>
+          <t>DSP5.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06818176751435234</v>
+        <v>0.06312826810751782</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.06598120245503725</v>
+        <v>0.0576603727520637</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HMXJ.MI</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.06362885470279989</v>
+        <v>0.05740528103446185</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>HSBC MSCI Pacific ex Japan UCITS ETF USD</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06322178060028194</v>
+        <v>0.05594848253555607</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>HMXJ.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05995239995680479</v>
+        <v>0.05536525778939683</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>HSBC MSCI Pacific ex Japan UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>XASX.L</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05667397359993021</v>
+        <v>0.05523298367868001</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI UK ESG UCITS ETF 1D</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VMIG.MI</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05444064701143914</v>
+        <v>0.05351524062664703</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05440340692477053</v>
+        <v>0.05350191580639807</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>CD8.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05415020458135578</v>
+        <v>0.0446601793603989</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI EMU High Dividend UCITS ETF UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3060408373746395</v>
+        <v>0.2978320318753249</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2032893368772473</v>
+        <v>0.2101033683565792</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.202612972680158</v>
+        <v>0.1974284811015947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -999,30 +999,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1920444797175866</v>
+        <v>0.192883474945037</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1904968268654668</v>
+        <v>0.1923680866520845</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1727876384578966</v>
+        <v>0.1756335400958848</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1542123844268339</v>
+        <v>0.1586843630759756</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1309668444587726</v>
+        <v>0.1427617587548986</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1074,105 +1074,105 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1270866375528152</v>
+        <v>0.1318401576304999</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JPXX.L</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1265271433124402</v>
+        <v>0.1262337108428784</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>CS1.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1241953116877907</v>
+        <v>0.1210526583487528</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>Amundi IBEX 35 UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JPXH.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1211520158259134</v>
+        <v>0.1134712196825023</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - EUR Hedged (C)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CS1.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1195175438596492</v>
+        <v>0.1102475632336646</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi IBEX 35 UCITS ETF Acc</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>JPXY.AS</t>
+          <t>JPXX.L</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1191642141906604</v>
+        <v>0.1082788904359002</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR (C)</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1130059636847576</v>
+        <v>0.1067342520579524</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.356489441210518</v>
+        <v>0.3309125566329236</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1225,15 +1225,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3251460188189632</v>
+        <v>0.3134672929278626</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3201561704756302</v>
+        <v>0.3079115096183029</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1255,15 +1255,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3030768344811456</v>
+        <v>0.3055532702911796</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.291556816579017</v>
+        <v>0.3040999338596238</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2645200411049755</v>
+        <v>0.2784573808618938</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,30 +1300,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2119464691499418</v>
+        <v>0.2166896425444504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2033058188216326</v>
+        <v>0.2099615116427436</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1944436945323824</v>
+        <v>0.2089399254903981</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1345,30 +1345,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1879687507978689</v>
+        <v>0.1992356176332397</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1872117086386251</v>
+        <v>0.1854699233951136</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1869231346775195</v>
+        <v>0.1749834862776145</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1390,45 +1390,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1826412986017907</v>
+        <v>0.1698208902034162</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1720941743539581</v>
+        <v>0.167635119115314</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>FEMI.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1674086621059085</v>
+        <v>0.1635533771704403</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.199252666078826</v>
+        <v>1.257182409654312</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.197342523060042</v>
+        <v>1.252240706812685</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8295104519574059</v>
+        <v>0.868416376698508</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.691181226358478</v>
+        <v>0.722576424313097</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6035650462929905</v>
+        <v>0.6566474955767954</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5981354805886723</v>
+        <v>0.6508120406489362</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5174858356981804</v>
+        <v>0.5461384200428483</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1571,45 +1571,45 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.508468016805885</v>
+        <v>0.5245419660208448</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5015469259559266</v>
+        <v>0.5170343537588076</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4754639637906344</v>
+        <v>0.5049019951583886</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4750652778892799</v>
+        <v>0.4909144656550632</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1631,30 +1631,30 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4738669904955386</v>
+        <v>0.4851435400573503</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4659346306946659</v>
+        <v>0.4811492209142376</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4567582047849701</v>
+        <v>0.4745756317790153</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1676,15 +1676,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4548611262961326</v>
+        <v>0.4729722935332479</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.26315217541724</v>
+        <v>2.334396085530692</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.170005295847507</v>
+        <v>2.231943954714517</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.372089300819692</v>
+        <v>1.39549376780578</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.363033614018655</v>
+        <v>1.384607225985109</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.316312276781028</v>
+        <v>1.34014673579985</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.287634185186082</v>
+        <v>1.323737968638585</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.224502484263345</v>
+        <v>1.252807019094232</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.218225379079816</v>
+        <v>1.22830282847666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.094695615271011</v>
+        <v>1.116397559547861</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.072170909186204</v>
+        <v>1.071638332916537</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.007923840655183</v>
+        <v>1.030381095756263</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1887,45 +1887,45 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9949913970904412</v>
+        <v>1.019795309880554</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9637351167439614</v>
+        <v>1.017676524133295</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9534989256417323</v>
+        <v>0.9788383307243835</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9136974068664006</v>
+        <v>0.9535309015254672</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1978,30 +1978,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6267902985761387</v>
+        <v>0.6490681804547855</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6250066791519002</v>
+        <v>0.6480859584487622</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3873872865297867</v>
+        <v>0.4018564234636679</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3785496737856442</v>
+        <v>0.3959164028936193</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3625527267980537</v>
+        <v>0.3652843038802773</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2053,15 +2053,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3400281046111047</v>
+        <v>0.3507431308191968</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3349632847060491</v>
+        <v>0.347952258459254</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2083,75 +2083,75 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3341173305691574</v>
+        <v>0.3336876252056498</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3219979359014637</v>
+        <v>0.3316056803196257</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2849817879640288</v>
+        <v>0.3013064118844526</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2813656142193151</v>
+        <v>0.2893314524800592</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2681755680541547</v>
+        <v>0.2833333636087092</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2656045539928089</v>
+        <v>0.2601485042901817</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2547476732002929</v>
+        <v>0.2537981385602344</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,15 +2188,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>FEMI.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2328859782448727</v>
+        <v>0.238991784079793</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,45 +442,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04314871177265545</v>
+        <v>0.04389779538605265</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LYINR.SW</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03188149769529813</v>
+        <v>0.04354411107242639</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi MSCI India Swap UCITS ETF USD Acc</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MSEC.SW</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02738095238095228</v>
+        <v>0.04122301826734631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 II UCITS ETF CHF Hedged Acc</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02667142486385266</v>
+        <v>0.03959695501926097</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -502,165 +502,165 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>UESG.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02357872599469157</v>
+        <v>0.03908540300112384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI USA ESG Leaders Extra UCITS ETF DR - USD (D)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SEL.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02309276148216011</v>
+        <v>0.0382522147971236</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>XUCM.L</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0229952462036116</v>
+        <v>0.03721414352957053</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Xtrackers MSCI USA Communication Services UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C50U.PA</t>
+          <t>S500H.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02199750469797945</v>
+        <v>0.0367731978804855</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Core EURO STOXX 50 UCITS ETF USD Acc</t>
+          <t>Amundi S&amp;P 500 Screened UCITS ETF Acc EUR Hedged</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CG1.PA</t>
+          <t>LYINR.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02154780579858762</v>
+        <v>0.0363573814030993</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi ETF DAX UCITS ETF DR</t>
+          <t>Amundi MSCI India Swap UCITS ETF USD Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DAX.PA</t>
+          <t>5ESGE.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02102498023475552</v>
+        <v>0.03558331750484278</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi DAX II UCITS ETF Acc</t>
+          <t>UBS S&amp;P 500 Scored &amp; Screened UCITS ETF hEUR acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>U500.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02035730839690908</v>
+        <v>0.03470673524153622</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi S&amp;P 500 Screened UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>INR.PA</t>
+          <t>SPEUS.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.019611760844777</v>
+        <v>0.03464128768305019</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI India Swap UCITS ETF EUR Acc</t>
+          <t>BNP Paribas Easy S&amp;P 500 Scored and Screened UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CEU2.AS</t>
+          <t>SPEUH.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01957165241254311</v>
+        <v>0.03432386752797578</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Core MSCI Europe UCITS ETF Acc</t>
+          <t>BNP Paribas Easy S&amp;P 500 Scored and Screened UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CAC.PA</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01776619678524449</v>
+        <v>0.03318343092783205</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi CAC 40 UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>C50U.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01770187217637886</v>
+        <v>0.03308020801033273</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi Core EURO STOXX 50 UCITS ETF USD Acc</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1822698878492666</v>
+        <v>0.1601799850760504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1087783958204438</v>
+        <v>0.1175475049466284</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09272971047797607</v>
+        <v>0.09014488869618842</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -743,30 +743,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>INDO.PA</t>
+          <t>SEL.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08687112536504449</v>
+        <v>0.06150243214340589</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
+          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SEL.PA</t>
+          <t>INDO.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.07170625808923869</v>
+        <v>0.05427148992609676</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
+          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.06351393867761379</v>
+        <v>0.05228012870426424</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -788,135 +788,135 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DSP5.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06312826810751782</v>
+        <v>0.05120989442712887</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>HMXJ.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0576603727520637</v>
+        <v>0.04796749133648914</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>HSBC MSCI Pacific ex Japan UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.05740528103446185</v>
+        <v>0.04674743068041254</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.05594848253555607</v>
+        <v>0.04337746185204661</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HMXJ.MI</t>
+          <t>UINC.L</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05536525778939683</v>
+        <v>0.04182124789207431</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HSBC MSCI Pacific ex Japan UCITS ETF USD</t>
+          <t>First Trust US Equity Income UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05523298367868001</v>
+        <v>0.03718655554161887</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05351524062664703</v>
+        <v>0.03648224592494986</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05350191580639807</v>
+        <v>0.03554051806445147</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CD8.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0446601793603989</v>
+        <v>0.03400234527306112</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI EMU High Dividend UCITS ETF UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2978320318753249</v>
+        <v>0.3118300835925885</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2101033683565792</v>
+        <v>0.2692973538457579</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -984,30 +984,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1974284811015947</v>
+        <v>0.2636526118808524</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.192883474945037</v>
+        <v>0.251587322007266</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1923680866520845</v>
+        <v>0.2412166247264795</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1029,15 +1029,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1756335400958848</v>
+        <v>0.2249531133314071</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1586843630759756</v>
+        <v>0.1931114902226068</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1059,60 +1059,60 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>CS1.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1427617587548986</v>
+        <v>0.1631620809769687</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi IBEX 35 UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1318401576304999</v>
+        <v>0.1521739532594961</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1262337108428784</v>
+        <v>0.1468957198095839</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CS1.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1210526583487528</v>
+        <v>0.1395833284636727</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi IBEX 35 UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1134712196825023</v>
+        <v>0.1394195507724376</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1134,45 +1134,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1102475632336646</v>
+        <v>0.137293301838842</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>JPXX.L</t>
+          <t>MIB.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1082788904359002</v>
+        <v>0.1355772248380183</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>ETDD.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1067342520579524</v>
+        <v>0.1307364350513687</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>BNP Paribas Easy EURO STOXX 50 UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3309125566329236</v>
+        <v>0.3395017091472183</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3134672929278626</v>
+        <v>0.3312110345933117</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3079115096183029</v>
+        <v>0.3306479964500932</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3055532702911796</v>
+        <v>0.3264481367447718</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1270,165 +1270,165 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3040999338596238</v>
+        <v>0.3252298291792974</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2784573808618938</v>
+        <v>0.3100707336552686</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2166896425444504</v>
+        <v>0.2271018736993335</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2099615116427436</v>
+        <v>0.2171814466102495</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2089399254903981</v>
+        <v>0.1976753305687584</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1992356176332397</v>
+        <v>0.1928460351372714</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1854699233951136</v>
+        <v>0.1918130717034388</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MIB.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1749834862776145</v>
+        <v>0.1854089846636784</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1698208902034162</v>
+        <v>0.1800760693205985</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>MIB.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.167635119115314</v>
+        <v>0.1792248189264816</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FEMI.MI</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1635533771704403</v>
+        <v>0.1786891116174512</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.257182409654312</v>
+        <v>1.333634037625493</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.252240706812685</v>
+        <v>1.322836308980482</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.868416376698508</v>
+        <v>0.9014135273482125</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.722576424313097</v>
+        <v>0.8187195910549068</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1526,60 +1526,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6566474955767954</v>
+        <v>0.785249038540869</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6508120406489362</v>
+        <v>0.7113837530299225</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5461384200428483</v>
+        <v>0.6830644154186285</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5245419660208448</v>
+        <v>0.57431204723981</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5170343537588076</v>
+        <v>0.5653542101669287</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,30 +1601,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5049019951583886</v>
+        <v>0.5532975562561064</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4909144656550632</v>
+        <v>0.5369952929371582</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4851435400573503</v>
+        <v>0.5039042909831404</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1646,45 +1646,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4811492209142376</v>
+        <v>0.4972624287970411</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4745756317790153</v>
+        <v>0.4928774167812096</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4729722935332479</v>
+        <v>0.4894573003125335</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.334396085530692</v>
+        <v>2.603481102032469</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.231943954714517</v>
+        <v>2.284357966527074</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.39549376780578</v>
+        <v>1.49000441874129</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1767,30 +1767,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.384607225985109</v>
+        <v>1.474414711837033</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.34014673579985</v>
+        <v>1.469037450273916</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.323737968638585</v>
+        <v>1.366024563043999</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1812,120 +1812,120 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.252807019094232</v>
+        <v>1.274939329162021</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.22830282847666</v>
+        <v>1.267719328213014</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.116397559547861</v>
+        <v>1.255943598009028</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.071638332916537</v>
+        <v>1.155819884217489</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MIB.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.030381095756263</v>
+        <v>1.133493573554198</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>MIB.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.019795309880554</v>
+        <v>1.109953299675884</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.017676524133295</v>
+        <v>1.07132313430963</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9788383307243835</v>
+        <v>1.070064583866063</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9535309015254672</v>
+        <v>1.00671267207126</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6490681804547855</v>
+        <v>0.6389709418374536</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6480859584487622</v>
+        <v>0.6344434184096037</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4018564234636679</v>
+        <v>0.4269724499301473</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2023,60 +2023,60 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3959164028936193</v>
+        <v>0.4020362166047036</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3652843038802773</v>
+        <v>0.4009286714196947</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3507431308191968</v>
+        <v>0.3921614731517296</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.347952258459254</v>
+        <v>0.35923564505983</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3336876252056498</v>
+        <v>0.3322706266278845</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2098,15 +2098,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3316056803196257</v>
+        <v>0.3169314958742511</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3013064118844526</v>
+        <v>0.3001502791318944</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2893314524800592</v>
+        <v>0.2856375536643974</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2143,30 +2143,30 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2833333636087092</v>
+        <v>0.2835007258706546</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2601485042901817</v>
+        <v>0.2642857272608754</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2537981385602344</v>
+        <v>0.2613944156807031</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,15 +2188,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FEMI.MI</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.238991784079793</v>
+        <v>0.250627711369932</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,75 +442,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04389779538605265</v>
+        <v>0.1104878957012911</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04354411107242639</v>
+        <v>0.1079433426047707</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04122301826734631</v>
+        <v>0.1033018907410059</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03959695501926097</v>
+        <v>0.09873007435121495</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UESG.MI</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03908540300112384</v>
+        <v>0.08291258332641616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA ESG Leaders Extra UCITS ETF DR - USD (D)</t>
+          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0382522147971236</v>
+        <v>0.07722580690557779</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -532,135 +532,135 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>XUCM.L</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03721414352957053</v>
+        <v>0.07630831958989726</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Communication Services UCITS ETF 1D</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S500H.PA</t>
+          <t>AIPO.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0367731978804855</v>
+        <v>0.07537482253469929</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P 500 Screened UCITS ETF Acc EUR Hedged</t>
+          <t>Defiance AI &amp; Power Infrastructure UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LYINR.SW</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0363573814030993</v>
+        <v>0.07301532931023136</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI India Swap UCITS ETF USD Acc</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5ESGE.MI</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03558331750484278</v>
+        <v>0.07246047746417017</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UBS S&amp;P 500 Scored &amp; Screened UCITS ETF hEUR acc</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>U500.AS</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03470673524153622</v>
+        <v>0.07057595592609345</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P 500 Screened UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SPEUS.PA</t>
+          <t>ARKX.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03464128768305019</v>
+        <v>0.06960535919303257</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy S&amp;P 500 Scored and Screened UCITS ETF Acc</t>
+          <t>ARK Space &amp; Defence Innovation UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SPEUH.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.03432386752797578</v>
+        <v>0.06917543005593063</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy S&amp;P 500 Scored and Screened UCITS ETF EUR Hedged Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>R1GR.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.03318343092783205</v>
+        <v>0.0620610188180315</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>iShares Russell 1000 Growth UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C50U.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.03308020801033273</v>
+        <v>0.06167038845745076</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Core EURO STOXX 50 UCITS ETF USD Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1601799850760504</v>
+        <v>0.131234183890228</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1175475049466284</v>
+        <v>0.09923191773465412</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -728,90 +728,90 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>INDO.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09014488869618842</v>
+        <v>0.07987125564252651</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SEL.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06150243214340589</v>
+        <v>0.07819390990097164</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>INDO.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05427148992609676</v>
+        <v>0.07492749483789241</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>SEL.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05228012870426424</v>
+        <v>0.06533304075686064</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>HMXJ.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.05120989442712887</v>
+        <v>0.06002707763050963</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>HSBC MSCI Pacific ex Japan UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HMXJ.MI</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04796749133648914</v>
+        <v>0.05782217929763633</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HSBC MSCI Pacific ex Japan UCITS ETF USD</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.04674743068041254</v>
+        <v>0.05491170638827647</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.04337746185204661</v>
+        <v>0.0492984178311584</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -848,15 +848,15 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UINC.L</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04182124789207431</v>
+        <v>0.04701963891157823</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>First Trust US Equity Income UCITS ETF Dist</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03718655554161887</v>
+        <v>0.04501529425291473</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -878,45 +878,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.03648224592494986</v>
+        <v>0.04398421813240372</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>UINC.L</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.03554051806445147</v>
+        <v>0.0431703204047218</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>First Trust US Equity Income UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.03400234527306112</v>
+        <v>0.04124078512577278</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3118300835925885</v>
+        <v>0.3656205256250176</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2692973538457579</v>
+        <v>0.2527796443215919</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2636526118808524</v>
+        <v>0.2421774383629209</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -999,30 +999,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.251587322007266</v>
+        <v>0.240984363009028</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2412166247264795</v>
+        <v>0.2249932061367714</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2249531133314071</v>
+        <v>0.2057142606907618</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1931114902226068</v>
+        <v>0.1926846885582856</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1059,30 +1059,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CS1.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1631620809769687</v>
+        <v>0.1703969910931331</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi IBEX 35 UCITS ETF Acc</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1521739532594961</v>
+        <v>0.1561877688181426</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1468957198095839</v>
+        <v>0.1557089072151243</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1104,75 +1104,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>CS1.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1395833284636727</v>
+        <v>0.1447513812154697</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi IBEX 35 UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1394195507724376</v>
+        <v>0.1423090108624425</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.137293301838842</v>
+        <v>0.1327272973879419</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MIB.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1355772248380183</v>
+        <v>0.1307276421324155</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ETDD.PA</t>
+          <t>MIB.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1307364350513687</v>
+        <v>0.1247309440095334</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy EURO STOXX 50 UCITS ETF</t>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1210,60 +1210,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3395017091472183</v>
+        <v>0.4397403528718913</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3312110345933117</v>
+        <v>0.3901835731640844</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3306479964500932</v>
+        <v>0.3892064204664796</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3264481367447718</v>
+        <v>0.3532569835765844</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3252298291792974</v>
+        <v>0.3427345192379376</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1285,150 +1285,150 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3100707336552686</v>
+        <v>0.2808109547202629</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2271018736993335</v>
+        <v>0.2674685797647016</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2171814466102495</v>
+        <v>0.2661997370197071</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1976753305687584</v>
+        <v>0.2342123111505541</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1928460351372714</v>
+        <v>0.2051337426021262</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1918130717034388</v>
+        <v>0.2012947536833709</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>FEMI.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1854089846636784</v>
+        <v>0.1989020394990848</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>MIB.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1800760693205985</v>
+        <v>0.1852252101111771</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MIB.PA</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1792248189264816</v>
+        <v>0.1832727049691827</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1786891116174512</v>
+        <v>0.1790620177931723</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.333634037625493</v>
+        <v>1.480673476497517</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.322836308980482</v>
+        <v>1.470652023212977</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9014135273482125</v>
+        <v>0.9762403813684166</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8187195910549068</v>
+        <v>0.8969884844313154</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.785249038540869</v>
+        <v>0.7686949409686745</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1541,150 +1541,150 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7113837530299225</v>
+        <v>0.7440597575211509</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6830644154186285</v>
+        <v>0.7060503898369672</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.57431204723981</v>
+        <v>0.5955577024006391</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5653542101669287</v>
+        <v>0.5870283308440405</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5532975562561064</v>
+        <v>0.5463821668755175</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5369952929371582</v>
+        <v>0.5424538925373985</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5039042909831404</v>
+        <v>0.5367646613769728</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4972624287970411</v>
+        <v>0.5226447375503711</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4928774167812096</v>
+        <v>0.5200134316352476</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4894573003125335</v>
+        <v>0.4829905264982715</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.603481102032469</v>
+        <v>2.699216520748323</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.284357966527074</v>
+        <v>2.30997484713849</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.49000441874129</v>
+        <v>1.696933488169813</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1767,30 +1767,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.474414711837033</v>
+        <v>1.678895546677013</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.469037450273916</v>
+        <v>1.496206577646392</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.366024563043999</v>
+        <v>1.379451273698084</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.274939329162021</v>
+        <v>1.340220612198887</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1827,30 +1827,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.267719328213014</v>
+        <v>1.311499174130097</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.255943598009028</v>
+        <v>1.278130535314913</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.155819884217489</v>
+        <v>1.192975705056575</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.133493573554198</v>
+        <v>1.173902479732098</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1887,60 +1887,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MIB.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.109953299675884</v>
+        <v>1.145796699407935</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>MIB.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.07132313430963</v>
+        <v>1.138007978526338</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.070064583866063</v>
+        <v>1.109267210397941</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.00671267207126</v>
+        <v>1.093384915551892</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6389709418374536</v>
+        <v>0.7751758133076243</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6344434184096037</v>
+        <v>0.7733644317089192</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4269724499301473</v>
+        <v>0.5132405295170392</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4020362166047036</v>
+        <v>0.4392847883193536</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4009286714196947</v>
+        <v>0.4188533417527713</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2053,150 +2053,150 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3921614731517296</v>
+        <v>0.394712610605231</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.35923564505983</v>
+        <v>0.3574278716943917</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3322706266278845</v>
+        <v>0.3467476855820397</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3169314958742511</v>
+        <v>0.3369590090434431</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3001502791318944</v>
+        <v>0.3334900426394494</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2856375536643974</v>
+        <v>0.3136733859661569</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>FEMI.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2835007258706546</v>
+        <v>0.2931977289345093</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2642857272608754</v>
+        <v>0.2924579110362109</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2613944156807031</v>
+        <v>0.2893933386407748</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.250627711369932</v>
+        <v>0.2741613226883377</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,225 +442,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1104878957012911</v>
+        <v>0.1625553867045315</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1079433426047707</v>
+        <v>0.1573400363902975</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1033018907410059</v>
+        <v>0.1503608065920747</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.09873007435121495</v>
+        <v>0.1430334771270283</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08291258332641616</v>
+        <v>0.1309775251545109</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>AIPO.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07722580690557779</v>
+        <v>0.1206574015309243</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Defiance AI &amp; Power Infrastructure UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.07630831958989726</v>
+        <v>0.1017309360860341</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AIPO.MI</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.07537482253469929</v>
+        <v>0.1004150693299475</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Defiance AI &amp; Power Infrastructure UCITS ETF Acc</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07301532931023136</v>
+        <v>0.09807751035380652</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.07246047746417017</v>
+        <v>0.09712418923116561</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.07057595592609345</v>
+        <v>0.09505228961903711</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ARKX.MI</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06960535919303257</v>
+        <v>0.09276750645934539</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ARK Space &amp; Defence Innovation UCITS ETF USD (Acc)</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>AASU.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06917543005593063</v>
+        <v>0.08769895461357669</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R1GR.AS</t>
+          <t>ARKX.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0620610188180315</v>
+        <v>0.08727887731701234</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares Russell 1000 Growth UCITS ETF USD (Acc)</t>
+          <t>ARK Space &amp; Defence Innovation UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>R1GR.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06167038845745076</v>
+        <v>0.08656087334671247</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares Russell 1000 Growth UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.131234183890228</v>
+        <v>0.1278976802348823</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -713,75 +713,75 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09923191773465412</v>
+        <v>0.09951452351932444</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>INDO.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07987125564252651</v>
+        <v>0.06829815002645034</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07819390990097164</v>
+        <v>0.06828151852319886</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>SEL.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.07492749483789241</v>
+        <v>0.06279166573605521</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SEL.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.06533304075686064</v>
+        <v>0.05978199598305811</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06002707763050963</v>
+        <v>0.05518828891507033</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -803,120 +803,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05782217929763633</v>
+        <v>0.05296488672166344</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>INDO.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.05491170638827647</v>
+        <v>0.05285896806587975</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0492984178311584</v>
+        <v>0.05032022118483992</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>VMIG.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04701963891157823</v>
+        <v>0.04967142658392687</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04501529425291473</v>
+        <v>0.04622562154854215</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>UINC.L</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.04398421813240372</v>
+        <v>0.04405286343612325</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>First Trust US Equity Income UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UINC.L</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0431703204047218</v>
+        <v>0.04081348750257585</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>First Trust US Equity Income UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>SPEUS.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04124078512577278</v>
+        <v>0.04028577403094147</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>BNP Paribas Easy S&amp;P 500 Scored and Screened UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3656205256250176</v>
+        <v>0.3667240856672795</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2527796443215919</v>
+        <v>0.2104487700223259</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -984,60 +984,60 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2421774383629209</v>
+        <v>0.1906810608862846</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.240984363009028</v>
+        <v>0.1838490927994874</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2249932061367714</v>
+        <v>0.1696499969652367</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2057142606907618</v>
+        <v>0.1591055811753483</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1926846885582856</v>
+        <v>0.1542491562246882</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1059,45 +1059,45 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1703969910931331</v>
+        <v>0.1467023811191384</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1561877688181426</v>
+        <v>0.1362485125935862</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1557089072151243</v>
+        <v>0.135206946842573</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1447513812154697</v>
+        <v>0.1194480937304208</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1119,60 +1119,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>DJE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1423090108624425</v>
+        <v>0.1148247050008953</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi Dow Jones Industrial Average UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1327272973879419</v>
+        <v>0.1110890318073692</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1307276421324155</v>
+        <v>0.110673467104661</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MIB.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1247309440095334</v>
+        <v>0.1081878575210629</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4397403528718913</v>
+        <v>0.4956240383965944</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1225,60 +1225,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3901835731640844</v>
+        <v>0.4437185066340474</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3892064204664796</v>
+        <v>0.4142627557362293</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3532569835765844</v>
+        <v>0.4106631042352755</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3427345192379376</v>
+        <v>0.3351826297409366</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2808109547202629</v>
+        <v>0.3051328999020051</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2674685797647016</v>
+        <v>0.2996894812795008</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2661997370197071</v>
+        <v>0.2418756545515186</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2342123111505541</v>
+        <v>0.2415197257641455</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2051337426021262</v>
+        <v>0.2199432373402497</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2012947536833709</v>
+        <v>0.2126569242498173</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1375,60 +1375,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FEMI.MI</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1989020394990848</v>
+        <v>0.206646565072691</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MIB.PA</t>
+          <t>FEMI.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1852252101111771</v>
+        <v>0.2029938810343284</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1832727049691827</v>
+        <v>0.199134582941334</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1790620177931723</v>
+        <v>0.1831299812372749</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.480673476497517</v>
+        <v>1.46619464323778</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.470652023212977</v>
+        <v>1.455317783462296</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9762403813684166</v>
+        <v>1.032792571123795</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8969884844313154</v>
+        <v>0.9017290959237811</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1526,30 +1526,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7686949409686745</v>
+        <v>0.7673579284676419</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7440597575211509</v>
+        <v>0.7595997743649483</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7060503898369672</v>
+        <v>0.7481519390811</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1571,45 +1571,45 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5955577024006391</v>
+        <v>0.586888661847728</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5870283308440405</v>
+        <v>0.5832324925195835</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5463821668755175</v>
+        <v>0.5394736278789412</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5424538925373985</v>
+        <v>0.5381448923787799</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1631,15 +1631,15 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5367646613769728</v>
+        <v>0.5364102671574145</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5226447375503711</v>
+        <v>0.5309699094035556</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5200134316352476</v>
+        <v>0.5114798928943958</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4829905264982715</v>
+        <v>0.5033996253531416</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.699216520748323</v>
+        <v>2.686451749559323</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.30997484713849</v>
+        <v>2.320304315831575</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.696933488169813</v>
+        <v>1.699544641799948</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.678895546677013</v>
+        <v>1.676885075545107</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.496206577646392</v>
+        <v>1.460209875465992</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.379451273698084</v>
+        <v>1.376890994853276</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.340220612198887</v>
+        <v>1.359291537812763</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.311499174130097</v>
+        <v>1.287966879322306</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.278130535314913</v>
+        <v>1.267719328213014</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1857,90 +1857,90 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.192975705056575</v>
+        <v>1.196158799805076</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.173902479732098</v>
+        <v>1.185240907734496</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.145796699407935</v>
+        <v>1.179677736848425</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MIB.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.138007978526338</v>
+        <v>1.169332550483148</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.109267210397941</v>
+        <v>1.166599462105605</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>MIB.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.093384915551892</v>
+        <v>1.134501125090085</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7751758133076243</v>
+        <v>0.7768945270947378</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7733644317089192</v>
+        <v>0.7720335481659892</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5132405295170392</v>
+        <v>0.5162434449537534</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2023,30 +2023,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4392847883193536</v>
+        <v>0.4555663544595732</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4188533417527713</v>
+        <v>0.4343182931451302</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.394712610605231</v>
+        <v>0.3982273316986409</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3574278716943917</v>
+        <v>0.3555418123401739</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3467476855820397</v>
+        <v>0.3510083383846798</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2098,75 +2098,75 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3369590090434431</v>
+        <v>0.3358406822311886</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3334900426394494</v>
+        <v>0.3089662456918001</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>FEMI.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3136733859661569</v>
+        <v>0.3056483483051464</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FEMI.MI</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2931977289345093</v>
+        <v>0.2957846445933119</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2924579110362109</v>
+        <v>0.2845447180308118</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2893933386407748</v>
+        <v>0.2835007258706546</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,15 +2188,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2741613226883377</v>
+        <v>0.2792999999586034</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,120 +442,120 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1625553867045315</v>
+        <v>0.1063141539445875</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>ARKX.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1573400363902975</v>
+        <v>0.103634108284405</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>ARK Space &amp; Defence Innovation UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1503608065920747</v>
+        <v>0.09749257172633974</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1430334771270283</v>
+        <v>0.08939494065079234</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1309775251545109</v>
+        <v>0.08643253772169479</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AIPO.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1206574015309243</v>
+        <v>0.08520269708566341</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Defiance AI &amp; Power Infrastructure UCITS ETF Acc</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>AIPO.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1017309360860341</v>
+        <v>0.08238555610653808</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
+          <t>Defiance AI &amp; Power Infrastructure UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>FEMI.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1004150693299475</v>
+        <v>0.07788469339621384</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09807751035380652</v>
+        <v>0.07767927156187726</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -577,90 +577,90 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.09712418923116561</v>
+        <v>0.07141478360359454</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.09505228961903711</v>
+        <v>0.07099421985607446</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>R1GR.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.09276750645934539</v>
+        <v>0.0660442091569089</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>iShares Russell 1000 Growth UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AASU.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08769895461357669</v>
+        <v>0.06504398332737726</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF USD</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ARKX.MI</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.08727887731701234</v>
+        <v>0.06269368522635932</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ARK Space &amp; Defence Innovation UCITS ETF USD (Acc)</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R1GR.AS</t>
+          <t>LAFRI.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.08656087334671247</v>
+        <v>0.06242003841546051</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares Russell 1000 Growth UCITS ETF USD (Acc)</t>
+          <t>Amundi Pan Africa UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -698,60 +698,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1278976802348823</v>
+        <v>0.1452841744662738</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09951452351932444</v>
+        <v>0.1021659699939153</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.06829815002645034</v>
+        <v>0.08637559921323734</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06828151852319886</v>
+        <v>0.07626641655105337</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.06279166573605521</v>
+        <v>0.0689874752259263</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -773,75 +773,75 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05978199598305811</v>
+        <v>0.06711870544093634</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HMXJ.MI</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.05518828891507033</v>
+        <v>0.05969561699198866</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HSBC MSCI Pacific ex Japan UCITS ETF USD</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05296488672166344</v>
+        <v>0.05968015829109019</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>INDO.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.05285896806587975</v>
+        <v>0.05560070610200119</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.05032022118483992</v>
+        <v>0.05521990173228097</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04967142658392687</v>
+        <v>0.05313169855887745</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -863,60 +863,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04622562154854215</v>
+        <v>0.05032605954989111</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>UINC.L</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.04405286343612325</v>
+        <v>0.04844170110924462</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>First Trust US Equity Income UCITS ETF Dist</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.04081348750257585</v>
+        <v>0.0470461988003259</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SPEUS.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04028577403094147</v>
+        <v>0.04584741766517708</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy S&amp;P 500 Scored and Screened UCITS ETF Acc</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3667240856672795</v>
+        <v>0.3547406753505902</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2104487700223259</v>
+        <v>0.2175781971330408</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -984,195 +984,195 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1906810608862846</v>
+        <v>0.2122661792736467</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1838490927994874</v>
+        <v>0.2008506166562076</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1696499969652367</v>
+        <v>0.1904699982721754</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1591055811753483</v>
+        <v>0.1649985775335829</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1542491562246882</v>
+        <v>0.160596948868539</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1467023811191384</v>
+        <v>0.1441416931398423</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1362485125935862</v>
+        <v>0.1353170299953041</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>CS1.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.135206946842573</v>
+        <v>0.1282549445401135</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi IBEX 35 UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CS1.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1194480937304208</v>
+        <v>0.126431148030081</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi IBEX 35 UCITS ETF Acc</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DJE.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1148247050008953</v>
+        <v>0.1216529210900508</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Dow Jones Industrial Average UCITS ETF Dist</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1110890318073692</v>
+        <v>0.1149764109566018</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.110673467104661</v>
+        <v>0.1131294067374118</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>MIB.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1081878575210629</v>
+        <v>0.1127273097182766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4956240383965944</v>
+        <v>0.5037491036956667</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4437185066340474</v>
+        <v>0.4888121886863201</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1240,30 +1240,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4142627557362293</v>
+        <v>0.4080003256735947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4106631042352755</v>
+        <v>0.4019104003266849</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3351826297409366</v>
+        <v>0.3966467394800244</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3051328999020051</v>
+        <v>0.3235597371505827</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2996894812795008</v>
+        <v>0.3082963803238115</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1315,75 +1315,75 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2418756545515186</v>
+        <v>0.2712172036671361</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2415197257641455</v>
+        <v>0.2651265126512652</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2199432373402497</v>
+        <v>0.2506786076514567</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2126569242498173</v>
+        <v>0.2417177668724291</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.206646565072691</v>
+        <v>0.2186768305974394</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2029938810343284</v>
+        <v>0.2186572400057962</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1405,15 +1405,15 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.199134582941334</v>
+        <v>0.2142505295681256</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1831299812372749</v>
+        <v>0.2114027282682434</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.46619464323778</v>
+        <v>1.421534214428779</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.455317783462296</v>
+        <v>1.411924271040247</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.032792571123795</v>
+        <v>1.022762539345026</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9017290959237811</v>
+        <v>0.8870829989558531</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1526,15 +1526,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7673579284676419</v>
+        <v>0.804127802905767</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7595997743649483</v>
+        <v>0.7533396704129764</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1556,15 +1556,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7481519390811</v>
+        <v>0.7496716692564072</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.586888661847728</v>
+        <v>0.5701724085314521</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5832324925195835</v>
+        <v>0.5585107870271728</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5394736278789412</v>
+        <v>0.5400366903681089</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5381448923787799</v>
+        <v>0.5286286307815908</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5364102671574145</v>
+        <v>0.519629901198619</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5309699094035556</v>
+        <v>0.5186327876746299</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5114798928943958</v>
+        <v>0.5164248889495022</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5033996253531416</v>
+        <v>0.5087400341196884</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.686451749559323</v>
+        <v>2.748217951853834</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.320304315831575</v>
+        <v>2.314293793086003</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.699544641799948</v>
+        <v>1.664539764545988</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.676885075545107</v>
+        <v>1.639971754868074</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.460209875465992</v>
+        <v>1.508578192076366</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1797,30 +1797,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.376890994853276</v>
+        <v>1.372316705705429</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.359291537812763</v>
+        <v>1.365853850346674</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.287966879322306</v>
+        <v>1.301606592925761</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.267719328213014</v>
+        <v>1.259010486622427</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.196158799805076</v>
+        <v>1.205301862761404</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.185240907734496</v>
+        <v>1.190276811838599</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.179677736848425</v>
+        <v>1.187402174413315</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.169332550483148</v>
+        <v>1.183957823592419</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.166599462105605</v>
+        <v>1.180607276023945</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.134501125090085</v>
+        <v>1.153687219451018</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7768945270947378</v>
+        <v>0.7403727605991994</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7720335481659892</v>
+        <v>0.7326032196338643</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5162434449537534</v>
+        <v>0.5055964252444849</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2023,30 +2023,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4555663544595732</v>
+        <v>0.4479761785562484</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4343182931451302</v>
+        <v>0.4441205116497382</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3982273316986409</v>
+        <v>0.3916564226348644</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3555418123401739</v>
+        <v>0.3494484669411411</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3510083383846798</v>
+        <v>0.339382663778802</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2098,105 +2098,105 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3358406822311886</v>
+        <v>0.3263432727909785</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3089662456918001</v>
+        <v>0.3259344336803227</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FEMI.MI</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3056483483051464</v>
+        <v>0.3122564718441421</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>FEMI.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2957846445933119</v>
+        <v>0.3091405687133861</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2845447180308118</v>
+        <v>0.2825556360029591</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2835007258706546</v>
+        <v>0.2799519994101236</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2792999999586034</v>
+        <v>0.2772893738600448</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,225 +442,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1063141539445875</v>
+        <v>0.1178123429000617</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ARKX.MI</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.103634108284405</v>
+        <v>0.1130564000285481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ARK Space &amp; Defence Innovation UCITS ETF USD (Acc)</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09749257172633974</v>
+        <v>0.1119822402147517</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>ARKX.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08939494065079234</v>
+        <v>0.1095626540022985</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>ARK Space &amp; Defence Innovation UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08643253772169479</v>
+        <v>0.1068764079978415</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08520269708566341</v>
+        <v>0.1001375487530145</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AIPO.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.08238555610653808</v>
+        <v>0.08276527652468091</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Defiance AI &amp; Power Infrastructure UCITS ETF Acc</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FEMI.MI</t>
+          <t>LAFRI.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.07788469339621384</v>
+        <v>0.0825858493629068</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
+          <t>Amundi Pan Africa UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07767927156187726</v>
+        <v>0.08038010217001812</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.07141478360359454</v>
+        <v>0.07981928701033625</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.07099421985607446</v>
+        <v>0.07749717237198483</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R1GR.AS</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0660442091569089</v>
+        <v>0.0768318029428714</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares Russell 1000 Growth UCITS ETF USD (Acc)</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>MATW.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06504398332737726</v>
+        <v>0.07355757414152686</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>R1GR.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.06269368522635932</v>
+        <v>0.06739251866381624</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>iShares Russell 1000 Growth UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LAFRI.MI</t>
+          <t>FEMI.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06242003841546051</v>
+        <v>0.06372554748620329</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Pan Africa UCITS ETF Acc</t>
+          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1452841744662738</v>
+        <v>0.2202003780691797</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -713,210 +713,210 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1021659699939153</v>
+        <v>0.141880920120387</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08637559921323734</v>
+        <v>0.116531703382394</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07626641655105337</v>
+        <v>0.1038726103721845</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SEL.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0689874752259263</v>
+        <v>0.09453949257252225</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.06711870544093634</v>
+        <v>0.08834659115894161</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>SEL.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.05969561699198866</v>
+        <v>0.08539464965957788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05968015829109019</v>
+        <v>0.08452533667831741</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>VMIG.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.05560070610200119</v>
+        <v>0.08348095663202271</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>MATW.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.05521990173228097</v>
+        <v>0.08184077541160062</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VMIG.MI</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05313169855887745</v>
+        <v>0.08034086279999775</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>LAFRI.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05032605954989111</v>
+        <v>0.07997162006102698</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi Pan Africa UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.04844170110924462</v>
+        <v>0.07914912072524571</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0470461988003259</v>
+        <v>0.07551893037124446</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>INDO.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04584741766517708</v>
+        <v>0.07414909327881869</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3547406753505902</v>
+        <v>0.4158282242694638</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2175781971330408</v>
+        <v>0.2272947633008178</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -984,195 +984,195 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2122661792736467</v>
+        <v>0.2188624000528478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2008506166562076</v>
+        <v>0.213780188635347</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1904699982721754</v>
+        <v>0.2095526275282757</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1649985775335829</v>
+        <v>0.1815805085310511</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.160596948868539</v>
+        <v>0.174182332517157</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1441416931398423</v>
+        <v>0.1555600443315845</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1353170299953041</v>
+        <v>0.1505477777285869</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CS1.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1282549445401135</v>
+        <v>0.1424883624985753</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi IBEX 35 UCITS ETF Acc</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.126431148030081</v>
+        <v>0.1423260198608707</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>CS1.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1216529210900508</v>
+        <v>0.139176949457346</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi IBEX 35 UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1149764109566018</v>
+        <v>0.1368225544815667</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1131294067374118</v>
+        <v>0.1320619979683442</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MIB.PA</t>
+          <t>SRIJ.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1127273097182766</v>
+        <v>0.1270464989269402</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Dis</t>
         </is>
       </c>
     </row>
@@ -1210,45 +1210,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5037491036956667</v>
+        <v>0.5006596352405317</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4888121886863201</v>
+        <v>0.480101140505879</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4080003256735947</v>
+        <v>0.3933095220863232</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4019104003266849</v>
+        <v>0.3679882443249112</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1270,15 +1270,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3966467394800244</v>
+        <v>0.3652626494271716</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3235597371505827</v>
+        <v>0.3107860934252922</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3082963803238115</v>
+        <v>0.2923669664737327</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2712172036671361</v>
+        <v>0.2453945421822985</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2651265126512652</v>
+        <v>0.2376516036372245</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1345,30 +1345,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2506786076514567</v>
+        <v>0.2308197326168095</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>FEMI.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2417177668724291</v>
+        <v>0.2067288333817043</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2186768305974394</v>
+        <v>0.2051905189779555</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1390,45 +1390,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FEMI.MI</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2186572400057962</v>
+        <v>0.2042614665698732</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>MIB.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2142505295681256</v>
+        <v>0.2024017600913528</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2114027282682434</v>
+        <v>0.2019528622992823</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.421534214428779</v>
+        <v>1.374644336337739</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.411924271040247</v>
+        <v>1.366373804906539</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.022762539345026</v>
+        <v>1.024080009149581</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8870829989558531</v>
+        <v>0.8676519806321144</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.804127802905767</v>
+        <v>0.8458417381659109</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1541,90 +1541,90 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7533396704129764</v>
+        <v>0.7296577532806801</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7496716692564072</v>
+        <v>0.7201017367881319</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5701724085314521</v>
+        <v>0.5650397871667987</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5585107870271728</v>
+        <v>0.558403486553176</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5400366903681089</v>
+        <v>0.5279889139038398</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5286286307815908</v>
+        <v>0.5206457094684893</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.519629901198619</v>
+        <v>0.5195580942574927</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1646,45 +1646,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5186327876746299</v>
+        <v>0.5112973246767771</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5164248889495022</v>
+        <v>0.5049020432650022</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5087400341196884</v>
+        <v>0.4875630384787053</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.748217951853834</v>
+        <v>2.905982191254441</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.314293793086003</v>
+        <v>2.429549167640102</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.664539764545988</v>
+        <v>1.669842933055134</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.639971754868074</v>
+        <v>1.641963146618459</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.508578192076366</v>
+        <v>1.502403391988491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1797,30 +1797,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.372316705705429</v>
+        <v>1.407325390695203</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.365853850346674</v>
+        <v>1.394434024211083</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.301606592925761</v>
+        <v>1.348664851195201</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.259010486622427</v>
+        <v>1.287385486776389</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.205301862761404</v>
+        <v>1.280909543930469</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1872,30 +1872,30 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.190276811838599</v>
+        <v>1.264823613660186</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.187402174413315</v>
+        <v>1.250874878045039</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.183957823592419</v>
+        <v>1.248709832591128</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.180607276023945</v>
+        <v>1.23026334681932</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.153687219451018</v>
+        <v>1.197037190353063</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7403727605991994</v>
+        <v>0.7214672367520867</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7326032196338643</v>
+        <v>0.7133040754738535</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5055964252444849</v>
+        <v>0.5178814579995386</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2023,30 +2023,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4479761785562484</v>
+        <v>0.4739229123017092</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4441205116497382</v>
+        <v>0.4479761785562484</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3916564226348644</v>
+        <v>0.3843214082854476</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3494484669411411</v>
+        <v>0.3407650307664596</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.339382663778802</v>
+        <v>0.3393193740448952</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2098,75 +2098,75 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3263432727909785</v>
+        <v>0.3207294643129357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3259344336803227</v>
+        <v>0.3189613382329421</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>FEMI.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3122564718441421</v>
+        <v>0.3179472138511856</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FEMI.MI</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3091405687133861</v>
+        <v>0.3041091100728683</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2825556360029591</v>
+        <v>0.2888279251497687</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2799519994101236</v>
+        <v>0.2885382671707835</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,15 +2188,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2772893738600448</v>
+        <v>0.2883885212180373</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1178123429000617</v>
+        <v>0.1286005945426365</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -457,30 +457,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1130564000285481</v>
+        <v>0.1099121045116498</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>LAFRI.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1119822402147517</v>
+        <v>0.09495798122904442</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi Pan Africa UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1095626540022985</v>
+        <v>0.08995060794253118</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -502,15 +502,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1068764079978415</v>
+        <v>0.08584356747289523</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1001375487530145</v>
+        <v>0.08066489436458246</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -532,135 +532,135 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.08276527652468091</v>
+        <v>0.07835776923339921</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LAFRI.MI</t>
+          <t>MATW.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0825858493629068</v>
+        <v>0.07366984549435074</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Pan Africa UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.08038010217001812</v>
+        <v>0.06963838284429924</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.07981928701033625</v>
+        <v>0.06521493802323342</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.07749717237198483</v>
+        <v>0.06363508431551912</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0768318029428714</v>
+        <v>0.06162047565166806</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MATW.PA</t>
+          <t>JPXX.L</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07355757414152686</v>
+        <v>0.05828672357962916</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R1GR.AS</t>
+          <t>JPXY.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.06739251866381624</v>
+        <v>0.05514839155277418</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares Russell 1000 Growth UCITS ETF USD (Acc)</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR (C)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FEMI.MI</t>
+          <t>JPHE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06372554748620329</v>
+        <v>0.05490310679257004</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
+          <t>Amundi JPX Nikkei 400 UCITS ETF Daily Hedged EUR (C)</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2202003780691797</v>
+        <v>0.1614075058125071</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.141880920120387</v>
+        <v>0.0996121970881636</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.116531703382394</v>
+        <v>0.09875817029068323</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -743,180 +743,180 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1038726103721845</v>
+        <v>0.0931501650843547</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>LAFRI.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.09453949257252225</v>
+        <v>0.08658786007749075</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi Pan Africa UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08834659115894161</v>
+        <v>0.08476612149804774</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SEL.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.08539464965957788</v>
+        <v>0.08360927032815058</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.08452533667831741</v>
+        <v>0.07559008956546487</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VMIG.MI</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.08348095663202271</v>
+        <v>0.07147332218971569</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MATW.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.08184077541160062</v>
+        <v>0.06984759735855706</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08034086279999775</v>
+        <v>0.06983315301183857</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LAFRI.MI</t>
+          <t>SEL.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.07997162006102698</v>
+        <v>0.06953009871654858</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Pan Africa UCITS ETF Acc</t>
+          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>VMIG.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07914912072524571</v>
+        <v>0.0629478972063604</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.07551893037124446</v>
+        <v>0.06234638917379542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>INDO.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.07414909327881869</v>
+        <v>0.06017719986581427</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4158282242694638</v>
+        <v>0.4564579241731022</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2272947633008178</v>
+        <v>0.227195329942079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2188624000528478</v>
+        <v>0.2243452931200474</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -999,75 +999,75 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.213780188635347</v>
+        <v>0.2055076506064404</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2095526275282757</v>
+        <v>0.193270370220505</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1815805085310511</v>
+        <v>0.1700387151526404</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.174182332517157</v>
+        <v>0.1608030199117183</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1555600443315845</v>
+        <v>0.1601068142380395</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1505477777285869</v>
+        <v>0.1535235821353904</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1089,45 +1089,45 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1424883624985753</v>
+        <v>0.152890825976373</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>CS1.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1423260198608707</v>
+        <v>0.1392986591670264</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi IBEX 35 UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CS1.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.139176949457346</v>
+        <v>0.1363796472430869</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi IBEX 35 UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1368225544815667</v>
+        <v>0.1355913014549379</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1149,30 +1149,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>MSEU.L</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1320619979683442</v>
+        <v>0.1216862523143751</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 II UCITS ETF USD Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SRIJ.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1270464989269402</v>
+        <v>0.1203016231183502</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Dis</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5006596352405317</v>
+        <v>0.5674321528270572</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.480101140505879</v>
+        <v>0.4618904320622081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1240,45 +1240,45 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3933095220863232</v>
+        <v>0.339291723284044</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3679882443249112</v>
+        <v>0.3357831562808016</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3652626494271716</v>
+        <v>0.3349543956403862</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3107860934252922</v>
+        <v>0.3031036891167731</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2923669664737327</v>
+        <v>0.2634480157160815</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1315,120 +1315,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2453945421822985</v>
+        <v>0.2532902360605447</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2376516036372245</v>
+        <v>0.2280822126832727</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2308197326168095</v>
+        <v>0.2155714352833542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FEMI.MI</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2067288333817043</v>
+        <v>0.2122712734303358</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2051905189779555</v>
+        <v>0.1980028193583241</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2042614665698732</v>
+        <v>0.1857919392832044</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MIB.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2024017600913528</v>
+        <v>0.1803378428370095</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2019528622992823</v>
+        <v>0.1787967343951105</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.374644336337739</v>
+        <v>1.356256902297533</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.366373804906539</v>
+        <v>1.345777559896149</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.024080009149581</v>
+        <v>1.009596324358591</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1511,30 +1511,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8676519806321144</v>
+        <v>0.9225634257102964</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8458417381659109</v>
+        <v>0.8661548678253099</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7296577532806801</v>
+        <v>0.7168121328076542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7201017367881319</v>
+        <v>0.6917631834802955</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5650397871667987</v>
+        <v>0.566045540028725</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1586,30 +1586,30 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.558403486553176</v>
+        <v>0.5586359308439022</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5279889139038398</v>
+        <v>0.5330027740703127</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5206457094684893</v>
+        <v>0.5329434220510325</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1631,30 +1631,30 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5195580942574927</v>
+        <v>0.508797000050631</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5112973246767771</v>
+        <v>0.489799237733334</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5049020432650022</v>
+        <v>0.4842916783371327</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4875630384787053</v>
+        <v>0.4826860580035219</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.905982191254441</v>
+        <v>2.817048829414692</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.429549167640102</v>
+        <v>2.355503909208428</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.669842933055134</v>
+        <v>1.661572648060416</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.641963146618459</v>
+        <v>1.63476883055457</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1782,150 +1782,150 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.502403391988491</v>
+        <v>1.420513564543717</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.407325390695203</v>
+        <v>1.409031690656535</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.394434024211083</v>
+        <v>1.375181956494008</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.348664851195201</v>
+        <v>1.359821181345086</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.287385486776389</v>
+        <v>1.314508217942151</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.280909543930469</v>
+        <v>1.304181369954299</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.264823613660186</v>
+        <v>1.26177819502863</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.250874878045039</v>
+        <v>1.261097703866631</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.248709832591128</v>
+        <v>1.252943930688578</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.23026334681932</v>
+        <v>1.222410823932984</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.197037190353063</v>
+        <v>1.169442022208266</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7214672367520867</v>
+        <v>0.7062140206789822</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7133040754738535</v>
+        <v>0.6969995144845444</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2008,30 +2008,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5178814579995386</v>
+        <v>0.5549076899661431</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4739229123017092</v>
+        <v>0.5263445037066505</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4479761785562484</v>
+        <v>0.4442512834935768</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3843214082854476</v>
+        <v>0.3699571849214069</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3407650307664596</v>
+        <v>0.3632950389419618</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2083,120 +2083,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3393193740448952</v>
+        <v>0.3580924195927788</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3207294643129357</v>
+        <v>0.3295943550995137</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3189613382329421</v>
+        <v>0.3253630752703429</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FEMI.MI</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3179472138511856</v>
+        <v>0.3159340747633177</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3041091100728683</v>
+        <v>0.3131737272535589</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2888279251497687</v>
+        <v>0.2911342112214861</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2885382671707835</v>
+        <v>0.2897449844907618</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2883885212180373</v>
+        <v>0.2826336851009232</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,225 +442,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1286005945426365</v>
+        <v>0.1004565951548846</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1099121045116498</v>
+        <v>0.07358583522037843</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LAFRI.MI</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09495798122904442</v>
+        <v>0.06487168865050741</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi Pan Africa UCITS ETF Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKX.MI</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08995060794253118</v>
+        <v>0.06297266574992588</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Space &amp; Defence Innovation UCITS ETF USD (Acc)</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08584356747289523</v>
+        <v>0.06117395686815796</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>LAFRI.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08066489436458246</v>
+        <v>0.05918366645220896</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Amundi Pan Africa UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.07835776923339921</v>
+        <v>0.05734966342446035</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MATW.PA</t>
+          <t>JPXY.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.07366984549435074</v>
+        <v>0.05474555270396309</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR (C)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>JPXX.L</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.06963838284429924</v>
+        <v>0.05433829973707271</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>JPXH.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06521493802323342</v>
+        <v>0.05322459818411618</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - EUR Hedged (C)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06363508431551912</v>
+        <v>0.0502979944530233</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>MATW.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06162047565166806</v>
+        <v>0.0498334532679896</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JPXX.L</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05828672357962916</v>
+        <v>0.04920108069221429</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>JPXY.AS</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05514839155277418</v>
+        <v>0.04560875381537977</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR (C)</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JPHE.PA</t>
+          <t>SRIJC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05490310679257004</v>
+        <v>0.04560514588420772</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi JPX Nikkei 400 UCITS ETF Daily Hedged EUR (C)</t>
+          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1614075058125071</v>
+        <v>0.1478294015470352</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -713,135 +713,135 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0996121970881636</v>
+        <v>0.114039039913246</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09875817029068323</v>
+        <v>0.1123446526704659</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0931501650843547</v>
+        <v>0.1026386512865343</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LAFRI.MI</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08658786007749075</v>
+        <v>0.09899154670148524</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi Pan Africa UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08476612149804774</v>
+        <v>0.09046832718482545</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>LAFRI.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.08360927032815058</v>
+        <v>0.08200134283172611</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi Pan Africa UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.07559008956546487</v>
+        <v>0.08086211058445647</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07147332218971569</v>
+        <v>0.08007174640012504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06984759735855706</v>
+        <v>0.07786543446123906</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06983315301183857</v>
+        <v>0.07578910155364271</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -863,60 +863,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SEL.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06953009871654858</v>
+        <v>0.07203152760436415</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VMIG.MI</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0629478972063604</v>
+        <v>0.06998010310532643</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>SEL.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.06234638917379542</v>
+        <v>0.06974277438080723</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06017719986581427</v>
+        <v>0.06826816324415153</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4564579241731022</v>
+        <v>0.5233881803256337</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -969,210 +969,210 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.227195329942079</v>
+        <v>0.2664469465236114</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2243452931200474</v>
+        <v>0.2477627526846826</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2055076506064404</v>
+        <v>0.2327841238327764</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.193270370220505</v>
+        <v>0.225551185648583</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1700387151526404</v>
+        <v>0.1951629606581888</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1608030199117183</v>
+        <v>0.1853203677784601</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1601068142380395</v>
+        <v>0.1808791092677657</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>CS1.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1535235821353904</v>
+        <v>0.1603019153371634</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>Amundi IBEX 35 UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.152890825976373</v>
+        <v>0.1547126146231599</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CS1.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1392986591670264</v>
+        <v>0.1533875233973259</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi IBEX 35 UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1363796472430869</v>
+        <v>0.1484684758000188</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1355913014549379</v>
+        <v>0.1477596217155299</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MSEU.L</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1216862523143751</v>
+        <v>0.14474634864723</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 II UCITS ETF USD Hedged Acc</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>MSEU.L</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1203016231183502</v>
+        <v>0.1396100992090494</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 II UCITS ETF USD Hedged Acc</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5674321528270572</v>
+        <v>0.5447067561014374</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4618904320622081</v>
+        <v>0.4599685726637068</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.339291723284044</v>
+        <v>0.3898333972142722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1255,30 +1255,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3357831562808016</v>
+        <v>0.3889853459106887</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3349543956403862</v>
+        <v>0.3406846369613943</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3031036891167731</v>
+        <v>0.3029875223826626</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,30 +1300,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2634480157160815</v>
+        <v>0.2889227381573864</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2532902360605447</v>
+        <v>0.2555399327660277</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2280822126832727</v>
+        <v>0.2413651429732449</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2155714352833542</v>
+        <v>0.2342831909653662</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2122712734303358</v>
+        <v>0.2046257954051462</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1375,45 +1375,45 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1980028193583241</v>
+        <v>0.1932458231263452</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1857919392832044</v>
+        <v>0.1927394740819506</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1803378428370095</v>
+        <v>0.1901170210977694</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1787967343951105</v>
+        <v>0.1890519734558813</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.356256902297533</v>
+        <v>1.422186357691689</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.345777559896149</v>
+        <v>1.41493785383581</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.009596324358591</v>
+        <v>0.9996668891642007</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9225634257102964</v>
+        <v>0.9213393561215792</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8661548678253099</v>
+        <v>0.8565961665339652</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7168121328076542</v>
+        <v>0.7162380275693805</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6917631834802955</v>
+        <v>0.7066162328804027</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1571,105 +1571,105 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.566045540028725</v>
+        <v>0.5703108592852562</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5586359308439022</v>
+        <v>0.5397823897437692</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5330027740703127</v>
+        <v>0.5353811993383311</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5329434220510325</v>
+        <v>0.5275701937968882</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.508797000050631</v>
+        <v>0.5203969248015334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.489799237733334</v>
+        <v>0.5169121023595795</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4842916783371327</v>
+        <v>0.5061088129826683</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4826860580035219</v>
+        <v>0.4993495786093114</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.817048829414692</v>
+        <v>2.830174907132418</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.355503909208428</v>
+        <v>2.355919504431874</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.661572648060416</v>
+        <v>1.739657126610439</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.63476883055457</v>
+        <v>1.716653265539395</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1782,30 +1782,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.420513564543717</v>
+        <v>1.428757668029672</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.409031690656535</v>
+        <v>1.416395748979471</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.375181956494008</v>
+        <v>1.366152025178556</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.359821181345086</v>
+        <v>1.332232330844454</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.314508217942151</v>
+        <v>1.327409842958541</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.304181369954299</v>
+        <v>1.300235763707252</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.26177819502863</v>
+        <v>1.277136734203751</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1887,30 +1887,30 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.261097703866631</v>
+        <v>1.260900646137112</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.252943930688578</v>
+        <v>1.254092544247333</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.222410823932984</v>
+        <v>1.236478295131001</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.169442022208266</v>
+        <v>1.172600367175864</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7062140206789822</v>
+        <v>0.7562704533660796</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6969995144845444</v>
+        <v>0.7497395669709865</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5549076899661431</v>
+        <v>0.5613865174893846</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5263445037066505</v>
+        <v>0.5233414580932658</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4442512834935768</v>
+        <v>0.4492177786678002</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2053,15 +2053,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3699571849214069</v>
+        <v>0.3947411753117875</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3632950389419618</v>
+        <v>0.3872329667189378</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2083,120 +2083,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3580924195927788</v>
+        <v>0.3840158361228501</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3295943550995137</v>
+        <v>0.3496280568758805</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3253630752703429</v>
+        <v>0.3441500876011483</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3159340747633177</v>
+        <v>0.3282850732720621</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3131737272535589</v>
+        <v>0.3232601102405621</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2911342112214861</v>
+        <v>0.2969343329785645</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2897449844907618</v>
+        <v>0.2889377134912614</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2826336851009232</v>
+        <v>0.2840830277042332</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1004565951548846</v>
+        <v>0.06691398055466502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -457,30 +457,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07358583522037843</v>
+        <v>0.06076252629779333</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>JPJY.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.06487168865050741</v>
+        <v>0.0591066938825382</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>State Street SPDR MSCI Japan UCITS ETF JPY Unhedged</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06297266574992588</v>
+        <v>0.05022333949707924</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -502,30 +502,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>LAFRI.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.06117395686815796</v>
+        <v>0.05016184236609478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi Pan Africa UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LAFRI.MI</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05918366645220896</v>
+        <v>0.04781794152716889</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Pan Africa UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.05734966342446035</v>
+        <v>0.0472696811870601</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -547,120 +547,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JPXY.AS</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05474555270396309</v>
+        <v>0.04614420445361489</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR (C)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JPXX.L</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.05433829973707271</v>
+        <v>0.04193856310693422</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JPXH.PA</t>
+          <t>JPXY.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.05322459818411618</v>
+        <v>0.04065290050727777</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - EUR Hedged (C)</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR (C)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0502979944530233</v>
+        <v>0.04018591435024343</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MATW.PA</t>
+          <t>JPXH.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0498334532679896</v>
+        <v>0.03978616533038437</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - EUR Hedged (C)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>JPXX.L</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.04920108069221429</v>
+        <v>0.03786277147799355</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.04560875381537977</v>
+        <v>0.03758816865308967</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SRIJC.PA</t>
+          <t>XMK9.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04560514588420772</v>
+        <v>0.03733820216845229</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
+          <t>Xtrackers MSCI Japan UCITS ETF 4C - EUR Hedged</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1478294015470352</v>
+        <v>0.1664099289108509</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -713,30 +713,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.114039039913246</v>
+        <v>0.1028705228355069</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1123446526704659</v>
+        <v>0.09979255411773469</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1026386512865343</v>
+        <v>0.09741900523234648</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -758,90 +758,90 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>LAFRI.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.09899154670148524</v>
+        <v>0.08695047428826141</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi Pan Africa UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.09046832718482545</v>
+        <v>0.0837879535849777</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LAFRI.MI</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.08200134283172611</v>
+        <v>0.08212223565156762</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Pan Africa UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.08086211058445647</v>
+        <v>0.07600904305664358</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.08007174640012504</v>
+        <v>0.07526883462875378</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.07786543446123906</v>
+        <v>0.07159243349594524</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.07578910155364271</v>
+        <v>0.07158639938200673</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -863,60 +863,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.07203152760436415</v>
+        <v>0.06809975329057383</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>SEL.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06998010310532643</v>
+        <v>0.0671877533795493</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEL.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.06974277438080723</v>
+        <v>0.06673955863704184</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06826816324415153</v>
+        <v>0.0654911701756129</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5233881803256337</v>
+        <v>0.4964103504472772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -969,105 +969,105 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2664469465236114</v>
+        <v>0.2423426855902351</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2477627526846826</v>
+        <v>0.2384044031151453</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2327841238327764</v>
+        <v>0.2210631335692299</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.225551185648583</v>
+        <v>0.1999176270430858</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1951629606581888</v>
+        <v>0.1773470652875557</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1853203677784601</v>
+        <v>0.176624949671734</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1808791092677657</v>
+        <v>0.1732365145228216</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1603019153371634</v>
+        <v>0.156056602687908</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1089,30 +1089,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1547126146231599</v>
+        <v>0.1548780465111856</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1533875233973259</v>
+        <v>0.153105714898369</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1484684758000188</v>
+        <v>0.1400403916573447</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1134,30 +1134,30 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1477596217155299</v>
+        <v>0.1391865867332549</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>VMIG.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.14474634864723</v>
+        <v>0.1295422190903399</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1396100992090494</v>
+        <v>0.1292198732666681</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5447067561014374</v>
+        <v>0.6006678373987882</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4599685726637068</v>
+        <v>0.4815007883491398</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3898333972142722</v>
+        <v>0.4144062303105527</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3889853459106887</v>
+        <v>0.4124696941375814</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3406846369613943</v>
+        <v>0.3569266063805363</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3029875223826626</v>
+        <v>0.3061514658719664</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,75 +1300,75 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2889227381573864</v>
+        <v>0.2767047173056465</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2555399327660277</v>
+        <v>0.2470619748741449</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2413651429732449</v>
+        <v>0.2432692598661739</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2342831909653662</v>
+        <v>0.2352195786757136</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2046257954051462</v>
+        <v>0.2227301532264703</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1932458231263452</v>
+        <v>0.2184848488187223</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1390,45 +1390,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1927394740819506</v>
+        <v>0.209187434100309</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1901170210977694</v>
+        <v>0.2085935460508368</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1890519734558813</v>
+        <v>0.1976541563254763</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.422186357691689</v>
+        <v>1.528944747609165</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.41493785383581</v>
+        <v>1.519195254353555</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9996668891642007</v>
+        <v>0.9980205358082845</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9213393561215792</v>
+        <v>0.8896334061422089</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8565961665339652</v>
+        <v>0.8727482329011014</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7162380275693805</v>
+        <v>0.7044950885481052</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7066162328804027</v>
+        <v>0.6731974777436371</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5703108592852562</v>
+        <v>0.5932285487600313</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5397823897437692</v>
+        <v>0.5867459587867487</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,60 +1601,60 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5353811993383311</v>
+        <v>0.5596248521157712</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5275701937968882</v>
+        <v>0.5473998367679409</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5203969248015334</v>
+        <v>0.5392381824517365</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5169121023595795</v>
+        <v>0.5350506466877127</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5061088129826683</v>
+        <v>0.5190964995614795</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4993495786093114</v>
+        <v>0.4859646315734745</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.830174907132418</v>
+        <v>2.824924375901684</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.355919504431874</v>
+        <v>2.367143366397426</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.739657126610439</v>
+        <v>1.865832140794345</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.716653265539395</v>
+        <v>1.84141736628434</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.428757668029672</v>
+        <v>1.452233416934532</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.366152025178556</v>
+        <v>1.370812556031488</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.332232330844454</v>
+        <v>1.353215462871664</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.327409842958541</v>
+        <v>1.336416725385268</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.300235763707252</v>
+        <v>1.299841240709919</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.277136734203751</v>
+        <v>1.297352190810675</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1887,30 +1887,30 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.260900646137112</v>
+        <v>1.275108434230271</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.254092544247333</v>
+        <v>1.249761293073101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.236478295131001</v>
+        <v>1.221198225754027</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7562704533660796</v>
+        <v>0.8371555565462736</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7497395669709865</v>
+        <v>0.8300975156205872</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5613865174893846</v>
+        <v>0.5529640931979056</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5233414580932658</v>
+        <v>0.5468194715139598</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4492177786678002</v>
+        <v>0.4472311427069042</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2053,90 +2053,90 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3947411753117875</v>
+        <v>0.4269558950128198</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3872329667189378</v>
+        <v>0.3885023416185718</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3840158361228501</v>
+        <v>0.3729171359314218</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3496280568758805</v>
+        <v>0.3679239169789741</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3441500876011483</v>
+        <v>0.3549816778212094</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3282850732720621</v>
+        <v>0.3478569353372993</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3232601102405621</v>
+        <v>0.3324176196539916</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2969343329785645</v>
+        <v>0.3019533609283107</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2188,15 +2188,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2840830277042332</v>
+        <v>0.2864343326125105</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.06691398055466502</v>
+        <v>0.08538957925020263</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -457,30 +457,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.06076252629779333</v>
+        <v>0.08350819912672103</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JPJY.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0591066938825382</v>
+        <v>0.08306127882250314</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Japan UCITS ETF JPY Unhedged</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05022333949707924</v>
+        <v>0.07626889377310841</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -502,165 +502,165 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LAFRI.MI</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05016184236609478</v>
+        <v>0.05557316581176885</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi Pan Africa UCITS ETF Acc</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04781794152716889</v>
+        <v>0.05275087816670565</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0472696811870601</v>
+        <v>0.04514960625700293</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04614420445361489</v>
+        <v>0.04153641494093785</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.04193856310693422</v>
+        <v>0.03996247792936436</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JPXY.AS</t>
+          <t>EJAH.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.04065290050727777</v>
+        <v>0.0396487320482799</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR (C)</t>
+          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>LCJP.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04018591435024343</v>
+        <v>0.03743908145971209</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi Core MSCI Japan UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JPXH.PA</t>
+          <t>XMK9.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03978616533038437</v>
+        <v>0.03742170233224162</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - EUR Hedged (C)</t>
+          <t>Xtrackers MSCI Japan UCITS ETF 4C - EUR Hedged</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JPXX.L</t>
+          <t>LJPN.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.03786277147799355</v>
+        <v>0.03726475311848887</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
+          <t>Amundi Core MSCI Japan UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>JPJY.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.03758816865308967</v>
+        <v>0.03723974954694609</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>State Street SPDR MSCI Japan UCITS ETF JPY Unhedged</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XMK9.MI</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.03733820216845229</v>
+        <v>0.03627221735375974</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI Japan UCITS ETF 4C - EUR Hedged</t>
+          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -698,60 +698,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1664099289108509</v>
+        <v>0.08809899299062618</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1028705228355069</v>
+        <v>0.08690808612417822</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09979255411773469</v>
+        <v>0.08344529409265022</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.09741900523234648</v>
+        <v>0.08332350998191873</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08695047428826141</v>
+        <v>0.08102765002549428</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -773,150 +773,150 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0837879535849777</v>
+        <v>0.07748150750636928</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.08212223565156762</v>
+        <v>0.07225893290228691</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>VMIG.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.07600904305664358</v>
+        <v>0.06859137519206526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07526883462875378</v>
+        <v>0.06859043885023608</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.07159243349594524</v>
+        <v>0.05887315651547298</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>SEL.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.07158639938200673</v>
+        <v>0.05624344636631884</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06809975329057383</v>
+        <v>0.05445274217384188</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SEL.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0671877533795493</v>
+        <v>0.05384328879164446</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>MSEC.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.06673955863704184</v>
+        <v>0.05279504486689013</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi EURO STOXX 50 II UCITS ETF CHF Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0654911701756129</v>
+        <v>0.05119877907683645</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4964103504472772</v>
+        <v>0.503625374927652</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2423426855902351</v>
+        <v>0.2329532801605012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2384044031151453</v>
+        <v>0.2101105749978229</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2210631335692299</v>
+        <v>0.2047769370805768</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1999176270430858</v>
+        <v>0.1815234800178185</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1773470652875557</v>
+        <v>0.1662851059430126</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.176624949671734</v>
+        <v>0.1568979688219212</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1059,90 +1059,90 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1732365145228216</v>
+        <v>0.1460004804437744</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CS1.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.156056602687908</v>
+        <v>0.1455008517972969</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi IBEX 35 UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>CS1.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1548780465111856</v>
+        <v>0.1441412504600383</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>Amundi IBEX 35 UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.153105714898369</v>
+        <v>0.1386979483561879</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1400403916573447</v>
+        <v>0.132546599435355</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>MSEC.SW</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1391865867332549</v>
+        <v>0.1248086420051187</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi EURO STOXX 50 II UCITS ETF CHF Hedged Acc</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1295422190903399</v>
+        <v>0.1182076615395133</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1292198732666681</v>
+        <v>0.1144388020791367</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6006678373987882</v>
+        <v>0.6548106790210901</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4815007883491398</v>
+        <v>0.538297296834696</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4144062303105527</v>
+        <v>0.4267254387084818</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4124696941375814</v>
+        <v>0.4180130183619486</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3569266063805363</v>
+        <v>0.3725581875978083</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3061514658719664</v>
+        <v>0.35078636289929</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2767047173056465</v>
+        <v>0.3196471066691073</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1315,120 +1315,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2470619748741449</v>
+        <v>0.301592626648205</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2432692598661739</v>
+        <v>0.24887552625502</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2352195786757136</v>
+        <v>0.2467875680664784</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2227301532264703</v>
+        <v>0.242145739734609</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2184848488187223</v>
+        <v>0.2420255130448556</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.209187434100309</v>
+        <v>0.2365960514160765</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2085935460508368</v>
+        <v>0.2334567536974894</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1976541563254763</v>
+        <v>0.2313926533840314</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.528944747609165</v>
+        <v>1.569337883538306</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.519195254353555</v>
+        <v>1.554507574347086</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1496,75 +1496,75 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9980205358082845</v>
+        <v>0.9032523647012978</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8896334061422089</v>
+        <v>0.8975522801829348</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8727482329011014</v>
+        <v>0.811330160289639</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7044950885481052</v>
+        <v>0.6582531083084475</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6731974777436371</v>
+        <v>0.6564880310570191</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5932285487600313</v>
+        <v>0.593657265235261</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5867459587867487</v>
+        <v>0.5836298865668932</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,75 +1601,75 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5596248521157712</v>
+        <v>0.5576306073802533</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5473998367679409</v>
+        <v>0.5559654775899716</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5392381824517365</v>
+        <v>0.52906607984164</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5350506466877127</v>
+        <v>0.5055705662975929</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5190964995614795</v>
+        <v>0.5049993701263695</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4859646315734745</v>
+        <v>0.4641605599912502</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.824924375901684</v>
+        <v>2.78581083448615</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.367143366397426</v>
+        <v>2.367379103875961</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.865832140794345</v>
+        <v>1.964320107082837</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.84141736628434</v>
+        <v>1.93004966489549</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.452233416934532</v>
+        <v>1.523793786237172</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.416395748979471</v>
+        <v>1.399044876569716</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.370812556031488</v>
+        <v>1.369530423471872</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1827,30 +1827,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.353215462871664</v>
+        <v>1.33210696010549</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.336416725385268</v>
+        <v>1.298900270385033</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.299841240709919</v>
+        <v>1.295540183972964</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.297352190810675</v>
+        <v>1.277072476033069</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.275108434230271</v>
+        <v>1.274530197232032</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.249761293073101</v>
+        <v>1.222923945572569</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.221198225754027</v>
+        <v>1.220289729010919</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.172600367175864</v>
+        <v>1.158895501742325</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8371555565462736</v>
+        <v>0.8857081556460387</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8300975156205872</v>
+        <v>0.8765154587486395</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2008,30 +2008,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5529640931979056</v>
+        <v>0.5735735110262243</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5468194715139598</v>
+        <v>0.5674333545260966</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4472311427069042</v>
+        <v>0.4482244606873522</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4269558950128198</v>
+        <v>0.428025572461058</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3885023416185718</v>
+        <v>0.396309045181205</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2083,45 +2083,45 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3729171359314218</v>
+        <v>0.3852039779787977</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3679239169789741</v>
+        <v>0.3695893336558043</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3549816778212094</v>
+        <v>0.3684580315267132</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3478569353372993</v>
+        <v>0.3453773145098358</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3324176196539916</v>
+        <v>0.3179487380128725</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2158,45 +2158,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3019533609283107</v>
+        <v>0.3033145818016401</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2889377134912614</v>
+        <v>0.2897449844907618</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>AASI.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2864343326125105</v>
+        <v>0.2801907647669588</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,225 +442,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.08538957925020263</v>
+        <v>0.09653064863947214</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08350819912672103</v>
+        <v>0.09487275514259919</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08306127882250314</v>
+        <v>0.06661710142531563</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07626889377310841</v>
+        <v>0.04890165011876557</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05557316581176885</v>
+        <v>0.03884289760014203</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05275087816670565</v>
+        <v>0.03190498615277959</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04514960625700293</v>
+        <v>0.03100482425131501</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HYPE.SW</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04153641494093785</v>
+        <v>0.02958169923887133</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>21shares Hyperliquid ETP</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.03996247792936436</v>
+        <v>0.02939998827730417</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EJAH.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0396487320482799</v>
+        <v>0.02905627636885133</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LCJP.AS</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03743908145971209</v>
+        <v>0.02815067400097448</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Core MSCI Japan UCITS ETF Acc</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>XMK9.MI</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03742170233224162</v>
+        <v>0.02771411866627393</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI Japan UCITS ETF 4C - EUR Hedged</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LJPN.AS</t>
+          <t>EJAH.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.03726475311848887</v>
+        <v>0.02649639570522155</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Core MSCI Japan UCITS ETF Dist</t>
+          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>JPJY.PA</t>
+          <t>LJPN.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.03723974954694609</v>
+        <v>0.02624813876759147</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Japan UCITS ETF JPY Unhedged</t>
+          <t>Amundi Core MSCI Japan UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>JPJY.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.03627221735375974</v>
+        <v>0.02583481677369259</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
+          <t>State Street SPDR MSCI Japan UCITS ETF JPY Unhedged</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.08809899299062618</v>
+        <v>0.1122608329356276</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08690808612417822</v>
+        <v>0.09880744321567336</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -728,15 +728,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08344529409265022</v>
+        <v>0.09726895190868978</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08332350998191873</v>
+        <v>0.08517691567032348</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -758,165 +758,165 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LAFRI.MI</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08102765002549428</v>
+        <v>0.08278268875998318</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi Pan Africa UCITS ETF Acc</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07748150750636928</v>
+        <v>0.07672942789204806</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>LAFRI.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.07225893290228691</v>
+        <v>0.06908581831046701</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi Pan Africa UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VMIG.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.06859137519206526</v>
+        <v>0.06771712294834797</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.06859043885023608</v>
+        <v>0.0669327502831718</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.05887315651547298</v>
+        <v>0.06467185981002066</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SEL.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05624344636631884</v>
+        <v>0.06341903617270228</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>VMIG.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05445274217384188</v>
+        <v>0.06033818859352769</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05384328879164446</v>
+        <v>0.05987970399554943</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MSEC.SW</t>
+          <t>SEL.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05279504486689013</v>
+        <v>0.05874968536524916</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 II UCITS ETF CHF Hedged Acc</t>
+          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>DDGT.L</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05119877907683645</v>
+        <v>0.05812955400261788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Dimensional Global Targeted Value UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.503625374927652</v>
+        <v>0.5063718866651377</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -969,30 +969,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2329532801605012</v>
+        <v>0.2538272111164737</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2101105749978229</v>
+        <v>0.2501922903180909</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2047769370805768</v>
+        <v>0.2322622958653249</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1815234800178185</v>
+        <v>0.2216387266796569</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1029,15 +1029,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1662851059430126</v>
+        <v>0.2003792770343396</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1568979688219212</v>
+        <v>0.1946651133937456</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1059,120 +1059,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1460004804437744</v>
+        <v>0.1867923778253258</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>CS1.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1455008517972969</v>
+        <v>0.1554226054012631</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>Amundi IBEX 35 UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CS1.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1441412504600383</v>
+        <v>0.1519924757817048</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi IBEX 35 UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1386979483561879</v>
+        <v>0.143953472228229</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.132546599435355</v>
+        <v>0.1426692168538994</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MSEC.SW</t>
+          <t>VMIG.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1248086420051187</v>
+        <v>0.140789777210476</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 II UCITS ETF CHF Hedged Acc</t>
+          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VMIG.MI</t>
+          <t>MSEU.L</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1182076615395133</v>
+        <v>0.1337990752754148</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
+          <t>Amundi EURO STOXX 50 II UCITS ETF USD Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MSEU.L</t>
+          <t>MSE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1144388020791367</v>
+        <v>0.1301577983825961</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 II UCITS ETF USD Hedged Acc</t>
+          <t>Amundi EURO STOXX 50 II UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6548106790210901</v>
+        <v>0.5094957839828718</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.538297296834696</v>
+        <v>0.4930876189401106</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1240,45 +1240,45 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4267254387084818</v>
+        <v>0.4176011915395559</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4180130183619486</v>
+        <v>0.4034597207482646</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3725581875978083</v>
+        <v>0.3977980452501493</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.35078636289929</v>
+        <v>0.3418431115894747</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3196471066691073</v>
+        <v>0.3103179896923138</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1315,75 +1315,75 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.301592626648205</v>
+        <v>0.2896825396825398</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.24887552625502</v>
+        <v>0.2706662314125177</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2467875680664784</v>
+        <v>0.2632277998011205</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.242145739734609</v>
+        <v>0.2557643464381054</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2420255130448556</v>
+        <v>0.2393068823112765</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2365960514160765</v>
+        <v>0.2368076585502492</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1405,30 +1405,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2334567536974894</v>
+        <v>0.2321655505665667</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2313926533840314</v>
+        <v>0.2316613555477156</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.569337883538306</v>
+        <v>1.598633536910964</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.554507574347086</v>
+        <v>1.581999415054894</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1496,30 +1496,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9032523647012978</v>
+        <v>0.9130005124604961</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8975522801829348</v>
+        <v>0.8762408791286471</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.811330160289639</v>
+        <v>0.7348218404334936</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1541,90 +1541,90 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6582531083084475</v>
+        <v>0.6518697216025704</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6564880310570191</v>
+        <v>0.6182113605028239</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.593657265235261</v>
+        <v>0.6168112285681293</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5836298865668932</v>
+        <v>0.5823515881870247</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5576306073802533</v>
+        <v>0.5695715156805479</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5559654775899716</v>
+        <v>0.5436907327142706</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.52906607984164</v>
+        <v>0.5391076108401867</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1646,45 +1646,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5055705662975929</v>
+        <v>0.4996518358131412</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5049993701263695</v>
+        <v>0.4635481989047538</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4641605599912502</v>
+        <v>0.4589945503516841</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.78581083448615</v>
+        <v>2.774775496468254</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.367379103875961</v>
+        <v>2.404595961581927</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.964320107082837</v>
+        <v>1.979383546923488</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.93004966489549</v>
+        <v>1.943662573600936</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.523793786237172</v>
+        <v>1.49610329726839</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1797,30 +1797,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.399044876569716</v>
+        <v>1.40889666749752</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.369530423471872</v>
+        <v>1.406625557977431</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.33210696010549</v>
+        <v>1.383387445449782</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1842,90 +1842,90 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.298900270385033</v>
+        <v>1.360436907522277</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.295540183972964</v>
+        <v>1.289683874222297</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.277072476033069</v>
+        <v>1.285381960032109</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.274530197232032</v>
+        <v>1.280047184780286</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.222923945572569</v>
+        <v>1.263541021666727</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.220289729010919</v>
+        <v>1.252530343552794</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.158895501742325</v>
+        <v>1.175920227140716</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8857081556460387</v>
+        <v>0.8876415857273654</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8765154587486395</v>
+        <v>0.8758499535111017</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5735735110262243</v>
+        <v>0.5479115236033736</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5674333545260966</v>
+        <v>0.4933592918939638</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2038,30 +2038,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4482244606873522</v>
+        <v>0.4520170094453393</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.428025572461058</v>
+        <v>0.4440030013624732</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.396309045181205</v>
+        <v>0.4068267194780761</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2083,45 +2083,45 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3852039779787977</v>
+        <v>0.3804271386565892</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3695893336558043</v>
+        <v>0.3782350079233008</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3684580315267132</v>
+        <v>0.3573323174129488</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3453773145098358</v>
+        <v>0.3547644866948412</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3179487380128725</v>
+        <v>0.3135531726195275</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2158,45 +2158,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3033145818016401</v>
+        <v>0.2961204757132325</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2897449844907618</v>
+        <v>0.2909344880612472</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AASI.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2801907647669588</v>
+        <v>0.2804453047355906</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,225 +442,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.09653064863947214</v>
+        <v>0.1611764945235907</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09487275514259919</v>
+        <v>0.1589649998876053</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.06661710142531563</v>
+        <v>0.08198548074758705</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04890165011876557</v>
+        <v>0.07782532834964484</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03884289760014203</v>
+        <v>0.05894260822305242</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>FEMI.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03190498615277959</v>
+        <v>0.05595045967057666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03100482425131501</v>
+        <v>0.05561946714029209</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>AASU.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02958169923887133</v>
+        <v>0.05111965341457525</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>AASI.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02939998827730417</v>
+        <v>0.04851939599312538</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>AJEUAS.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02905627636885133</v>
+        <v>0.04606145227923086</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02815067400097448</v>
+        <v>0.03987688155602376</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>AUEM.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02771411866627393</v>
+        <v>0.03861278638069221</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Swap UCITS ETF USD Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EJAH.PA</t>
+          <t>EIMI.L</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02649639570522155</v>
+        <v>0.03712689804324532</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF (Acc)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LJPN.AS</t>
+          <t>AEEM.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02624813876759147</v>
+        <v>0.03685405643640727</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Core MSCI Japan UCITS ETF Dist</t>
+          <t>Amundi MSCI Emerging Markets Swap UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JPJY.PA</t>
+          <t>AVEM.L</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02583481677369259</v>
+        <v>0.03665844581780187</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Japan UCITS ETF JPY Unhedged</t>
+          <t>Avantis Emerging Markets Equity UCITS ETF USD Acc</t>
         </is>
       </c>
     </row>
@@ -698,225 +698,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1122608329356276</v>
+        <v>0.1760844127411501</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09880744321567336</v>
+        <v>0.1556182850673165</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09726895190868978</v>
+        <v>0.1515800116536499</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08517691567032348</v>
+        <v>0.122845251635475</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>LAFRI.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08278268875998318</v>
+        <v>0.1148942664372892</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi Pan Africa UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>FEMI.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07672942789204806</v>
+        <v>0.1104413313772317</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LAFRI.MI</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06908581831046701</v>
+        <v>0.1102208647211551</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Pan Africa UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.06771712294834797</v>
+        <v>0.1083852724958341</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0669327502831718</v>
+        <v>0.1059027362579101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06467185981002066</v>
+        <v>0.1034113303804325</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06341903617270228</v>
+        <v>0.09746552703186184</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VMIG.MI</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06033818859352769</v>
+        <v>0.09604786398881915</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05987970399554943</v>
+        <v>0.09239188194023806</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEL.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05874968536524916</v>
+        <v>0.08927839686028283</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DDGT.L</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05812955400261788</v>
+        <v>0.08667957864023101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dimensional Global Targeted Value UCITS ETF USD (Acc)</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5063718866651377</v>
+        <v>0.5288220184142174</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -969,30 +969,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2538272111164737</v>
+        <v>0.2402637370041771</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2501922903180909</v>
+        <v>0.2360885401322736</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2322622958653249</v>
+        <v>0.2207569124856865</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,45 +1014,45 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2216387266796569</v>
+        <v>0.20908153876391</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2003792770343396</v>
+        <v>0.2089241169524481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1946651133937456</v>
+        <v>0.1958516701635105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1867923778253258</v>
+        <v>0.174557565918948</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1074,105 +1074,105 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CS1.PA</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1554226054012631</v>
+        <v>0.1598444640358216</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi IBEX 35 UCITS ETF Acc</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1519924757817048</v>
+        <v>0.1477477343313407</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.143953472228229</v>
+        <v>0.1428762356991036</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1426692168538994</v>
+        <v>0.1400348997152692</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VMIG.MI</t>
+          <t>FEMI.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.140789777210476</v>
+        <v>0.1354950029394473</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
+          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MSEU.L</t>
+          <t>CS1.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1337990752754148</v>
+        <v>0.1354555701581366</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 II UCITS ETF USD Hedged Acc</t>
+          <t>Amundi IBEX 35 UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MSE.PA</t>
+          <t>MSEU.L</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1301577983825961</v>
+        <v>0.1300520676966956</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 II UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 II UCITS ETF USD Hedged Acc</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5094957839828718</v>
+        <v>0.555259935191164</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4930876189401106</v>
+        <v>0.5146630572341266</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1240,45 +1240,45 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4176011915395559</v>
+        <v>0.4486606562578705</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4034597207482646</v>
+        <v>0.4462958541116553</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3977980452501493</v>
+        <v>0.4134568233838893</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3418431115894747</v>
+        <v>0.342220468533196</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3103179896923138</v>
+        <v>0.3258786859809246</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1315,75 +1315,75 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2896825396825398</v>
+        <v>0.2743036849713663</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>FEMI.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2706662314125177</v>
+        <v>0.2733306084239255</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2632277998011205</v>
+        <v>0.2631917962509571</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2557643464381054</v>
+        <v>0.2587008631173005</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2393068823112765</v>
+        <v>0.2543560988886244</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2368076585502492</v>
+        <v>0.2496972315827317</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1405,30 +1405,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2321655505665667</v>
+        <v>0.2485501305593605</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2316613555477156</v>
+        <v>0.2444836244000475</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.598633536910964</v>
+        <v>1.73585172434085</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.581999415054894</v>
+        <v>1.726720615595658</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9130005124604961</v>
+        <v>0.9479321782135588</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8762408791286471</v>
+        <v>0.9084553594933971</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7348218404334936</v>
+        <v>0.7599096234493821</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6518697216025704</v>
+        <v>0.6521167744631031</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1556,120 +1556,120 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6182113605028239</v>
+        <v>0.6507828926273702</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6168112285681293</v>
+        <v>0.6134805069513241</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5823515881870247</v>
+        <v>0.5881809296670328</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5695715156805479</v>
+        <v>0.576535241187017</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5436907327142706</v>
+        <v>0.5723068066051584</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5391076108401867</v>
+        <v>0.5658547492891794</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4996518358131412</v>
+        <v>0.5340218171422775</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4635481989047538</v>
+        <v>0.5035470608219748</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4589945503516841</v>
+        <v>0.4757281253754881</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.774775496468254</v>
+        <v>2.947952288797171</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.404595961581927</v>
+        <v>2.424988322157277</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.979383546923488</v>
+        <v>2.1854440167387</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.943662573600936</v>
+        <v>2.159447171924452</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.49610329726839</v>
+        <v>1.688927871652402</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1797,135 +1797,135 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.40889666749752</v>
+        <v>1.482280613020109</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.406625557977431</v>
+        <v>1.451419349309654</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.383387445449782</v>
+        <v>1.434513959584164</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.360436907522277</v>
+        <v>1.391611089353166</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.289683874222297</v>
+        <v>1.365161054203069</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.285381960032109</v>
+        <v>1.335885552072759</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.280047184780286</v>
+        <v>1.331910632342388</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.263541021666727</v>
+        <v>1.329298545384066</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.252530343552794</v>
+        <v>1.329031707827937</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.175920227140716</v>
+        <v>1.207948404487857</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8876415857273654</v>
+        <v>0.977442332284447</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8758499535111017</v>
+        <v>0.9705159474373986</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5479115236033736</v>
+        <v>0.5651104653191126</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4933592918939638</v>
+        <v>0.5149552120089853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4520170094453393</v>
+        <v>0.4822737833307995</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4440030013624732</v>
+        <v>0.4397814473095776</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4068267194780761</v>
+        <v>0.4122489101510136</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2083,30 +2083,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3804271386565892</v>
+        <v>0.4079641142677264</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>FEMI.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3782350079233008</v>
+        <v>0.3984209058848989</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3573323174129488</v>
+        <v>0.3862117502260329</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2128,75 +2128,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3547644866948412</v>
+        <v>0.3853555018479931</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3135531726195275</v>
+        <v>0.3538788836976754</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2961204757132325</v>
+        <v>0.3230769209271922</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>AASI.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2909344880612472</v>
+        <v>0.298302497910635</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>AJEUAS.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2804453047355906</v>
+        <v>0.2903093220671729</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,225 +442,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1611764945235907</v>
+        <v>0.08711425087068214</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1589649998876053</v>
+        <v>0.04891244694824648</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>AJEUAS.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08198548074758705</v>
+        <v>0.03719027697041355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HYPE.SW</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07782532834964484</v>
+        <v>0.0358547588436875</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21shares Hyperliquid ETP</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05894260822305242</v>
+        <v>0.0272988841042936</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FEMI.MI</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05595045967057666</v>
+        <v>0.02706967344564437</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>SHC.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.05561946714029209</v>
+        <v>0.02474090411688024</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AASU.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05111965341457525</v>
+        <v>0.02311925858897168</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF USD</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AASI.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.04851939599312538</v>
+        <v>0.02291531524264112</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AJEUAS.MI</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.04606145227923086</v>
+        <v>0.02099741819583079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03987688155602376</v>
+        <v>0.01929477352911269</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AUEM.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03861278638069221</v>
+        <v>0.01421083532567535</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Swap UCITS ETF USD Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EIMI.L</t>
+          <t>TELE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.03712689804324532</v>
+        <v>0.01380627775530496</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF (Acc)</t>
+          <t>Amundi STOXX Europe 600 Telecommunications UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AEEM.PA</t>
+          <t>BSX.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.03685405643640727</v>
+        <v>0.01326053668804517</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Swap UCITS ETF EUR Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AVEM.L</t>
+          <t>BERMIB.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.03665844581780187</v>
+        <v>0.01322519551512502</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avantis Emerging Markets Equity UCITS ETF USD Acc</t>
+          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1760844127411501</v>
+        <v>0.1494230478916054</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -713,90 +713,90 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1556182850673165</v>
+        <v>0.1030315013716887</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1515800116536499</v>
+        <v>0.09339233086749599</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>LAFRI.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.122845251635475</v>
+        <v>0.08982901912689067</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi Pan Africa UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LAFRI.MI</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1148942664372892</v>
+        <v>0.08732971287123448</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi Pan Africa UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FEMI.MI</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1104413313772317</v>
+        <v>0.08591385622471748</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1102208647211551</v>
+        <v>0.08416764913618779</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1083852724958341</v>
+        <v>0.07827828189752251</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -818,105 +818,105 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1059027362579101</v>
+        <v>0.07516778523489931</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1034113303804325</v>
+        <v>0.07509226183040019</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.09746552703186184</v>
+        <v>0.07377249894741778</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.09604786398881915</v>
+        <v>0.07083267883622968</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>AJEUAS.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.09239188194023806</v>
+        <v>0.06766596800131297</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.08927839686028283</v>
+        <v>0.06729568625865801</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.08667957864023101</v>
+        <v>0.06503650993931065</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5288220184142174</v>
+        <v>0.522240566008092</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2402637370041771</v>
+        <v>0.2327021718188063</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2360885401322736</v>
+        <v>0.2114579256067564</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -999,60 +999,60 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2207569124856865</v>
+        <v>0.2114345551897381</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.20908153876391</v>
+        <v>0.2064632526608143</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2089241169524481</v>
+        <v>0.2051705725901642</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1958516701635105</v>
+        <v>0.198268565638406</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.174557565918948</v>
+        <v>0.1622473876949682</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1074,105 +1074,105 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>CS1.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1598444640358216</v>
+        <v>0.1402694903638744</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi IBEX 35 UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1477477343313407</v>
+        <v>0.1305507560263215</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1428762356991036</v>
+        <v>0.1289799337178759</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1400348997152692</v>
+        <v>0.1238927263669369</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FEMI.MI</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1354950029394473</v>
+        <v>0.1222903811009777</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CS1.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1354555701581366</v>
+        <v>0.1200488635486376</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi IBEX 35 UCITS ETF Acc</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MSEU.L</t>
+          <t>VMIG.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1300520676966956</v>
+        <v>0.1152940833050271</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 II UCITS ETF USD Hedged Acc</t>
+          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.555259935191164</v>
+        <v>0.5039062774869523</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5146630572341266</v>
+        <v>0.4536804714606939</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1240,45 +1240,45 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4486606562578705</v>
+        <v>0.3638548225803673</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4462958541116553</v>
+        <v>0.3314654769841094</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4134568233838893</v>
+        <v>0.3307759213308432</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.342220468533196</v>
+        <v>0.3125907484133914</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3258786859809246</v>
+        <v>0.2852112730211502</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1315,90 +1315,90 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2743036849713663</v>
+        <v>0.2845510698938183</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FEMI.MI</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2733306084239255</v>
+        <v>0.2621613836988907</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2631917962509571</v>
+        <v>0.2619553870944857</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2587008631173005</v>
+        <v>0.2350933092505718</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2543560988886244</v>
+        <v>0.2282592398969665</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>FEMI.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2496972315827317</v>
+        <v>0.2227921688700361</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2485501305593605</v>
+        <v>0.2197121247559453</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1420,15 +1420,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2444836244000475</v>
+        <v>0.2189885401384266</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.73585172434085</v>
+        <v>1.505354368245337</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.726720615595658</v>
+        <v>1.49405785934008</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9479321782135588</v>
+        <v>0.8894521346271822</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9084553594933971</v>
+        <v>0.8394648770760855</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7599096234493821</v>
+        <v>0.7281794096732537</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6521167744631031</v>
+        <v>0.6549089216474502</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6507828926273702</v>
+        <v>0.6225448546183345</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1571,120 +1571,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6134805069513241</v>
+        <v>0.5900973949524428</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5881809296670328</v>
+        <v>0.5803953146943779</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.576535241187017</v>
+        <v>0.544378489369195</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5723068066051584</v>
+        <v>0.5428413439620388</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5658547492891794</v>
+        <v>0.519739787982515</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5340218171422775</v>
+        <v>0.4991275882808379</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5035470608219748</v>
+        <v>0.4974803136897197</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4757281253754881</v>
+        <v>0.4898111557979266</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.947952288797171</v>
+        <v>2.864199623286128</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.424988322157277</v>
+        <v>2.391538587274995</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.1854440167387</v>
+        <v>1.894568318929839</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.159447171924452</v>
+        <v>1.869751144330671</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.688927871652402</v>
+        <v>1.621792419600061</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.482280613020109</v>
+        <v>1.437596340946956</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.451419349309654</v>
+        <v>1.435500849900162</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.434513959584164</v>
+        <v>1.379324498517759</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.391611089353166</v>
+        <v>1.366656515807983</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.365161054203069</v>
+        <v>1.35264497496582</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1872,60 +1872,60 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.335885552072759</v>
+        <v>1.292361421415301</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.331910632342388</v>
+        <v>1.288412530978594</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.329298545384066</v>
+        <v>1.287933566701074</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.329031707827937</v>
+        <v>1.266816114957912</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.207948404487857</v>
+        <v>1.187832256879301</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.977442332284447</v>
+        <v>0.7968741241296204</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9705159474373986</v>
+        <v>0.7898354007406492</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5651104653191126</v>
+        <v>0.501501457718357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5149552120089853</v>
+        <v>0.4965986541668495</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4822737833307995</v>
+        <v>0.4517114372827418</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2053,105 +2053,105 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4397814473095776</v>
+        <v>0.4447492838019529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4122489101510136</v>
+        <v>0.4092376298709264</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4079641142677264</v>
+        <v>0.4069467059673288</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FEMI.MI</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3984209058848989</v>
+        <v>0.37796676159493</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3862117502260329</v>
+        <v>0.347112016938085</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>FEMI.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3853555018479931</v>
+        <v>0.3392043335563546</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3538788836976754</v>
+        <v>0.3262701844361782</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3230769209271922</v>
+        <v>0.3210622576776374</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2173,30 +2173,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AASI.PA</t>
+          <t>AJEUAS.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.298302497910635</v>
+        <v>0.2903093220671729</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AJEUAS.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2903093220671729</v>
+        <v>0.2736027921182518</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,60 +442,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HYPE.SW</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.08711425087068214</v>
+        <v>0.05565488477999514</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21shares Hyperliquid ETP</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04891244694824648</v>
+        <v>0.0426922765774882</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AJEUAS.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03719027697041355</v>
+        <v>0.04229693437749549</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0358547588436875</v>
+        <v>0.04177780151367183</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0272988841042936</v>
+        <v>0.04088946887731182</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -517,150 +517,150 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02706967344564437</v>
+        <v>0.03470083383413458</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SHC.PA</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02474090411688024</v>
+        <v>0.0253329858860436</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>ESIH.L</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02311925858897168</v>
+        <v>0.02176735242602912</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02291531524264112</v>
+        <v>0.02086571621552746</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>BERMIB.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02099741819583079</v>
+        <v>0.02069817993288603</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>HLT.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.01929477352911269</v>
+        <v>0.01975925376093612</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SHC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.01421083532567535</v>
+        <v>0.01974043390752622</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TELE.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01380627775530496</v>
+        <v>0.01839682838756307</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Telecommunications UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BSX.PA</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01326053668804517</v>
+        <v>0.01700153756033673</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BERMIB.MI</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01322519551512502</v>
+        <v>0.01537056468681386</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
@@ -698,225 +698,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1494230478916054</v>
+        <v>0.1973810355270329</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1030315013716887</v>
+        <v>0.1741871951248846</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09339233086749599</v>
+        <v>0.1183406589268905</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LAFRI.MI</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08982901912689067</v>
+        <v>0.1167672347989392</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi Pan Africa UCITS ETF Acc</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08732971287123448</v>
+        <v>0.1153785216858068</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>LAFRI.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08591385622471748</v>
+        <v>0.1122419740840093</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi Pan Africa UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.08416764913618779</v>
+        <v>0.09770568295121884</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.07827828189752251</v>
+        <v>0.08042138131876397</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>MATW.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07516778523489931</v>
+        <v>0.0769968887664767</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.07509226183040019</v>
+        <v>0.07641743142151802</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.07377249894741778</v>
+        <v>0.07178223537318074</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.07083267883622968</v>
+        <v>0.07132741202295345</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AJEUAS.MI</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06766596800131297</v>
+        <v>0.07040100018396012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>USRI.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.06729568625865801</v>
+        <v>0.06995125483191211</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI USA SRI Climate Paris Aligned UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06503650993931065</v>
+        <v>0.06784125628684334</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.522240566008092</v>
+        <v>0.5894011259117899</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -969,75 +969,75 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2327021718188063</v>
+        <v>0.2561494002487268</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2114579256067564</v>
+        <v>0.189050637428736</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2114345551897381</v>
+        <v>0.1779748602956768</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2064632526608143</v>
+        <v>0.155216460653123</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2051705725901642</v>
+        <v>0.1547633775225088</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.198268565638406</v>
+        <v>0.1444626050922235</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1059,105 +1059,105 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1622473876949682</v>
+        <v>0.1381184915115639</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CS1.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1402694903638744</v>
+        <v>0.1263705080250206</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi IBEX 35 UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1305507560263215</v>
+        <v>0.123338557847392</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1289799337178759</v>
+        <v>0.1209696207720627</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1238927263669369</v>
+        <v>0.1111994662558287</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>CS1.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1222903811009777</v>
+        <v>0.1079214360401475</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi IBEX 35 UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>WELE.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1200488635486376</v>
+        <v>0.1035819868974404</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi S&amp;P 500 Equal Weight ESG UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1152940833050271</v>
+        <v>0.1019088589050583</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5039062774869523</v>
+        <v>0.5742179565280288</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4536804714606939</v>
+        <v>0.4247500087924783</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1240,15 +1240,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3638548225803673</v>
+        <v>0.3137644102497406</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3314654769841094</v>
+        <v>0.3127842085110215</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1270,15 +1270,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3307759213308432</v>
+        <v>0.3104818933535998</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3125907484133914</v>
+        <v>0.2755122289332206</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,30 +1300,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2852112730211502</v>
+        <v>0.2681751587547088</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2845510698938183</v>
+        <v>0.2578928980516964</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2621613836988907</v>
+        <v>0.2355402280083685</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1345,75 +1345,75 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2619553870944857</v>
+        <v>0.2172836306088555</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2350933092505718</v>
+        <v>0.2171421396508308</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2282592398969665</v>
+        <v>0.2115056992008881</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FEMI.MI</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2227921688700361</v>
+        <v>0.2083932109574682</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2197121247559453</v>
+        <v>0.2039939184702022</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2189885401384266</v>
+        <v>0.2005038992970403</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.505354368245337</v>
+        <v>1.543485788935556</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.49405785934008</v>
+        <v>1.529793516982871</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8894521346271822</v>
+        <v>0.9605197978329709</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1511,30 +1511,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8394648770760855</v>
+        <v>0.9020802414620199</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7281794096732537</v>
+        <v>0.844963859560192</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6549089216474502</v>
+        <v>0.6831516460662665</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1556,120 +1556,120 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6225448546183345</v>
+        <v>0.6150766128950167</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5900973949524428</v>
+        <v>0.5825059884610955</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5803953146943779</v>
+        <v>0.5721765622801047</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.544378489369195</v>
+        <v>0.5542873234790244</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5428413439620388</v>
+        <v>0.5469240590632123</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.519739787982515</v>
+        <v>0.5331434657533531</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4991275882808379</v>
+        <v>0.5241535677703599</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4974803136897197</v>
+        <v>0.5219681517604167</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4898111557979266</v>
+        <v>0.4941989105729507</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.864199623286128</v>
+        <v>2.813811707741414</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.391538587274995</v>
+        <v>2.335224702368454</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.894568318929839</v>
+        <v>1.902182003389668</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.869751144330671</v>
+        <v>1.874019119699298</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.621792419600061</v>
+        <v>1.656766153164181</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1797,45 +1797,45 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.437596340946956</v>
+        <v>1.454283297667434</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.435500849900162</v>
+        <v>1.421802817762383</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.379324498517759</v>
+        <v>1.406667717680077</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.366656515807983</v>
+        <v>1.401189756280351</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1857,60 +1857,60 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.35264497496582</v>
+        <v>1.361053848443244</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.292361421415301</v>
+        <v>1.341339862155826</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.288412530978594</v>
+        <v>1.280946832540878</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.287933566701074</v>
+        <v>1.273864105256824</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.266816114957912</v>
+        <v>1.265175146845153</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.187832256879301</v>
+        <v>1.174153270366521</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7968741241296204</v>
+        <v>0.8016005050913986</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7898354007406492</v>
+        <v>0.7924972947586544</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2008,90 +2008,90 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.501501457718357</v>
+        <v>0.6192636657796187</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4965986541668495</v>
+        <v>0.4976794706704151</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4517114372827418</v>
+        <v>0.4472317340450114</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4447492838019529</v>
+        <v>0.420558505333414</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4092376298709264</v>
+        <v>0.412744399437029</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4069467059673288</v>
+        <v>0.3908616261447051</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.37796676159493</v>
+        <v>0.3726532280676862</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.347112016938085</v>
+        <v>0.3625547120113191</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2128,75 +2128,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FEMI.MI</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3392043335563546</v>
+        <v>0.3318110326596713</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fidelity Emerging Markets Quality Income UCITS ETF ACC-USD</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3262701844361782</v>
+        <v>0.3302197670910669</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3210622576776374</v>
+        <v>0.2921866597782714</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AJEUAS.MI</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2903093220671729</v>
+        <v>0.2766827079583207</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2736027921182518</v>
+        <v>0.2719555570713654</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,15 +442,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05565488477999514</v>
+        <v>0.2581475358723864</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0426922765774882</v>
+        <v>0.07536510596552981</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -472,195 +472,195 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04229693437749549</v>
+        <v>0.056599998474121</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HYPE.SW</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04177780151367183</v>
+        <v>0.05264965442020797</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21shares Hyperliquid ETP</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04088946887731182</v>
+        <v>0.04182647500493486</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03470083383413458</v>
+        <v>0.04017209664674715</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0253329858860436</v>
+        <v>0.03660441854596352</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ESIH.L</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02176735242602912</v>
+        <v>0.03561139396046875</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02086571621552746</v>
+        <v>0.02738279369944707</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BERMIB.MI</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02069817993288603</v>
+        <v>0.02718773977865774</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HLT.PA</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.01975925376093612</v>
+        <v>0.02598415188691949</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SHC.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.01974043390752622</v>
+        <v>0.02545705979057433</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01839682838756307</v>
+        <v>0.02423436298965287</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>MATW.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01700153756033673</v>
+        <v>0.02358242338959937</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01537056468681386</v>
+        <v>0.02273169504277339</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1973810355270329</v>
+        <v>0.2220134219168899</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -713,60 +713,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1741871951248846</v>
+        <v>0.1721933418979864</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1183406589268905</v>
+        <v>0.123970013908643</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1167672347989392</v>
+        <v>0.1144394097941881</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1153785216858068</v>
+        <v>0.1097628667215189</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1122419740840093</v>
+        <v>0.09997168779383858</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -788,15 +788,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.09770568295121884</v>
+        <v>0.09501567591091042</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.08042138131876397</v>
+        <v>0.08078720864182087</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -818,105 +818,105 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MATW.PA</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0769968887664767</v>
+        <v>0.07928739422056319</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>MATW.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.07641743142151802</v>
+        <v>0.07789386416242938</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.07178223537318074</v>
+        <v>0.07608688906261607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>USRI.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.07132741202295345</v>
+        <v>0.07105954339156084</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI USA SRI Climate Paris Aligned UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>USRIH.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07040100018396012</v>
+        <v>0.06924853021698874</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>Amundi MSCI USA SRI Climate Paris Aligned UCITS ETF Acc EUR Hedged</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>USRI.AS</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.06995125483191211</v>
+        <v>0.05774271958299892</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA SRI Climate Paris Aligned UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>EKLD.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06784125628684334</v>
+        <v>0.05725337837650235</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>BNP Paribas Easy MSCI USA SRI S-Series PAB 5% Capped UCITS ETF USD Acc</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5894011259117899</v>
+        <v>0.5961145279024342</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2561494002487268</v>
+        <v>0.2383966824829959</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -984,30 +984,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.189050637428736</v>
+        <v>0.1858135982522295</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1779748602956768</v>
+        <v>0.1679127799395017</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.155216460653123</v>
+        <v>0.1606392429123187</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1547633775225088</v>
+        <v>0.1542678056788702</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1444626050922235</v>
+        <v>0.1430903874537812</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1381184915115639</v>
+        <v>0.1407481396812145</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1074,30 +1074,30 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1263705080250206</v>
+        <v>0.1278163426286734</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.123338557847392</v>
+        <v>0.1275546644259866</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1209696207720627</v>
+        <v>0.1241239653783723</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1119,15 +1119,15 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>USRI.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1111994662558287</v>
+        <v>0.1125248175059552</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>Amundi MSCI USA SRI Climate Paris Aligned UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1079214360401475</v>
+        <v>0.110821706256266</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1149,30 +1149,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WELE.MI</t>
+          <t>USRIH.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1035819868974404</v>
+        <v>0.1096580630710662</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P 500 Equal Weight ESG UCITS ETF Acc</t>
+          <t>Amundi MSCI USA SRI Climate Paris Aligned UCITS ETF Acc EUR Hedged</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VMIG.MI</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1019088589050583</v>
+        <v>0.1014031763287988</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5742179565280288</v>
+        <v>0.6530763445439638</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4247500087924783</v>
+        <v>0.429990781190037</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1240,60 +1240,60 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3137644102497406</v>
+        <v>0.3464775136942495</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3127842085110215</v>
+        <v>0.3275152596536191</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3104818933535998</v>
+        <v>0.322923450103296</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2755122289332206</v>
+        <v>0.2640974320153184</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2681751587547088</v>
+        <v>0.2575291541028886</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1315,45 +1315,45 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2578928980516964</v>
+        <v>0.2549776295369475</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2355402280083685</v>
+        <v>0.2383693875740109</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2172836306088555</v>
+        <v>0.2292543168972596</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2171421396508308</v>
+        <v>0.2222093030952219</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1375,15 +1375,15 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2115056992008881</v>
+        <v>0.2173131178635881</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2083932109574682</v>
+        <v>0.207792173854815</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1405,30 +1405,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2039939184702022</v>
+        <v>0.2059128201226856</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2005038992970403</v>
+        <v>0.2011676391667294</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.543485788935556</v>
+        <v>1.613343116430664</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.529793516982871</v>
+        <v>1.606346069757474</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1496,30 +1496,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9605197978329709</v>
+        <v>1.066728414122183</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9020802414620199</v>
+        <v>0.9815120054022861</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.844963859560192</v>
+        <v>0.8822921991868085</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6831516460662665</v>
+        <v>0.6925078062340215</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6150766128950167</v>
+        <v>0.60958291736723</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5825059884610955</v>
+        <v>0.5993120818511337</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5721765622801047</v>
+        <v>0.571587737260363</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5542873234790244</v>
+        <v>0.5526818885050289</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1616,60 +1616,60 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5469240590632123</v>
+        <v>0.5458422129118665</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5331434657533531</v>
+        <v>0.5436018440700805</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5241535677703599</v>
+        <v>0.5433594600164566</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5219681517604167</v>
+        <v>0.5424363579663969</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4941989105729507</v>
+        <v>0.5092204803783309</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.813811707741414</v>
+        <v>2.756934078762449</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.335224702368454</v>
+        <v>2.317599529066231</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.902182003389668</v>
+        <v>1.959210119616843</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.874019119699298</v>
+        <v>1.942343446152457</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.656766153164181</v>
+        <v>1.790785255928031</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.454283297667434</v>
+        <v>1.461349185745563</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1812,60 +1812,60 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.421802817762383</v>
+        <v>1.40637697609529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.406667717680077</v>
+        <v>1.395949351636669</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.401189756280351</v>
+        <v>1.386569332092781</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.361053848443244</v>
+        <v>1.377903895008617</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.341339862155826</v>
+        <v>1.289420414825439</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.280946832540878</v>
+        <v>1.257945525573907</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.273864105256824</v>
+        <v>1.244670025794711</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.265175146845153</v>
+        <v>1.219484907993713</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.174153270366521</v>
+        <v>1.152017341412752</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8016005050913986</v>
+        <v>0.8383371517867182</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7924972947586544</v>
+        <v>0.8362533438687014</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6192636657796187</v>
+        <v>0.6855631353838618</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4976794706704151</v>
+        <v>0.4930384120112452</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4472317340450114</v>
+        <v>0.454711730558641</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.420558505333414</v>
+        <v>0.4405068739751525</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.412744399437029</v>
+        <v>0.421149091234684</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3908616261447051</v>
+        <v>0.3906133440136015</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3726532280676862</v>
+        <v>0.3822175039609748</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3625547120113191</v>
+        <v>0.3721212800477074</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3318110326596713</v>
+        <v>0.3390308908629422</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3302197670910669</v>
+        <v>0.3375458025683113</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2921866597782714</v>
+        <v>0.2837764219009569</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2173,15 +2173,15 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2766827079583207</v>
+        <v>0.2758931843387271</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2719555570713654</v>
+        <v>0.2723176024038043</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2581475358723864</v>
+        <v>0.3814317437595351</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07536510596552981</v>
+        <v>0.1230657753937683</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.056599998474121</v>
+        <v>0.08599305673159985</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -487,180 +487,180 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05264965442020797</v>
+        <v>0.08027562288815759</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04182647500493486</v>
+        <v>0.06762327878692731</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04017209664674715</v>
+        <v>0.05466533216348624</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03660441854596352</v>
+        <v>0.05316195888350328</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03561139396046875</v>
+        <v>0.04997126129574259</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>MATW.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02738279369944707</v>
+        <v>0.04493656003430369</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>ESIH.L</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02718773977865774</v>
+        <v>0.04466057884637786</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>HLT.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02598415188691949</v>
+        <v>0.04277366196754873</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02545705979057433</v>
+        <v>0.03917995671864238</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>LAFRI.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02423436298965287</v>
+        <v>0.03890343885503311</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi Pan Africa UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MATW.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02358242338959937</v>
+        <v>0.03519213154954071</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02273169504277339</v>
+        <v>0.03499995369996367</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -698,30 +698,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2220134219168899</v>
+        <v>0.3135503553446215</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HYPE.SW</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1721933418979864</v>
+        <v>0.2126795799395107</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>21shares Hyperliquid ETP</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.123970013908643</v>
+        <v>0.138319094405136</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1144394097941881</v>
+        <v>0.1234489756174264</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -758,30 +758,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>LAFRI.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1097628667215189</v>
+        <v>0.1106769330738913</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi Pan Africa UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LAFRI.MI</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.09997168779383858</v>
+        <v>0.1073467411181941</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Pan Africa UCITS ETF Acc</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.09501567591091042</v>
+        <v>0.1022623452866738</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -803,60 +803,60 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.08078720864182087</v>
+        <v>0.09367466746007458</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>MATW.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07928739422056319</v>
+        <v>0.07932054913068431</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MATW.PA</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.07789386416242938</v>
+        <v>0.07333075859677574</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>USRIH.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.07608688906261607</v>
+        <v>0.06712957546217213</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI USA SRI Climate Paris Aligned UCITS ETF Acc EUR Hedged</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.07105954339156084</v>
+        <v>0.06704076836518702</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -878,30 +878,30 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>USRIH.MI</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06924853021698874</v>
+        <v>0.05556917574341469</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA SRI Climate Paris Aligned UCITS ETF Acc EUR Hedged</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05774271958299892</v>
+        <v>0.05536969525616731</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05725337837650235</v>
+        <v>0.05434217790591611</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5961145279024342</v>
+        <v>0.5600641900574379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2383966824829959</v>
+        <v>0.2424700597391176</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -984,30 +984,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1858135982522295</v>
+        <v>0.1906205447124716</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1679127799395017</v>
+        <v>0.1864336057849663</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1606392429123187</v>
+        <v>0.1603190288877461</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1542678056788702</v>
+        <v>0.144153339032548</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1044,15 +1044,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1430903874537812</v>
+        <v>0.1383735642921675</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1407481396812145</v>
+        <v>0.1308811249671549</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1074,90 +1074,90 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1278163426286734</v>
+        <v>0.1307400319939591</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1275546644259866</v>
+        <v>0.1286231753300273</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1241239653783723</v>
+        <v>0.1218246399410394</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>USRI.AS</t>
+          <t>CS1.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1125248175059552</v>
+        <v>0.1198870972131694</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA SRI Climate Paris Aligned UCITS ETF Acc</t>
+          <t>Amundi IBEX 35 UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CS1.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.110821706256266</v>
+        <v>0.1165709256799239</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi IBEX 35 UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>USRIH.MI</t>
+          <t>LAFRI.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1096580630710662</v>
+        <v>0.1032857869006556</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA SRI Climate Paris Aligned UCITS ETF Acc EUR Hedged</t>
+          <t>Amundi Pan Africa UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1014031763287988</v>
+        <v>0.100026298214523</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6530763445439638</v>
+        <v>0.6699279848207773</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.429990781190037</v>
+        <v>0.4284599585377862</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3464775136942495</v>
+        <v>0.3085181258218068</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3275152596536191</v>
+        <v>0.2834424265991378</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.322923450103296</v>
+        <v>0.2778272778833264</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1285,60 +1285,60 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2640974320153184</v>
+        <v>0.2686149759776515</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2575291541028886</v>
+        <v>0.2611690887178242</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2549776295369475</v>
+        <v>0.2596194292556255</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2383693875740109</v>
+        <v>0.2519223234363215</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2292543168972596</v>
+        <v>0.2289233008197331</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1360,75 +1360,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2222093030952219</v>
+        <v>0.2277136714130423</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2173131178635881</v>
+        <v>0.2249483909342991</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.207792173854815</v>
+        <v>0.2114300333986421</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2059128201226856</v>
+        <v>0.21009149358391</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2011676391667294</v>
+        <v>0.2027234891405647</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.613343116430664</v>
+        <v>1.628285400709746</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.606346069757474</v>
+        <v>1.622877085438991</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1496,30 +1496,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.066728414122183</v>
+        <v>1.058089940848404</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9815120054022861</v>
+        <v>1.001546279625658</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8822921991868085</v>
+        <v>0.8941926032638408</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6925078062340215</v>
+        <v>0.7296921889360188</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1556,30 +1556,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.60958291736723</v>
+        <v>0.6227257747891981</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5993120818511337</v>
+        <v>0.6193579866594046</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.571587737260363</v>
+        <v>0.5838417069193982</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5526818885050289</v>
+        <v>0.5751142602500305</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5458422129118665</v>
+        <v>0.5619306375794337</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1631,60 +1631,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5436018440700805</v>
+        <v>0.5605012405579566</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5433594600164566</v>
+        <v>0.5355665666281619</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5424363579663969</v>
+        <v>0.5288084693336368</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5092204803783309</v>
+        <v>0.5129396516295859</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.756934078762449</v>
+        <v>2.710564201044157</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.317599529066231</v>
+        <v>2.334032689153755</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.959210119616843</v>
+        <v>1.953333206846265</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.942343446152457</v>
+        <v>1.941286000857047</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.790785255928031</v>
+        <v>1.850656228731355</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.461349185745563</v>
+        <v>1.514434552591008</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1812,45 +1812,45 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.40637697609529</v>
+        <v>1.418319772955306</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.395949351636669</v>
+        <v>1.412584169080641</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.386569332092781</v>
+        <v>1.394376803908405</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.377903895008617</v>
+        <v>1.329735728601863</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.289420414825439</v>
+        <v>1.294467382405348</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.257945525573907</v>
+        <v>1.251457364487601</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.244670025794711</v>
+        <v>1.233782302622738</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.219484907993713</v>
+        <v>1.182791202652576</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.152017341412752</v>
+        <v>1.138653090441551</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1978,30 +1978,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8383371517867182</v>
+        <v>0.8500621650181355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8362533438687014</v>
+        <v>0.8497233437916012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6855631353838618</v>
+        <v>0.6771407110923831</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4930384120112452</v>
+        <v>0.5004094056289434</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2038,45 +2038,45 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.454711730558641</v>
+        <v>0.4446821116820203</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4405068739751525</v>
+        <v>0.4359954786834552</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.421149091234684</v>
+        <v>0.4290073121147477</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3906133440136015</v>
+        <v>0.3923516031153771</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2098,105 +2098,105 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3822175039609748</v>
+        <v>0.3849505169442025</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3721212800477074</v>
+        <v>0.3613177461800665</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3390308908629422</v>
+        <v>0.35622720002191</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3375458025683113</v>
+        <v>0.3529669170855758</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2837764219009569</v>
+        <v>0.305075662917845</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2758931843387271</v>
+        <v>0.2999584764207197</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2723176024038043</v>
+        <v>0.2915723775667971</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3814317437595351</v>
+        <v>0.3377982377982378</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1230657753937683</v>
+        <v>0.07712050983715413</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -472,30 +472,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08599305673159985</v>
+        <v>0.07477580990197574</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08027562288815759</v>
+        <v>0.05618622007123952</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.06762327878692731</v>
+        <v>0.05614376691431788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -517,150 +517,150 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05466533216348624</v>
+        <v>0.0516091241714316</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>MATW.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.05316195888350328</v>
+        <v>0.04820831109107382</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04997126129574259</v>
+        <v>0.04744824614989152</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MATW.PA</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.04493656003430369</v>
+        <v>0.03922959085685185</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ESIH.L</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.04466057884637786</v>
+        <v>0.03769166295296889</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HLT.PA</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04277366196754873</v>
+        <v>0.03668205858924978</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>LAFRI.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03917995671864238</v>
+        <v>0.03196878591189445</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>Amundi Pan Africa UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LAFRI.MI</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.03890343885503311</v>
+        <v>0.03056449809697659</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Pan Africa UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>DSP5.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.03519213154954071</v>
+        <v>0.02981297072587097</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.03499995369996367</v>
+        <v>0.02822792404318264</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3135503553446215</v>
+        <v>0.3490923750096917</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2126795799395107</v>
+        <v>0.1948134683728551</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.138319094405136</v>
+        <v>0.1730058891854389</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -743,45 +743,45 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1234489756174264</v>
+        <v>0.1467855565635046</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LAFRI.MI</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1106769330738913</v>
+        <v>0.1383113666351024</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi Pan Africa UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>LAFRI.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1073467411181941</v>
+        <v>0.1192389315809561</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi Pan Africa UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1022623452866738</v>
+        <v>0.106973939673644</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -803,15 +803,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.09367466746007458</v>
+        <v>0.09801470312725469</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07932054913068431</v>
+        <v>0.0906652537210535</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.07333075859677574</v>
+        <v>0.08007776910987618</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -848,75 +848,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>USRIH.MI</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06712957546217213</v>
+        <v>0.06382729148271937</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA SRI Climate Paris Aligned UCITS ETF Acc EUR Hedged</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>USRI.AS</t>
+          <t>USRIH.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06704076836518702</v>
+        <v>0.06321174292042531</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA SRI Climate Paris Aligned UCITS ETF Acc</t>
+          <t>Amundi MSCI USA SRI Climate Paris Aligned UCITS ETF Acc EUR Hedged</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>USRI.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05556917574341469</v>
+        <v>0.06284748719066835</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>Amundi MSCI USA SRI Climate Paris Aligned UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05536969525616731</v>
+        <v>0.05596825809194295</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EKLD.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05434217790591611</v>
+        <v>0.05535378702831695</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI USA SRI S-Series PAB 5% Capped UCITS ETF USD Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5600641900574379</v>
+        <v>0.4894540313184166</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2424700597391176</v>
+        <v>0.2220026051645252</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -984,30 +984,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1906205447124716</v>
+        <v>0.1594123707016089</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1864336057849663</v>
+        <v>0.1554424783882977</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1603190288877461</v>
+        <v>0.1380682135352205</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1029,150 +1029,150 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.144153339032548</v>
+        <v>0.1159339898105667</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1383735642921675</v>
+        <v>0.1147747520535063</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1308811249671549</v>
+        <v>0.1132779758150568</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1307400319939591</v>
+        <v>0.1046283428368164</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>CS1.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1286231753300273</v>
+        <v>0.10202343920649</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi IBEX 35 UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1218246399410394</v>
+        <v>0.09851086109381213</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CS1.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1198870972131694</v>
+        <v>0.09692493182812489</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi IBEX 35 UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1165709256799239</v>
+        <v>0.09591163431971905</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LAFRI.MI</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1032857869006556</v>
+        <v>0.09357867282594379</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Pan Africa UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>DDGT.L</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.100026298214523</v>
+        <v>0.0867184729784074</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>Dimensional Global Targeted Value UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6699279848207773</v>
+        <v>0.6659685040413144</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4284599585377862</v>
+        <v>0.4244983517144738</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3085181258218068</v>
+        <v>0.2906654848861125</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1255,45 +1255,45 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2834424265991378</v>
+        <v>0.2892839575574451</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2778272778833264</v>
+        <v>0.2743690256216482</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2686149759776515</v>
+        <v>0.2697462892059648</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2611690887178242</v>
+        <v>0.2552188594291247</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1315,60 +1315,60 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2596194292556255</v>
+        <v>0.2528237148216952</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2519223234363215</v>
+        <v>0.2527472507937569</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2289233008197331</v>
+        <v>0.2280737454773949</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2277136714130423</v>
+        <v>0.2174616914135159</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2249483909342991</v>
+        <v>0.2027011347272019</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2114300333986421</v>
+        <v>0.200025587336141</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.21009149358391</v>
+        <v>0.1986001620471531</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1420,15 +1420,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2027234891405647</v>
+        <v>0.1952912097375707</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.628285400709746</v>
+        <v>1.486896730787007</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.622877085438991</v>
+        <v>1.468174007821568</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.058089940848404</v>
+        <v>1.051671192192368</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.001546279625658</v>
+        <v>0.871223386039701</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8941926032638408</v>
+        <v>0.8162234897755662</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7296921889360188</v>
+        <v>0.7117169715021778</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1556,30 +1556,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6227257747891981</v>
+        <v>0.6132633245776469</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6193579866594046</v>
+        <v>0.5943284150577224</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5838417069193982</v>
+        <v>0.5619047831973341</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,15 +1601,15 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5751142602500305</v>
+        <v>0.5365337425296761</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5619306375794337</v>
+        <v>0.5247885679887676</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1631,30 +1631,30 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5605012405579566</v>
+        <v>0.5075773361874634</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5355665666281619</v>
+        <v>0.5060914458410193</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5288084693336368</v>
+        <v>0.5024043521469577</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5129396516295859</v>
+        <v>0.4716217714150512</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.710564201044157</v>
+        <v>2.687993622546396</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.334032689153755</v>
+        <v>2.370706057774631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1752,45 +1752,45 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.953333206846265</v>
+        <v>1.878339830685605</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.941286000857047</v>
+        <v>1.818463453567618</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.850656228731355</v>
+        <v>1.78995170397972</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.514434552591008</v>
+        <v>1.564796027663562</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.418319772955306</v>
+        <v>1.44248637270229</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.412584169080641</v>
+        <v>1.432335154261096</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.394376803908405</v>
+        <v>1.410032216706096</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1857,30 +1857,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.329735728601863</v>
+        <v>1.339098025275521</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.294467382405348</v>
+        <v>1.309452364861916</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.251457364487601</v>
+        <v>1.27001636143583</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.233782302622738</v>
+        <v>1.255437487108273</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.182791202652576</v>
+        <v>1.167010356938581</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.138653090441551</v>
+        <v>1.12933493514765</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1978,30 +1978,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8500621650181355</v>
+        <v>0.7991299564634029</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8497233437916012</v>
+        <v>0.7890034874606906</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6771407110923831</v>
+        <v>0.6317893303395723</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5004094056289434</v>
+        <v>0.4731094051603073</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4446821116820203</v>
+        <v>0.4347493258991819</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4359954786834552</v>
+        <v>0.4143720075606141</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4290073121147477</v>
+        <v>0.4064773039392455</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3923516031153771</v>
+        <v>0.38713682581005</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3849505169442025</v>
+        <v>0.363679275421666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2113,30 +2113,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3613177461800665</v>
+        <v>0.3500000209598757</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.35622720002191</v>
+        <v>0.3428976092266218</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3529669170855758</v>
+        <v>0.3323147228435797</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2158,45 +2158,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.305075662917845</v>
+        <v>0.3169568111282877</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2999584764207197</v>
+        <v>0.3128579806072391</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2915723775667971</v>
+        <v>0.3008681489135254</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3377982377982378</v>
+        <v>0.3547579434386727</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -457,45 +457,45 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>HODLV.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07712050983715413</v>
+        <v>0.2654972926297559</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>21shares Crypto Basket Equal Weight ETP</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07477580990197574</v>
+        <v>0.1720057636058743</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05618622007123952</v>
+        <v>0.1087069853597373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05614376691431788</v>
+        <v>0.0972651191715781</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -517,105 +517,105 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0516091241714316</v>
+        <v>0.08858092376862392</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MATW.PA</t>
+          <t>LAFRI.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04820831109107382</v>
+        <v>0.07737307475091404</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
+          <t>Amundi Pan Africa UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04744824614989152</v>
+        <v>0.07584894538730591</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.03922959085685185</v>
+        <v>0.07003971561583056</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03769166295296889</v>
+        <v>0.06543794484902432</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>MATW.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03668205858924978</v>
+        <v>0.06433511988070539</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LAFRI.MI</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03196878591189445</v>
+        <v>0.04221129843570437</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Pan Africa UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.03056449809697659</v>
+        <v>0.03569654489990381</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -637,30 +637,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DSP5.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02981297072587097</v>
+        <v>0.03443325292245758</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02822792404318264</v>
+        <v>0.03392825305590641</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3490923750096917</v>
+        <v>0.3701983264123176</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -713,45 +713,45 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>HODLV.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1948134683728551</v>
+        <v>0.3480473205896957</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>21shares Crypto Basket Equal Weight ETP</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1730058891854389</v>
+        <v>0.2843137084879654</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1467855565635046</v>
+        <v>0.1826071497822996</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1383113666351024</v>
+        <v>0.1661717118163766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1192389315809561</v>
+        <v>0.1422128726143104</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -788,15 +788,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.106973939673644</v>
+        <v>0.1384863104209888</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.09801470312725469</v>
+        <v>0.1270638031058093</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -818,105 +818,105 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MATW.PA</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0906652537210535</v>
+        <v>0.116893084156892</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>MATW.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.08007776910987618</v>
+        <v>0.09388416041707903</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06382729148271937</v>
+        <v>0.09329446064139946</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>USRIH.MI</t>
+          <t>USRI.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06321174292042531</v>
+        <v>0.07025873787088477</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA SRI Climate Paris Aligned UCITS ETF Acc EUR Hedged</t>
+          <t>Amundi MSCI USA SRI Climate Paris Aligned UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>USRI.AS</t>
+          <t>USRIH.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06284748719066835</v>
+        <v>0.06971880281445419</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA SRI Climate Paris Aligned UCITS ETF Acc</t>
+          <t>Amundi MSCI USA SRI Climate Paris Aligned UCITS ETF Acc EUR Hedged</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05596825809194295</v>
+        <v>0.06496303577973617</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05535378702831695</v>
+        <v>0.0649269951154785</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4894540313184166</v>
+        <v>0.5906775999905864</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2220026051645252</v>
+        <v>0.2454965868149788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1594123707016089</v>
+        <v>0.1694510020719451</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1554424783882977</v>
+        <v>0.1584794750887446</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1380682135352205</v>
+        <v>0.145968564866531</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1029,15 +1029,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1159339898105667</v>
+        <v>0.1406833843525119</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1147747520535063</v>
+        <v>0.1385646847549167</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1059,120 +1059,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1132779758150568</v>
+        <v>0.1266062408603206</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1046283428368164</v>
+        <v>0.1265963718861687</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CS1.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.10202343920649</v>
+        <v>0.1172237470384738</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi IBEX 35 UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.09851086109381213</v>
+        <v>0.1145916485202583</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.09692493182812489</v>
+        <v>0.1095024918035223</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>CS1.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.09591163431971905</v>
+        <v>0.1064918740155225</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi IBEX 35 UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.09357867282594379</v>
+        <v>0.09994854122057872</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DDGT.L</t>
+          <t>VMIG.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0867184729784074</v>
+        <v>0.08818310005532015</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dimensional Global Targeted Value UCITS ETF USD (Acc)</t>
+          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6659685040413144</v>
+        <v>0.7317696463769578</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4244983517144738</v>
+        <v>0.4115513398370578</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2906654848861125</v>
+        <v>0.300184991637044</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2892839575574451</v>
+        <v>0.2918690933691694</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2743690256216482</v>
+        <v>0.2788281440734863</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2697462892059648</v>
+        <v>0.2574398063570769</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,30 +1300,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2552188594291247</v>
+        <v>0.2502438120899486</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2528237148216952</v>
+        <v>0.2498139200085319</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2527472507937569</v>
+        <v>0.2486837085800944</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1345,90 +1345,90 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2280737454773949</v>
+        <v>0.2297343933822331</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2174616914135159</v>
+        <v>0.2172491118841926</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2027011347272019</v>
+        <v>0.2143402734611717</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.200025587336141</v>
+        <v>0.2126480910414201</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1986001620471531</v>
+        <v>0.2039727428758031</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1952912097375707</v>
+        <v>0.2022334250082956</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.486896730787007</v>
+        <v>1.581684581579633</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.468174007821568</v>
+        <v>1.56564948553754</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1496,30 +1496,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.051671192192368</v>
+        <v>1.032786775684611</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.871223386039701</v>
+        <v>1.02946781164799</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8162234897755662</v>
+        <v>0.8396623236527481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7117169715021778</v>
+        <v>0.7287684491774791</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1556,45 +1556,45 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6132633245776469</v>
+        <v>0.603805649796018</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5943284150577224</v>
+        <v>0.5888806282417307</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5619047831973341</v>
+        <v>0.5757488067750587</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5365337425296761</v>
+        <v>0.5633031757534828</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1616,45 +1616,45 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5247885679887676</v>
+        <v>0.547688858124399</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5075773361874634</v>
+        <v>0.5470301962852522</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5060914458410193</v>
+        <v>0.5237088925690514</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5024043521469577</v>
+        <v>0.4919017901035105</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4716217714150512</v>
+        <v>0.4632218615516142</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.687993622546396</v>
+        <v>2.7117616128898</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.370706057774631</v>
+        <v>2.364805006503556</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.878339830685605</v>
+        <v>1.915746423602362</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.818463453567618</v>
+        <v>1.911856714354556</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.78995170397972</v>
+        <v>1.885951277989739</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.564796027663562</v>
+        <v>1.58578933662</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1812,30 +1812,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.44248637270229</v>
+        <v>1.429940118392665</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.432335154261096</v>
+        <v>1.4248101859987</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.410032216706096</v>
+        <v>1.419079276718363</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.339098025275521</v>
+        <v>1.355347222340336</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.309452364861916</v>
+        <v>1.313953450104661</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.27001636143583</v>
+        <v>1.297794089001997</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.255437487108273</v>
+        <v>1.261760198140427</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.167010356938581</v>
+        <v>1.181425084362885</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.12933493514765</v>
+        <v>1.137643340748768</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7991299564634029</v>
+        <v>0.8587463453155952</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7890034874606906</v>
+        <v>0.8505613891453976</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6317893303395723</v>
+        <v>0.7540222484883423</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4731094051603073</v>
+        <v>0.4878513923957037</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4347493258991819</v>
+        <v>0.442542756785544</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4143720075606141</v>
+        <v>0.4151886505808924</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4064773039392455</v>
+        <v>0.3977938677645643</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.38713682581005</v>
+        <v>0.3960764981780487</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.363679275421666</v>
+        <v>0.3874372446036438</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2113,15 +2113,15 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3500000209598757</v>
+        <v>0.3548138664934068</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3428976092266218</v>
+        <v>0.3471484360484167</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2143,15 +2143,15 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3323147228435797</v>
+        <v>0.3368131850473364</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3169568111282877</v>
+        <v>0.3277363354725633</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3128579806072391</v>
+        <v>0.32462196847444</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3008681489135254</v>
+        <v>0.3057514994885449</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3547579434386727</v>
+        <v>0.3946244830161756</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -472,120 +472,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1720057636058743</v>
+        <v>0.0792078770585618</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1087069853597373</v>
+        <v>0.07435341423105934</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0972651191715781</v>
+        <v>0.04425157462108142</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>LAFRI.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08858092376862392</v>
+        <v>0.04420678176885384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi Pan Africa UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LAFRI.MI</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.07737307475091404</v>
+        <v>0.04094420878166383</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Pan Africa UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.07584894538730591</v>
+        <v>0.03864138945485518</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07003971561583056</v>
+        <v>0.03779562695225347</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06543794484902432</v>
+        <v>0.03776519185645322</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06433511988070539</v>
+        <v>0.03739977988211862</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -607,60 +607,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04221129843570437</v>
+        <v>0.03666237846627074</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.03569654489990381</v>
+        <v>0.03535650269867308</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.03443325292245758</v>
+        <v>0.03142496351680135</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.03392825305590641</v>
+        <v>0.0285559705440166</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3701983264123176</v>
+        <v>0.4048129773801734</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2843137084879654</v>
+        <v>0.2491996874610298</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1826071497822996</v>
+        <v>0.2147714247606429</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1661717118163766</v>
+        <v>0.1596338359983058</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1422128726143104</v>
+        <v>0.1542955086002564</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -788,135 +788,135 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1384863104209888</v>
+        <v>0.1380059206185666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1270638031058093</v>
+        <v>0.1269891057098445</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.116893084156892</v>
+        <v>0.123439125756424</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MATW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.09388416041707903</v>
+        <v>0.1176823986822442</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.09329446064139946</v>
+        <v>0.1071910328291767</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>USRI.AS</t>
+          <t>MATW.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.07025873787088477</v>
+        <v>0.09994600690687117</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA SRI Climate Paris Aligned UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>USRIH.MI</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06971880281445419</v>
+        <v>0.08130384286168924</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA SRI Climate Paris Aligned UCITS ETF Acc EUR Hedged</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>USRIH.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.06496303577973617</v>
+        <v>0.0729713939130705</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI USA SRI Climate Paris Aligned UCITS ETF Acc EUR Hedged</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>USRI.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0649269951154785</v>
+        <v>0.07248094865652721</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi MSCI USA SRI Climate Paris Aligned UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5906775999905864</v>
+        <v>0.5120107627371264</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2454965868149788</v>
+        <v>0.2295459233502166</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1694510020719451</v>
+        <v>0.1769506036169537</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -999,60 +999,60 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1584794750887446</v>
+        <v>0.1501223378238488</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.145968564866531</v>
+        <v>0.1480351025641049</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1406833843525119</v>
+        <v>0.1331592113176756</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1385646847549167</v>
+        <v>0.131297691655571</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1266062408603206</v>
+        <v>0.1288659778981602</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1074,105 +1074,105 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1265963718861687</v>
+        <v>0.1264338905101199</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1172237470384738</v>
+        <v>0.1209432393850196</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1145916485202583</v>
+        <v>0.1177444635312261</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1095024918035223</v>
+        <v>0.1165722411096866</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CS1.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1064918740155225</v>
+        <v>0.1101328710479559</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi IBEX 35 UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.09994854122057872</v>
+        <v>0.1035466693693801</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VMIG.MI</t>
+          <t>CS1.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.08818310005532015</v>
+        <v>0.09946982908602853</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
+          <t>Amundi IBEX 35 UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7317696463769578</v>
+        <v>0.6459299153971036</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4115513398370578</v>
+        <v>0.3871009028909398</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.300184991637044</v>
+        <v>0.2799454588315604</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1255,45 +1255,45 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2918690933691694</v>
+        <v>0.2450250980243012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2788281440734863</v>
+        <v>0.2313183801239442</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2574398063570769</v>
+        <v>0.2293504674736773</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2502438120899486</v>
+        <v>0.2251391348935359</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1315,15 +1315,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2498139200085319</v>
+        <v>0.2240730526642161</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2486837085800944</v>
+        <v>0.2216317995751829</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2297343933822331</v>
+        <v>0.2111236740165978</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2172491118841926</v>
+        <v>0.2029661944357812</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2143402734611717</v>
+        <v>0.2001825281034215</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2126480910414201</v>
+        <v>0.1928589095565185</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1405,15 +1405,15 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2039727428758031</v>
+        <v>0.1912114155494218</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2022334250082956</v>
+        <v>0.1890442292194028</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.581684581579633</v>
+        <v>1.607748963002647</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.56564948553754</v>
+        <v>1.592915433847538</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1496,30 +1496,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.032786775684611</v>
+        <v>1.020420914632096</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.02946781164799</v>
+        <v>0.9719555172848955</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8396623236527481</v>
+        <v>0.8440723973142932</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7287684491774791</v>
+        <v>0.7360141156877851</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.603805649796018</v>
+        <v>0.6235273490413498</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5888806282417307</v>
+        <v>0.5942377152387117</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1586,45 +1586,45 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5757488067750587</v>
+        <v>0.5716931740390196</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5633031757534828</v>
+        <v>0.5702722526109905</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.547688858124399</v>
+        <v>0.5688713050043384</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5470301962852522</v>
+        <v>0.5670143163867847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1646,15 +1646,15 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5237088925690514</v>
+        <v>0.5514517299884003</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4919017901035105</v>
+        <v>0.4741296580925631</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4632218615516142</v>
+        <v>0.4690607287339306</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.7117616128898</v>
+        <v>2.724965828099015</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.364805006503556</v>
+        <v>2.392623917445996</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1752,45 +1752,45 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.915746423602362</v>
+        <v>1.922121592081842</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.911856714354556</v>
+        <v>1.897886321643814</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.885951277989739</v>
+        <v>1.8929463025975</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.58578933662</v>
+        <v>1.596285683088756</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.429940118392665</v>
+        <v>1.440419114145103</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1827,30 +1827,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.4248101859987</v>
+        <v>1.42636719682446</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.419079276718363</v>
+        <v>1.401065949458481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.355347222340336</v>
+        <v>1.385071556903372</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.313953450104661</v>
+        <v>1.323330794494416</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.297794089001997</v>
+        <v>1.302696099590525</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.261760198140427</v>
+        <v>1.270864917463035</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.137643340748768</v>
+        <v>1.143973576100769</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8587463453155952</v>
+        <v>0.8652987982115936</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8505613891453976</v>
+        <v>0.8582145089788626</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7540222484883423</v>
+        <v>0.6855631353838618</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4878513923957037</v>
+        <v>0.4883974835287459</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.442542756785544</v>
+        <v>0.4530866868935775</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4151886505808924</v>
+        <v>0.4136860722803835</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2068,45 +2068,45 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3977938677645643</v>
+        <v>0.4010428986242556</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3960764981780487</v>
+        <v>0.3923789795308312</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3874372446036438</v>
+        <v>0.3895798336179659</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3548138664934068</v>
+        <v>0.3623694754525333</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3471484360484167</v>
+        <v>0.3467942286318506</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3368131850473364</v>
+        <v>0.3397436551312361</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3277363354725633</v>
+        <v>0.3331259394897621</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.32462196847444</v>
+        <v>0.328241593319808</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,15 +2188,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3057514994885449</v>
+        <v>0.3134003527887481</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3946244830161756</v>
+        <v>0.1538854589695766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2654972926297559</v>
+        <v>0.1114213390466516</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -472,195 +472,195 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0792078770585618</v>
+        <v>0.08132590615418223</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07435341423105934</v>
+        <v>0.07397531810806024</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04425157462108142</v>
+        <v>0.04749337571406498</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LAFRI.MI</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04420678176885384</v>
+        <v>0.04438115194519154</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Pan Africa UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>LAFRI.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04094420878166383</v>
+        <v>0.03882253890814158</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi Pan Africa UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>MDAX.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03864138945485518</v>
+        <v>0.03804974584123233</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Invesco MDAX UCITS ETF A</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.03779562695225347</v>
+        <v>0.03269890069239567</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03776519185645322</v>
+        <v>0.03203546521443701</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MATW.PA</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03739977988211862</v>
+        <v>0.0285132147624565</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03666237846627074</v>
+        <v>0.02783643105211953</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.03535650269867308</v>
+        <v>0.02580646802020325</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.03142496351680135</v>
+        <v>0.02521317743849183</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0285559705440166</v>
+        <v>0.02472777973922846</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4048129773801734</v>
+        <v>0.5597788371913388</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2491996874610298</v>
+        <v>0.3113625471344816</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2147714247606429</v>
+        <v>0.2266412943924965</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1596338359983058</v>
+        <v>0.1881145300711158</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -773,150 +773,150 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LAFRI.MI</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1542955086002564</v>
+        <v>0.1646827029520805</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Pan Africa UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1380059206185666</v>
+        <v>0.1639518852582915</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>LAFRI.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1269891057098445</v>
+        <v>0.1557494578125627</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi Pan Africa UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.123439125756424</v>
+        <v>0.1405933670376271</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1176823986822442</v>
+        <v>0.1396760024586627</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1071910328291767</v>
+        <v>0.1152852978178505</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MATW.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.09994600690687117</v>
+        <v>0.1149461345068818</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08130384286168924</v>
+        <v>0.1130923255725533</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>USRIH.MI</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0729713939130705</v>
+        <v>0.1081427062843385</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA SRI Climate Paris Aligned UCITS ETF Acc EUR Hedged</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>USRI.AS</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.07248094865652721</v>
+        <v>0.1007090138749867</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA SRI Climate Paris Aligned UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5120107627371264</v>
+        <v>0.4737424133952317</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2295459233502166</v>
+        <v>0.2248649618875453</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1769506036169537</v>
+        <v>0.1633908955994461</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -999,60 +999,60 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1501223378238488</v>
+        <v>0.158354357475563</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1480351025641049</v>
+        <v>0.1389500113675588</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1331592113176756</v>
+        <v>0.1328926573918008</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.131297691655571</v>
+        <v>0.1251501906431445</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1288659778981602</v>
+        <v>0.1194690867248049</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1264338905101199</v>
+        <v>0.1167814174993382</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1089,90 +1089,90 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1209432393850196</v>
+        <v>0.1159148274779465</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1177444635312261</v>
+        <v>0.1022571749152863</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1165722411096866</v>
+        <v>0.09705650729101856</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>CS1.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1101328710479559</v>
+        <v>0.09608620608741214</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi IBEX 35 UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>USRI.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1035466693693801</v>
+        <v>0.09290063096715717</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi MSCI USA SRI Climate Paris Aligned UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CS1.PA</t>
+          <t>VMIG.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.09946982908602853</v>
+        <v>0.09227722470122979</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi IBEX 35 UCITS ETF Acc</t>
+          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6459299153971036</v>
+        <v>0.687163841369187</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3871009028909398</v>
+        <v>0.4336215416463525</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1240,15 +1240,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2799454588315604</v>
+        <v>0.2831716137531755</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2450250980243012</v>
+        <v>0.271457478404876</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1270,135 +1270,135 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2313183801239442</v>
+        <v>0.2640234598299225</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2293504674736773</v>
+        <v>0.2614615877342104</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2251391348935359</v>
+        <v>0.2362169692477429</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2240730526642161</v>
+        <v>0.2309468862863393</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2216317995751829</v>
+        <v>0.2159412315299336</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2111236740165978</v>
+        <v>0.2152962034099144</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2029661944357812</v>
+        <v>0.1946569541697476</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2001825281034215</v>
+        <v>0.1858293102062609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>CU2.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1928589095565185</v>
+        <v>0.1813461995754961</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1912114155494218</v>
+        <v>0.1805774501492521</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1420,15 +1420,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1890442292194028</v>
+        <v>0.1790933435986026</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.607748963002647</v>
+        <v>1.623675786564458</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.592915433847538</v>
+        <v>1.610442516299313</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.020420914632096</v>
+        <v>1.02991657339148</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9719555172848955</v>
+        <v>1.015879068086518</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8440723973142932</v>
+        <v>0.8694483345234207</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7360141156877851</v>
+        <v>0.7436530952753904</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6235273490413498</v>
+        <v>0.6363636839506916</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5942377152387117</v>
+        <v>0.5920084010111466</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1586,75 +1586,75 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5716931740390196</v>
+        <v>0.573773653628427</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5702722526109905</v>
+        <v>0.5722737964552151</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5688713050043384</v>
+        <v>0.5572185788059683</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5670143163867847</v>
+        <v>0.5563133696806595</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5514517299884003</v>
+        <v>0.555977245449967</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4741296580925631</v>
+        <v>0.4824766075604201</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1676,15 +1676,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4690607287339306</v>
+        <v>0.4609601229030147</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.724965828099015</v>
+        <v>2.55496111693708</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.392623917445996</v>
+        <v>2.271245121653918</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1752,45 +1752,45 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.922121592081842</v>
+        <v>1.967736216648974</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.897886321643814</v>
+        <v>1.923046145205617</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.8929463025975</v>
+        <v>1.898356620261819</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.596285683088756</v>
+        <v>1.568639204949879</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1812,45 +1812,45 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.440419114145103</v>
+        <v>1.38590980220121</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.42636719682446</v>
+        <v>1.383079332386796</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.401065949458481</v>
+        <v>1.353190582641777</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.385071556903372</v>
+        <v>1.331215302340164</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.323330794494416</v>
+        <v>1.324001531713253</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.302696099590525</v>
+        <v>1.264786094471447</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1902,30 +1902,30 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.270864917463035</v>
+        <v>1.215824832197893</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.181425084362885</v>
+        <v>1.1748741918187</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.143973576100769</v>
+        <v>1.091644845152569</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8652987982115936</v>
+        <v>0.8805521781902661</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8582145089788626</v>
+        <v>0.8720233301282967</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6855631353838618</v>
+        <v>0.7272433693321974</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4883974835287459</v>
+        <v>0.5167895360867956</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4530866868935775</v>
+        <v>0.457823929809573</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2053,45 +2053,45 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4136860722803835</v>
+        <v>0.3990786283558854</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4010428986242556</v>
+        <v>0.3940225942471025</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3923789795308312</v>
+        <v>0.3697541400642768</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3895798336179659</v>
+        <v>0.3693968355828796</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3623694754525333</v>
+        <v>0.3682460744318818</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2128,45 +2128,45 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3467942286318506</v>
+        <v>0.3382784200892863</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3397436551312361</v>
+        <v>0.3362354237488778</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3331259394897621</v>
+        <v>0.3322706266278845</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.328241593319808</v>
+        <v>0.3287845232386295</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3134003527887481</v>
+        <v>0.3027062747485469</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1538854589695766</v>
+        <v>0.0957085613297064</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1114213390466516</v>
+        <v>0.04007257728574376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -472,15 +472,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08132590615418223</v>
+        <v>0.03398051593690221</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07397531810806024</v>
+        <v>0.03396583135886799</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -502,45 +502,45 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04749337571406498</v>
+        <v>0.0331339788661944</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04438115194519154</v>
+        <v>0.03217537250897817</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LAFRI.MI</t>
+          <t>JPXX.L</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03882253890814158</v>
+        <v>0.03090423502479966</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Pan Africa UCITS ETF Acc</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03804974584123233</v>
+        <v>0.02911147554649318</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -562,105 +562,105 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>SRIJC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.03269890069239567</v>
+        <v>0.0283945171224913</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>SRIJ.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03203546521443701</v>
+        <v>0.02805950029226212</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Dis</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0285132147624565</v>
+        <v>0.02766988758587341</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>JPXY.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02783643105211953</v>
+        <v>0.02760837555949602</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR (C)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02580646802020325</v>
+        <v>0.02694540924436306</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>JPXH.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02521317743849183</v>
+        <v>0.0267169141692678</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - EUR Hedged (C)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02472777973922846</v>
+        <v>0.02457688475759778</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5597788371913388</v>
+        <v>0.5586271342994011</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3113625471344816</v>
+        <v>0.2855978786728328</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2266412943924965</v>
+        <v>0.2452467201442243</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -758,15 +758,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1881145300711158</v>
+        <v>0.2428140043712053</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1646827029520805</v>
+        <v>0.2361186965681237</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -788,15 +788,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1639518852582915</v>
+        <v>0.1996515149186262</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1557494578125627</v>
+        <v>0.1518175449023931</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -818,105 +818,105 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1405933670376271</v>
+        <v>0.1473553350313275</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1396760024586627</v>
+        <v>0.1423163443620563</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1152852978178505</v>
+        <v>0.1409322985462322</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1149461345068818</v>
+        <v>0.1386668310970038</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1130923255725533</v>
+        <v>0.1378025945367272</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1081427062843385</v>
+        <v>0.1324530226379099</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>AASU.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1007090138749867</v>
+        <v>0.1188660179910535</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4737424133952317</v>
+        <v>0.4156799356689</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2248649618875453</v>
+        <v>0.1915961891794449</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1633908955994461</v>
+        <v>0.1625470776758113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.158354357475563</v>
+        <v>0.1547916779229057</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1389500113675588</v>
+        <v>0.1442609327052984</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1029,150 +1029,150 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1328926573918008</v>
+        <v>0.1397496281068169</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1251501906431445</v>
+        <v>0.1378876063803822</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1194690867248049</v>
+        <v>0.1275861395557891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1167814174993382</v>
+        <v>0.1237057365651706</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1159148274779465</v>
+        <v>0.11795562480251</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>SRIJ.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1022571749152863</v>
+        <v>0.1085865958325001</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Dis</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>SRIJC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.09705650729101856</v>
+        <v>0.1082870570309089</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CS1.PA</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.09608620608741214</v>
+        <v>0.1053238306335962</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi IBEX 35 UCITS ETF Acc</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>USRI.AS</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.09290063096715717</v>
+        <v>0.1018919589657674</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA SRI Climate Paris Aligned UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VMIG.MI</t>
+          <t>CS1.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.09227722470122979</v>
+        <v>0.09763599895360908</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
+          <t>Amundi IBEX 35 UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.687163841369187</v>
+        <v>0.6581214719409527</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4336215416463525</v>
+        <v>0.4416859738236507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1240,195 +1240,195 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2831716137531755</v>
+        <v>0.3101044675037681</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.271457478404876</v>
+        <v>0.3076648746009558</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2640234598299225</v>
+        <v>0.2710769359882061</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2614615877342104</v>
+        <v>0.2669385564055231</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2362169692477429</v>
+        <v>0.2667896854393548</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2309468862863393</v>
+        <v>0.231647820606464</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2159412315299336</v>
+        <v>0.2300668467649014</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2152962034099144</v>
+        <v>0.2138607303634568</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1946569541697476</v>
+        <v>0.2107711055753698</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1858293102062609</v>
+        <v>0.1985249698424507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CU2.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1813461995754961</v>
+        <v>0.1976319529742385</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1805774501492521</v>
+        <v>0.1936437892292384</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>CU2.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1790933435986026</v>
+        <v>0.1932869530800636</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.623675786564458</v>
+        <v>1.650201616937309</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.610442516299313</v>
+        <v>1.615993512101431</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.02991657339148</v>
+        <v>1.035792639287201</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.015879068086518</v>
+        <v>1.001267978063556</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8694483345234207</v>
+        <v>0.8530828072037357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7436530952753904</v>
+        <v>0.7319446911934533</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6363636839506916</v>
+        <v>0.621903336494759</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5920084010111466</v>
+        <v>0.6076081576343972</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.573773653628427</v>
+        <v>0.5827477235067786</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,30 +1601,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5722737964552151</v>
+        <v>0.5729484527142739</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5572185788059683</v>
+        <v>0.5698175312345888</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5563133696806595</v>
+        <v>0.5582160743299109</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.555977245449967</v>
+        <v>0.5275175948868984</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4824766075604201</v>
+        <v>0.4861783033047542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4609601229030147</v>
+        <v>0.4775846512569426</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.55496111693708</v>
+        <v>2.5258499997023</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.271245121653918</v>
+        <v>2.284761607383222</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1752,45 +1752,45 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.967736216648974</v>
+        <v>1.938615311453308</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.923046145205617</v>
+        <v>1.919544938119436</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.898356620261819</v>
+        <v>1.801939712205532</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.568639204949879</v>
+        <v>1.553761240511335</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1812,45 +1812,45 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.38590980220121</v>
+        <v>1.390315337478395</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.383079332386796</v>
+        <v>1.352517950889678</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.353190582641777</v>
+        <v>1.350785375611319</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.331215302340164</v>
+        <v>1.346725019472802</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.324001531713253</v>
+        <v>1.326055285070193</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.264786094471447</v>
+        <v>1.261679952598621</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.215824832197893</v>
+        <v>1.187021331935638</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.1748741918187</v>
+        <v>1.182082431268252</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.091644845152569</v>
+        <v>1.080299702005866</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8805521781902661</v>
+        <v>0.8995648962789176</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8720233301282967</v>
+        <v>0.8926536116955279</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7272433693321974</v>
+        <v>0.7041356369805276</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5167895360867956</v>
+        <v>0.5219764255256665</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.457823929809573</v>
+        <v>0.4506417598345036</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2053,30 +2053,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3990786283558854</v>
+        <v>0.4108443938060979</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3940225942471025</v>
+        <v>0.4037510420526296</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3697541400642768</v>
+        <v>0.3883784259216019</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3693968355828796</v>
+        <v>0.3790189325723397</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3682460744318818</v>
+        <v>0.3764734411032198</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3382784200892863</v>
+        <v>0.3560440107085403</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3362354237488778</v>
+        <v>0.3441126468043569</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2158,45 +2158,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3322706266278845</v>
+        <v>0.3333091233352576</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3287845232386295</v>
+        <v>0.3123091012212318</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3027062747485469</v>
+        <v>0.2863537745631934</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,225 +442,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HYPE.SW</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0957085613297064</v>
+        <v>0.04089790805461613</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21shares Hyperliquid ETP</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HODLV.AS</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04007257728574376</v>
+        <v>0.04082581083869274</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>21shares Crypto Basket Equal Weight ETP</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03398051593690221</v>
+        <v>0.02876565020354871</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03396583135886799</v>
+        <v>0.02685390856098313</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>JPXX.L</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0331339788661944</v>
+        <v>0.0260110119612682</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>AVEM.L</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03217537250897817</v>
+        <v>0.02522133718647512</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Avantis Emerging Markets Equity UCITS ETF USD Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JPXX.L</t>
+          <t>AASI.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03090423502479966</v>
+        <v>0.02491099096398686</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MDAX.MI</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02911147554649318</v>
+        <v>0.02381851828598114</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Invesco MDAX UCITS ETF A</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SRIJC.PA</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0283945171224913</v>
+        <v>0.02361005418231477</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SRIJ.PA</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02805950029226212</v>
+        <v>0.02221524107669959</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Dis</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>MDAX.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02766988758587341</v>
+        <v>0.02177208505344974</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Invesco MDAX UCITS ETF A</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JPXY.AS</t>
+          <t>AASU.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02760837555949602</v>
+        <v>0.02152677346731879</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR (C)</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>VFEM.L</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02694540924436306</v>
+        <v>0.02143798235727656</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Vanguard FTSE Emerging Markets UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>JPXH.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0267169141692678</v>
+        <v>0.02051145155698419</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - EUR Hedged (C)</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>SRIJ.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02457688475759778</v>
+        <v>0.02044375391211894</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Dis</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5586271342994011</v>
+        <v>0.4742779058620157</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2855978786728328</v>
+        <v>0.2079143833685755</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -743,60 +743,60 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2452467201442243</v>
+        <v>0.1920117364010421</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2428140043712053</v>
+        <v>0.1711930978485936</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2361186965681237</v>
+        <v>0.1356174536608221</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1996515149186262</v>
+        <v>0.129820320283623</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1518175449023931</v>
+        <v>0.1178983477928</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -818,30 +818,30 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1473553350313275</v>
+        <v>0.096195949200784</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>MATW.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1423163443620563</v>
+        <v>0.09611704350535932</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1409322985462322</v>
+        <v>0.09551649248752336</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -863,60 +863,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1386668310970038</v>
+        <v>0.09441609652680216</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1378025945367272</v>
+        <v>0.08155534012741472</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1324530226379099</v>
+        <v>0.0810565876894731</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AASU.PA</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1188660179910535</v>
+        <v>0.07655334104653821</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF USD</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4156799356689</v>
+        <v>0.3290506482058193</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1915961891794449</v>
+        <v>0.2015912648029012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1625470776758113</v>
+        <v>0.1718807132911855</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1547916779229057</v>
+        <v>0.1661478820497801</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1442609327052984</v>
+        <v>0.1483624090786206</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1029,150 +1029,150 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1397496281068169</v>
+        <v>0.1421334991629783</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1378876063803822</v>
+        <v>0.1266972401095154</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1275861395557891</v>
+        <v>0.1239175213056098</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1237057365651706</v>
+        <v>0.1228233078753136</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.11795562480251</v>
+        <v>0.1159536022387284</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SRIJ.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1085865958325001</v>
+        <v>0.1108779585920534</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Dis</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SRIJC.PA</t>
+          <t>CS1.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1082870570309089</v>
+        <v>0.1087049364342525</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
+          <t>Amundi IBEX 35 UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>SRIJ.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1053238306335962</v>
+        <v>0.1067230157355217</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Dis</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1018919589657674</v>
+        <v>0.1056818569330489</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CS1.PA</t>
+          <t>SRIJC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.09763599895360908</v>
+        <v>0.1052842338399009</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi IBEX 35 UCITS ETF Acc</t>
+          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6581214719409527</v>
+        <v>0.5744635040418007</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4416859738236507</v>
+        <v>0.4360449481703073</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1240,15 +1240,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3101044675037681</v>
+        <v>0.3161990072072682</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3076648746009558</v>
+        <v>0.2973793823753517</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1270,165 +1270,165 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2710769359882061</v>
+        <v>0.2567316137910274</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2669385564055231</v>
+        <v>0.2558889343208486</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2667896854393548</v>
+        <v>0.2513457210457093</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.231647820606464</v>
+        <v>0.2455135811158746</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2300668467649014</v>
+        <v>0.2371517476992975</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2138607303634568</v>
+        <v>0.2287107986225245</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2107711055753698</v>
+        <v>0.2236901388338353</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1985249698424507</v>
+        <v>0.2136033140588525</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1976319529742385</v>
+        <v>0.2114042204411304</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1936437892292384</v>
+        <v>0.2000592482355543</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CU2.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1932869530800636</v>
+        <v>0.1915172040985491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.650201616937309</v>
+        <v>1.642716281823838</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.615993512101431</v>
+        <v>1.621962850346852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.035792639287201</v>
+        <v>0.9374127288315928</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.001267978063556</v>
+        <v>0.9070541743428029</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8530828072037357</v>
+        <v>0.8478626227472514</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7319446911934533</v>
+        <v>0.7250456520693533</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.621903336494759</v>
+        <v>0.638487961516915</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6076081576343972</v>
+        <v>0.5966314024782269</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5827477235067786</v>
+        <v>0.5930035709957946</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5729484527142739</v>
+        <v>0.586833757146803</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5698175312345888</v>
+        <v>0.5562852665781475</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5582160743299109</v>
+        <v>0.5394664380017216</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5275175948868984</v>
+        <v>0.5027802592210668</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1661,15 +1661,15 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4861783033047542</v>
+        <v>0.4952918542685096</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4775846512569426</v>
+        <v>0.4864646660573386</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.5258499997023</v>
+        <v>2.576275844539584</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.284761607383222</v>
+        <v>2.337040569223188</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.938615311453308</v>
+        <v>1.868330587106033</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.919544938119436</v>
+        <v>1.841048816800823</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.801939712205532</v>
+        <v>1.708714746469772</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.553761240511335</v>
+        <v>1.393034856012692</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.390315337478395</v>
+        <v>1.389870608071297</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.352517950889678</v>
+        <v>1.382476430232448</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1842,90 +1842,90 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.350785375611319</v>
+        <v>1.35983899448334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.346725019472802</v>
+        <v>1.277996283001337</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.326055285070193</v>
+        <v>1.235898672739386</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.261679952598621</v>
+        <v>1.202943469608317</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.187021331935638</v>
+        <v>1.18359515033673</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.182082431268252</v>
+        <v>1.117801802392018</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.080299702005866</v>
+        <v>1.09614956232513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8995648962789176</v>
+        <v>0.8727106080011486</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8926536116955279</v>
+        <v>0.8620410054295224</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7041356369805276</v>
+        <v>0.6084656542333728</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5219764255256665</v>
+        <v>0.4987713925831581</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4506417598345036</v>
+        <v>0.4572126688982801</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4108443938060979</v>
+        <v>0.4301812893926058</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2068,90 +2068,90 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4037510420526296</v>
+        <v>0.3954470008655362</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3883784259216019</v>
+        <v>0.3916503168187409</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3790189325723397</v>
+        <v>0.3861435078296021</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3764734411032198</v>
+        <v>0.3657456767101446</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3560440107085403</v>
+        <v>0.3640484854323114</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3441126468043569</v>
+        <v>0.3542125367723552</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3333091233352576</v>
+        <v>0.3222690880530978</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3123091012212318</v>
+        <v>0.3081624285186515</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,15 +2188,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2863537745631934</v>
+        <v>0.2962271269407686</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,225 +442,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04089790805461613</v>
+        <v>0.03327177638681178</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04082581083869274</v>
+        <v>0.03273732240699578</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02876565020354871</v>
+        <v>0.03201313370167824</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02685390856098313</v>
+        <v>0.03176787449765173</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JPXX.L</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0260110119612682</v>
+        <v>0.03058102605204516</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AVEM.L</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02522133718647512</v>
+        <v>0.02590557839273422</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avantis Emerging Markets Equity UCITS ETF USD Acc</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AASI.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02491099096398686</v>
+        <v>0.02400948524898272</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02381851828598114</v>
+        <v>0.0184298822465554</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>BERMIB.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02361005418231477</v>
+        <v>0.01626307322639375</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HYPE.SW</t>
+          <t>SHC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02221524107669959</v>
+        <v>0.01614635297591049</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>21shares Hyperliquid ETP</t>
+          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MDAX.MI</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02177208505344974</v>
+        <v>0.01575560432301004</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Invesco MDAX UCITS ETF A</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AASU.PA</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02152677346731879</v>
+        <v>0.01541940808822484</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF USD</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VFEM.L</t>
+          <t>BSX.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02143798235727656</v>
+        <v>0.01473978111175756</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Emerging Markets UCITS ETF</t>
+          <t>Amundi EURO STOXX 50 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>VFEM.L</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02051145155698419</v>
+        <v>0.01470831093442881</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Vanguard FTSE Emerging Markets UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SRIJ.PA</t>
+          <t>JPN.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02044375391211894</v>
+        <v>0.01369991062159936</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Dis</t>
+          <t>Amundi Japan TOPIX II UCITS ETF EUR Dist</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4742779058620157</v>
+        <v>0.5135379578734165</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2079143833685755</v>
+        <v>0.2225105809363037</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1920117364010421</v>
+        <v>0.1874260585008636</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1711930978485936</v>
+        <v>0.1485296946212982</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1356174536608221</v>
+        <v>0.1245439980789351</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.129820320283623</v>
+        <v>0.1230567609715101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1178983477928</v>
+        <v>0.112202781339704</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -818,15 +818,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.096195949200784</v>
+        <v>0.1110400507650686</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.09611704350535932</v>
+        <v>0.08818703438456121</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.09551649248752336</v>
+        <v>0.08277097677296186</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -863,60 +863,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.09441609652680216</v>
+        <v>0.08125167601576355</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08155534012741472</v>
+        <v>0.08020486371172231</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0810565876894731</v>
+        <v>0.0744522988705878</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.07655334104653821</v>
+        <v>0.07318186561790929</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3290506482058193</v>
+        <v>0.3660746529255532</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2015912648029012</v>
+        <v>0.2480248416517081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1718807132911855</v>
+        <v>0.1581936642955162</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1661478820497801</v>
+        <v>0.1546630881628557</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,60 +1014,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1483624090786206</v>
+        <v>0.1500546620356646</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1421334991629783</v>
+        <v>0.1368036064439233</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1266972401095154</v>
+        <v>0.1315827109960905</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1239175213056098</v>
+        <v>0.1300293255810501</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1228233078753136</v>
+        <v>0.1190918913575025</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1089,90 +1089,90 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>SRIJC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1159536022387284</v>
+        <v>0.09681564465224191</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>CS1.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1108779585920534</v>
+        <v>0.09428729186131868</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi IBEX 35 UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CS1.PA</t>
+          <t>SRIJ.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1087049364342525</v>
+        <v>0.09206229683973621</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi IBEX 35 UCITS ETF Acc</t>
+          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Dis</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SRIJ.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1067230157355217</v>
+        <v>0.09134839632616387</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Dis</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1056818569330489</v>
+        <v>0.08045264073633818</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SRIJC.PA</t>
+          <t>JPXX.L</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1052842338399009</v>
+        <v>0.08021390374331561</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5744635040418007</v>
+        <v>0.6222963364560445</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4360449481703073</v>
+        <v>0.4711680951711561</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3161990072072682</v>
+        <v>0.3887470718070098</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1255,90 +1255,90 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2973793823753517</v>
+        <v>0.3778462646855665</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2567316137910274</v>
+        <v>0.3635774082307679</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2558889343208486</v>
+        <v>0.3073928210287045</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2513457210457093</v>
+        <v>0.3048221209149946</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2455135811158746</v>
+        <v>0.3015214590588347</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2371517476992975</v>
+        <v>0.2834527927236783</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2287107986225245</v>
+        <v>0.2817003367926714</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1360,30 +1360,30 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2236901388338353</v>
+        <v>0.2608431068521133</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2136033140588525</v>
+        <v>0.2466912580974254</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2114042204411304</v>
+        <v>0.2437849952239233</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1405,30 +1405,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2000592482355543</v>
+        <v>0.2423844301054932</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1915172040985491</v>
+        <v>0.2286852038298206</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.642716281823838</v>
+        <v>1.643028808530102</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.621962850346852</v>
+        <v>1.631191372610583</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1496,30 +1496,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9374127288315928</v>
+        <v>0.9286171655156878</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9070541743428029</v>
+        <v>0.8786764963687914</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8478626227472514</v>
+        <v>0.8352426366974721</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7250456520693533</v>
+        <v>0.7078188479888936</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.638487961516915</v>
+        <v>0.6257732217562801</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1571,60 +1571,60 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5966314024782269</v>
+        <v>0.6035146269717089</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5930035709957946</v>
+        <v>0.5804732387723197</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.586833757146803</v>
+        <v>0.5636004698986883</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5562852665781475</v>
+        <v>0.5352803253099303</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5394664380017216</v>
+        <v>0.5298226914010453</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5027802592210668</v>
+        <v>0.5247148164354714</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4952918542685096</v>
+        <v>0.4880000095741421</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1676,15 +1676,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4864646660573386</v>
+        <v>0.4753266410709764</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.576275844539584</v>
+        <v>2.485299399203623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.337040569223188</v>
+        <v>2.321988238755859</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.868330587106033</v>
+        <v>1.840361369788972</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.841048816800823</v>
+        <v>1.824041154753979</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.708714746469772</v>
+        <v>1.71447960912353</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1797,60 +1797,60 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.393034856012692</v>
+        <v>1.385453601889825</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.389870608071297</v>
+        <v>1.371974375750155</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.382476430232448</v>
+        <v>1.35432721568439</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.35983899448334</v>
+        <v>1.346727962658886</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.277996283001337</v>
+        <v>1.24476533252045</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1872,30 +1872,30 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.235898672739386</v>
+        <v>1.196939866638242</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.202943469608317</v>
+        <v>1.182520869451951</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.18359515033673</v>
+        <v>1.149944263796008</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.117801802392018</v>
+        <v>1.099509817366047</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.09614956232513</v>
+        <v>1.067360509546956</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8727106080011486</v>
+        <v>0.8544497247533795</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8620410054295224</v>
+        <v>0.8508940782980938</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6084656542333728</v>
+        <v>0.6279020338256274</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4987713925831581</v>
+        <v>0.4870324509611463</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2038,30 +2038,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4572126688982801</v>
+        <v>0.4604932740650363</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4301812893926058</v>
+        <v>0.4459046335046062</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3954470008655362</v>
+        <v>0.4313541790137758</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3916503168187409</v>
+        <v>0.3981916657842859</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2098,60 +2098,60 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3861435078296021</v>
+        <v>0.3912504687294138</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3657456767101446</v>
+        <v>0.3727795422875579</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3640484854323114</v>
+        <v>0.3578754846447252</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3542125367723552</v>
+        <v>0.350881572075848</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3222690880530978</v>
+        <v>0.306885475340529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3081624285186515</v>
+        <v>0.3051070073835875</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,15 +2188,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2962271269407686</v>
+        <v>0.2876526655261107</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,225 +442,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HYPE.SW</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03327177638681178</v>
+        <v>0.04305556187935111</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21shares Hyperliquid ETP</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03273732240699578</v>
+        <v>0.03904811666063779</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03201313370167824</v>
+        <v>0.03718372571528694</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03176787449765173</v>
+        <v>0.03557712191651419</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03058102605204516</v>
+        <v>0.03090702513543486</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02590557839273422</v>
+        <v>0.03009479703325035</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02400948524898272</v>
+        <v>0.02787383294715506</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0184298822465554</v>
+        <v>0.02310314117237344</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BERMIB.MI</t>
+          <t>SHC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01626307322639375</v>
+        <v>0.02269044144249133</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SHC.PA</t>
+          <t>BERMIB.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01614635297591049</v>
+        <v>0.02244292427833217</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.01575560432301004</v>
+        <v>0.01954283453647876</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>BSX.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.01541940808822484</v>
+        <v>0.01784885326130858</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi EURO STOXX 50 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BSX.PA</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01473978111175756</v>
+        <v>0.01408819210576673</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VFEM.L</t>
+          <t>MGT.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01470831093442881</v>
+        <v>0.01362394948872026</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Emerging Markets UCITS ETF</t>
+          <t>Amundi DJ Global Titans 50 UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JPN.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01369991062159936</v>
+        <v>0.01174741887093189</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Japan TOPIX II UCITS ETF EUR Dist</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5135379578734165</v>
+        <v>0.4947030000636077</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2225105809363037</v>
+        <v>0.1458301373286608</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -743,180 +743,180 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1874260585008636</v>
+        <v>0.1312023300207168</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1485296946212982</v>
+        <v>0.1300301225573361</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1245439980789351</v>
+        <v>0.126017967752605</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1230567609715101</v>
+        <v>0.1206335278221091</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LAFRI.MI</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.112202781339704</v>
+        <v>0.1183368489482588</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Pan Africa UCITS ETF Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1110400507650686</v>
+        <v>0.1025759608561956</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MATW.PA</t>
+          <t>LAFRI.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.08818703438456121</v>
+        <v>0.09117647549881736</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
+          <t>Amundi Pan Africa UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08277097677296186</v>
+        <v>0.08934453920415053</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>MATW.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.08125167601576355</v>
+        <v>0.08894951667056561</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08020486371172231</v>
+        <v>0.08559700958638206</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0744522988705878</v>
+        <v>0.08464654993452103</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.07318186561790929</v>
+        <v>0.08416627062633308</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3660746529255532</v>
+        <v>0.3668627825279787</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2480248416517081</v>
+        <v>0.2565884413021882</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1581936642955162</v>
+        <v>0.1822238592517662</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -999,135 +999,135 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1546630881628557</v>
+        <v>0.1602683575157036</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1500546620356646</v>
+        <v>0.1577109005339929</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1368036064439233</v>
+        <v>0.1521398644911955</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1315827109960905</v>
+        <v>0.1466432945017766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1300293255810501</v>
+        <v>0.1393629163664192</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1190918913575025</v>
+        <v>0.1075263796499373</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SRIJC.PA</t>
+          <t>CS1.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.09681564465224191</v>
+        <v>0.09635191823279898</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
+          <t>Amundi IBEX 35 UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CS1.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.09428729186131868</v>
+        <v>0.09588860099976437</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi IBEX 35 UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SRIJ.PA</t>
+          <t>UINC.L</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.09206229683973621</v>
+        <v>0.09447525890772801</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Dis</t>
+          <t>First Trust US Equity Income UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.09134839632616387</v>
+        <v>0.08969644818166245</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1149,30 +1149,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>XSMC.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.08045264073633818</v>
+        <v>0.0881792384096749</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Xtrackers Swiss Large Cap UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JPXX.L</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.08021390374331561</v>
+        <v>0.08088936668726165</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6222963364560445</v>
+        <v>0.5495101509556921</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4711680951711561</v>
+        <v>0.4176083991511672</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3887470718070098</v>
+        <v>0.3313652374017868</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1255,30 +1255,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3778462646855665</v>
+        <v>0.3214573814697748</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3635774082307679</v>
+        <v>0.3203053323443648</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3073928210287045</v>
+        <v>0.28365473865989</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,135 +1300,135 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3048221209149946</v>
+        <v>0.2765909600389491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3015214590588347</v>
+        <v>0.2573351462494164</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2834527927236783</v>
+        <v>0.2503666940867195</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2817003367926714</v>
+        <v>0.243882996019344</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2608431068521133</v>
+        <v>0.2421025167001134</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2466912580974254</v>
+        <v>0.2375618410232094</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2437849952239233</v>
+        <v>0.2216191247165</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2423844301054932</v>
+        <v>0.2145420480710594</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2286852038298206</v>
+        <v>0.2089523307445473</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.643028808530102</v>
+        <v>1.619807188954153</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.631191372610583</v>
+        <v>1.597054935366864</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9286171655156878</v>
+        <v>0.8952065828331326</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8786764963687914</v>
+        <v>0.8686108213736867</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8352426366974721</v>
+        <v>0.848526417113715</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7078188479888936</v>
+        <v>0.7400829355069338</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6257732217562801</v>
+        <v>0.6394064552102803</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6035146269717089</v>
+        <v>0.6001335166514359</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5804732387723197</v>
+        <v>0.5851900678576862</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,30 +1601,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5636004698986883</v>
+        <v>0.5752686112536975</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5352803253099303</v>
+        <v>0.5575073950597462</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5298226914010453</v>
+        <v>0.5371428898402624</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5247148164354714</v>
+        <v>0.5187490477236876</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1661,30 +1661,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4880000095741421</v>
+        <v>0.5044516638780729</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4753266410709764</v>
+        <v>0.4953448592935314</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.485299399203623</v>
+        <v>2.467360192489465</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.321988238755859</v>
+        <v>2.338713163809381</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.840361369788972</v>
+        <v>1.836741797437254</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.824041154753979</v>
+        <v>1.808048901531199</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.71447960912353</v>
+        <v>1.677687248245663</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.385453601889825</v>
+        <v>1.38604243120683</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.371974375750155</v>
+        <v>1.369473913840992</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.35432721568439</v>
+        <v>1.349602780219322</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.346727962658886</v>
+        <v>1.32950634852217</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.24476533252045</v>
+        <v>1.248400131756768</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.196939866638242</v>
+        <v>1.208240623706519</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.182520869451951</v>
+        <v>1.164993684414755</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.149944263796008</v>
+        <v>1.14351095610479</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.099509817366047</v>
+        <v>1.100526060292881</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.067360509546956</v>
+        <v>1.063081041717094</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8544497247533795</v>
+        <v>0.8520865342724904</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8508940782980938</v>
+        <v>0.8404126564042027</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6279020338256274</v>
+        <v>0.6052262919604872</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4870324509611463</v>
+        <v>0.4725634442039359</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4604932740650363</v>
+        <v>0.4688878509523069</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4459046335046062</v>
+        <v>0.4520170094453393</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4313541790137758</v>
+        <v>0.43252761246329</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3981916657842859</v>
+        <v>0.3927431598373923</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2098,15 +2098,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3912504687294138</v>
+        <v>0.3706959419305247</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3727795422875579</v>
+        <v>0.3675744448199205</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2128,75 +2128,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3578754846447252</v>
+        <v>0.3439284409407288</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.350881572075848</v>
+        <v>0.3079713351781721</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.306885475340529</v>
+        <v>0.3024880452485392</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3051070073835875</v>
+        <v>0.2977536477430542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2876526655261107</v>
+        <v>0.2854042399231347</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,225 +442,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04305556187935111</v>
+        <v>0.06014802576596501</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03904811666063779</v>
+        <v>0.04335901935384534</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03718372571528694</v>
+        <v>0.04297992337996748</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03557712191651419</v>
+        <v>0.04185467851002023</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03090702513543486</v>
+        <v>0.03268982738664361</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03009479703325035</v>
+        <v>0.03243468942767636</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02787383294715506</v>
+        <v>0.02839391898300847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>PRAJ.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02310314117237344</v>
+        <v>0.02809445828244406</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi Prime Japan UCITS ETF DR (C)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SHC.PA</t>
+          <t>ETFJAP.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02269044144249133</v>
+        <v>0.028034825651712</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi Prime Japan UCITS ETF DR (D)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BERMIB.MI</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02244292427833217</v>
+        <v>0.02722570140111458</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>EJAP.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.01954283453647876</v>
+        <v>0.02712895382789871</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BSX.PA</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.01784885326130858</v>
+        <v>0.02712234756867926</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>JPN.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01408819210576673</v>
+        <v>0.02703442453397042</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>Amundi Japan TOPIX II UCITS ETF EUR Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MGT.PA</t>
+          <t>TPXE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01362394948872026</v>
+        <v>0.02681444994989102</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi DJ Global Titans 50 UCITS ETF Dist</t>
+          <t>Amundi Japan Topix UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>XUCM.L</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01174741887093189</v>
+        <v>0.02445613318078732</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Xtrackers MSCI USA Communication Services UCITS ETF 1D</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4947030000636077</v>
+        <v>0.5056128464338576</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -728,195 +728,195 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1458301373286608</v>
+        <v>0.1366699391172093</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1312023300207168</v>
+        <v>0.1322678744799155</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1300301225573361</v>
+        <v>0.1216874879830365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.126017967752605</v>
+        <v>0.1056302531902498</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1206335278221091</v>
+        <v>0.105396867942563</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1183368489482588</v>
+        <v>0.1049015766565271</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1025759608561956</v>
+        <v>0.09667104866076337</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LAFRI.MI</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.09117647549881736</v>
+        <v>0.09609064542487733</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Pan Africa UCITS ETF Acc</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08934453920415053</v>
+        <v>0.09070009067999196</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MATW.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.08894951667056561</v>
+        <v>0.08930417494245146</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>LAFRI.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08559700958638206</v>
+        <v>0.08530616870940033</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>Amundi Pan Africa UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>MATW.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.08464654993452103</v>
+        <v>0.07528308751070423</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.08416627062633308</v>
+        <v>0.06122068725721164</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3668627825279787</v>
+        <v>0.2217112587834866</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2565884413021882</v>
+        <v>0.2188435364510199</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1822238592517662</v>
+        <v>0.1906649127827948</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -999,30 +999,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1602683575157036</v>
+        <v>0.1848739652414886</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1577109005339929</v>
+        <v>0.1708846141507059</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1521398644911955</v>
+        <v>0.1628037916235159</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1044,135 +1044,135 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1466432945017766</v>
+        <v>0.1313637447185663</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1393629163664192</v>
+        <v>0.1195931983753082</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1075263796499373</v>
+        <v>0.1144948162210091</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CS1.PA</t>
+          <t>INDO.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.09635191823279898</v>
+        <v>0.1139695285225928</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi IBEX 35 UCITS ETF Acc</t>
+          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>SRIJC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.09588860099976437</v>
+        <v>0.1057864749796757</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UINC.L</t>
+          <t>CS1.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.09447525890772801</v>
+        <v>0.1044424649807216</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>First Trust US Equity Income UCITS ETF Dist</t>
+          <t>Amundi IBEX 35 UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>SRIJ.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08969644818166245</v>
+        <v>0.1035922170156685</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Dis</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>XSMC.SW</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0881792384096749</v>
+        <v>0.09923049752993207</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Xtrackers Swiss Large Cap UCITS ETF 1C</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>LAFRI.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.08088936668726165</v>
+        <v>0.0867847507739834</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi Pan Africa UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5495101509556921</v>
+        <v>0.5820927065923294</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4176083991511672</v>
+        <v>0.4567639604197331</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1240,15 +1240,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3313652374017868</v>
+        <v>0.4063084278972506</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3214573814697748</v>
+        <v>0.4032200315425534</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1270,15 +1270,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3203053323443648</v>
+        <v>0.3959390322326415</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.28365473865989</v>
+        <v>0.3314362286658361</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,135 +1300,135 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2765909600389491</v>
+        <v>0.2968977795558063</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2573351462494164</v>
+        <v>0.283875672479547</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2503666940867195</v>
+        <v>0.2817683708357188</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.243882996019344</v>
+        <v>0.2815472987996122</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2421025167001134</v>
+        <v>0.266469054085652</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2375618410232094</v>
+        <v>0.266267476225146</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2216191247165</v>
+        <v>0.2626648447378015</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2145420480710594</v>
+        <v>0.2600305502907931</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2089523307445473</v>
+        <v>0.2456739165748822</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.619807188954153</v>
+        <v>1.588797534564748</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.597054935366864</v>
+        <v>1.574004846936096</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8952065828331326</v>
+        <v>0.8738035456145485</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1511,30 +1511,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8686108213736867</v>
+        <v>0.8572878157302564</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.848526417113715</v>
+        <v>0.8503298843542606</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7400829355069338</v>
+        <v>0.7327647708135978</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6394064552102803</v>
+        <v>0.6211415660492874</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6001335166514359</v>
+        <v>0.6048485669667394</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1586,30 +1586,30 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5851900678576862</v>
+        <v>0.6001905411544144</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5752686112536975</v>
+        <v>0.5916284302236257</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5575073950597462</v>
+        <v>0.5660448957808188</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5371428898402624</v>
+        <v>0.5481179494647435</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1646,45 +1646,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5187490477236876</v>
+        <v>0.519838806956348</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5044516638780729</v>
+        <v>0.5192572016804855</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4953448592935314</v>
+        <v>0.5117142541067941</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.467360192489465</v>
+        <v>2.524469476459497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.338713163809381</v>
+        <v>2.396777845354976</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.836741797437254</v>
+        <v>1.894827305785917</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.808048901531199</v>
+        <v>1.819086455291778</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.677687248245663</v>
+        <v>1.796605434079225</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.38604243120683</v>
+        <v>1.447929743154791</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.369473913840992</v>
+        <v>1.426422859025055</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.349602780219322</v>
+        <v>1.420586668395533</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.32950634852217</v>
+        <v>1.346073338951047</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.248400131756768</v>
+        <v>1.316675844155741</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.208240623706519</v>
+        <v>1.243281367976305</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.164993684414755</v>
+        <v>1.20256207159866</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.14351095610479</v>
+        <v>1.16296663570941</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.100526060292881</v>
+        <v>1.114655354608858</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.063081041717094</v>
+        <v>1.081727604683978</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8520865342724904</v>
+        <v>0.8562757966875996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8404126564042027</v>
+        <v>0.8505613891453976</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6052262919604872</v>
+        <v>0.6065220574651353</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4725634442039359</v>
+        <v>0.4993174837162002</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4688878509523069</v>
+        <v>0.4778703011642147</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4520170094453393</v>
+        <v>0.4365831086330607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.43252761246329</v>
+        <v>0.4287725394800124</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3927431598373923</v>
+        <v>0.400377502871073</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3706959419305247</v>
+        <v>0.3816850650126438</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3675744448199205</v>
+        <v>0.3716042224916882</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3439284409407288</v>
+        <v>0.3657809628705013</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3079713351781721</v>
+        <v>0.3237169932231796</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3024880452485392</v>
+        <v>0.3232214087614409</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2977536477430542</v>
+        <v>0.314488165754659</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2854042399231347</v>
+        <v>0.2982907962512891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,225 +442,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>INDO.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.06014802576596501</v>
+        <v>0.05046003421210332</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04335901935384534</v>
+        <v>0.05024039012616921</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04297992337996748</v>
+        <v>0.04990680889875887</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04185467851002023</v>
+        <v>0.04218088545730891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03268982738664361</v>
+        <v>0.03165212237634485</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03243468942767636</v>
+        <v>0.02634687258065282</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02839391898300847</v>
+        <v>0.02620834760707069</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PRAJ.PA</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02809445828244406</v>
+        <v>0.0226959848545174</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Prime Japan UCITS ETF DR (C)</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ETFJAP.MI</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.028034825651712</v>
+        <v>0.02212154711229464</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Prime Japan UCITS ETF DR (D)</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02722570140111458</v>
+        <v>0.0220393999529187</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EJAP.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02712895382789871</v>
+        <v>0.01852191100790934</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02712234756867926</v>
+        <v>0.01829909159640764</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JPN.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02703442453397042</v>
+        <v>0.01776820135357315</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Japan TOPIX II UCITS ETF EUR Dist</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TPXE.PA</t>
+          <t>ETFJAP.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02681444994989102</v>
+        <v>0.01710196089497873</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Japan Topix UCITS ETF EUR</t>
+          <t>Amundi Prime Japan UCITS ETF DR (D)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XUCM.L</t>
+          <t>EJAP.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02445613318078732</v>
+        <v>0.01708909954900029</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Communication Services UCITS ETF 1D</t>
+          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5056128464338576</v>
+        <v>0.4803750215023819</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3480473205896957</v>
+        <v>0.3514855501823135</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -728,90 +728,90 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1366699391172093</v>
+        <v>0.1252226065532993</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1322678744799155</v>
+        <v>0.1193989386032306</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1216874879830365</v>
+        <v>0.106228473076895</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1056302531902498</v>
+        <v>0.1004527077667143</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.105396867942563</v>
+        <v>0.09164339511626296</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1049015766565271</v>
+        <v>0.08852661515478055</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09667104866076337</v>
+        <v>0.08396949165244472</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -833,45 +833,45 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.09609064542487733</v>
+        <v>0.08312175161528512</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.09070009067999196</v>
+        <v>0.0818702567440559</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.08930417494245146</v>
+        <v>0.08033272181890827</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08530616870940033</v>
+        <v>0.07483822996964018</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -893,30 +893,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MATW.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.07528308751070423</v>
+        <v>0.06043714512892762</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Materials ESG UCITS ETF DR EUR (A)</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06122068725721164</v>
+        <v>0.05836302517978176</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -954,180 +954,180 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>HODLV.AS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2217112587834866</v>
+        <v>0.3565679254910576</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>21shares Crypto Basket Equal Weight ETP</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2188435364510199</v>
+        <v>0.3494662393345864</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1906649127827948</v>
+        <v>0.221835825214538</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1848739652414886</v>
+        <v>0.1962089672177176</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>INDO.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1708846141507059</v>
+        <v>0.1886247764165421</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1628037916235159</v>
+        <v>0.1835504071937044</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1313637447185663</v>
+        <v>0.1805946243764425</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1195931983753082</v>
+        <v>0.1639761222215561</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1144948162210091</v>
+        <v>0.149589912079791</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>INDO.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1139695285225928</v>
+        <v>0.1407721188012403</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SRIJC.PA</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1057864749796757</v>
+        <v>0.121128657829251</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CS1.PA</t>
+          <t>SRIJC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1044424649807216</v>
+        <v>0.1172778053841399</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi IBEX 35 UCITS ETF Acc</t>
+          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1035922170156685</v>
+        <v>0.1161259224855071</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1149,30 +1149,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.09923049752993207</v>
+        <v>0.1072625007633377</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LAFRI.MI</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0867847507739834</v>
+        <v>0.1049243119721195</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Pan Africa UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5820927065923294</v>
+        <v>0.6129306429117529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4567639604197331</v>
+        <v>0.4843018648632689</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4063084278972506</v>
+        <v>0.4649800927838961</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4032200315425534</v>
+        <v>0.4536819568933839</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3959390322326415</v>
+        <v>0.4210034809558854</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3314362286658361</v>
+        <v>0.3504240461465002</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,75 +1300,75 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2968977795558063</v>
+        <v>0.3071533664457744</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.283875672479547</v>
+        <v>0.3039844911479701</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2817683708357188</v>
+        <v>0.2998927218684486</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2815472987996122</v>
+        <v>0.2994757897360683</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.266469054085652</v>
+        <v>0.2952105133416181</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.266267476225146</v>
+        <v>0.2849253524049993</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1390,15 +1390,15 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2626648447378015</v>
+        <v>0.2762136931785131</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2600305502907931</v>
+        <v>0.2748137820840102</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1420,15 +1420,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2456739165748822</v>
+        <v>0.2692246254199202</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.588797534564748</v>
+        <v>1.682747728836988</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.574004846936096</v>
+        <v>1.663881866184949</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8738035456145485</v>
+        <v>0.9488629366723738</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1511,30 +1511,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8572878157302564</v>
+        <v>0.8819199960688904</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8503298843542606</v>
+        <v>0.8672268929113467</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7327647708135978</v>
+        <v>0.7458429853244362</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6211415660492874</v>
+        <v>0.6634664106531614</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6048485669667394</v>
+        <v>0.6158418259569234</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1586,15 +1586,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6001905411544144</v>
+        <v>0.6094589828529464</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5916284302236257</v>
+        <v>0.5970630943667241</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1616,15 +1616,15 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5660448957808188</v>
+        <v>0.573844581679068</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5481179494647435</v>
+        <v>0.557130001051009</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1646,45 +1646,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.519838806956348</v>
+        <v>0.5220906204012083</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5192572016804855</v>
+        <v>0.5027328366101771</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5117142541067941</v>
+        <v>0.4938348069032854</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.524469476459497</v>
+        <v>2.512707605180738</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.396777845354976</v>
+        <v>2.417607222895554</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.894827305785917</v>
+        <v>1.932405935244545</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.819086455291778</v>
+        <v>1.911772584709742</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.796605434079225</v>
+        <v>1.87339394020591</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.447929743154791</v>
+        <v>1.474216174288773</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.426422859025055</v>
+        <v>1.4667177000837</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.420586668395533</v>
+        <v>1.41480595585844</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.346073338951047</v>
+        <v>1.345117464679243</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.316675844155741</v>
+        <v>1.296374575895738</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1872,30 +1872,30 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.243281367976305</v>
+        <v>1.219584879409155</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.20256207159866</v>
+        <v>1.192414603009519</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.16296663570941</v>
+        <v>1.180119667834328</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.114655354608858</v>
+        <v>1.113983664522779</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.081727604683978</v>
+        <v>1.07469537383317</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8562757966875996</v>
+        <v>0.9245931126224662</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8505613891453976</v>
+        <v>0.917110389713419</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6065220574651353</v>
+        <v>0.6378361673762845</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4993174837162002</v>
+        <v>0.5165164254319392</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2038,90 +2038,90 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4778703011642147</v>
+        <v>0.4827321998677447</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4365831086330607</v>
+        <v>0.4480157312808355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4287725394800124</v>
+        <v>0.4258143870706474</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.400377502871073</v>
+        <v>0.415160740113927</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3816850650126438</v>
+        <v>0.3967897564891103</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3716042224916882</v>
+        <v>0.3783883560345089</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3657809628705013</v>
+        <v>0.3588279264633987</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2143,60 +2143,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3237169932231796</v>
+        <v>0.3284592289640602</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3232214087614409</v>
+        <v>0.328241593319808</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.314488165754659</v>
+        <v>0.3147042398817381</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2982907962512891</v>
+        <v>0.3087591611968061</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,225 +442,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>INDO.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05046003421210332</v>
+        <v>0.06174056268012618</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05024039012616921</v>
+        <v>0.06152440308800178</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04990680889875887</v>
+        <v>0.06028455882983619</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04218088545730891</v>
+        <v>0.05376822666523151</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03165212237634485</v>
+        <v>0.03482652296572475</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02634687258065282</v>
+        <v>0.0345889372461623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02620834760707069</v>
+        <v>0.03408164132890557</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0226959848545174</v>
+        <v>0.03397648744790205</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02212154711229464</v>
+        <v>0.03382567887390997</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0220393999529187</v>
+        <v>0.03263547029453351</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.01852191100790934</v>
+        <v>0.03241395708042738</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>EJAP.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.01829909159640764</v>
+        <v>0.03087738812247554</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>ETFJAP.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01776820135357315</v>
+        <v>0.02895271363170804</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi Prime Japan UCITS ETF DR (D)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ETFJAP.MI</t>
+          <t>AUEM.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01710196089497873</v>
+        <v>0.02676261390633727</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Prime Japan UCITS ETF DR (D)</t>
+          <t>Amundi MSCI Emerging Markets Swap UCITS ETF USD Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EJAP.PA</t>
+          <t>PRAJ.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01708909954900029</v>
+        <v>0.02671698436421943</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF</t>
+          <t>Amundi Prime Japan UCITS ETF DR (C)</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4803750215023819</v>
+        <v>0.5190538949220498</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -728,195 +728,195 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1252226065532993</v>
+        <v>0.1539133614045849</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1193989386032306</v>
+        <v>0.153438240606147</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.106228473076895</v>
+        <v>0.1151222411226231</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1004527077667143</v>
+        <v>0.1021245488910758</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.09164339511626296</v>
+        <v>0.09816742439450654</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.08852661515478055</v>
+        <v>0.09698018788284313</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.08396949165244472</v>
+        <v>0.08842038260332918</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.08312175161528512</v>
+        <v>0.08654250533173991</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0818702567440559</v>
+        <v>0.0847058370017415</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.08033272181890827</v>
+        <v>0.07526008093825487</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LAFRI.MI</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07483822996964018</v>
+        <v>0.07275686584167551</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Pan Africa UCITS ETF Acc</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.06043714512892762</v>
+        <v>0.06852274521625534</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05836302517978176</v>
+        <v>0.06826536116456738</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -954,30 +954,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HODLV.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3565679254910576</v>
+        <v>0.3681338009540558</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21shares Crypto Basket Equal Weight ETP</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>HODLV.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3494662393345864</v>
+        <v>0.3565679254910576</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>21shares Crypto Basket Equal Weight ETP</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.221835825214538</v>
+        <v>0.2281114143576572</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1962089672177176</v>
+        <v>0.2064275253980092</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1886247764165421</v>
+        <v>0.2057030448918267</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1029,30 +1029,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1835504071937044</v>
+        <v>0.1863875605392815</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1805946243764425</v>
+        <v>0.184875530115177</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1639761222215561</v>
+        <v>0.1643465830120914</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.149589912079791</v>
+        <v>0.1536094799606309</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1407721188012403</v>
+        <v>0.1372617564752179</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.121128657829251</v>
+        <v>0.1182965271213536</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1119,60 +1119,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SRIJC.PA</t>
+          <t>SRIJ.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1172778053841399</v>
+        <v>0.1130982649905548</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
+          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Dis</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SRIJ.PA</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1161259224855071</v>
+        <v>0.1123493072015247</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Dis</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1072625007633377</v>
+        <v>0.1118515676021448</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>SRIJC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1049243119721195</v>
+        <v>0.1110846761550646</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6129306429117529</v>
+        <v>0.6459517622366897</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4843018648632689</v>
+        <v>0.5128066577727348</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1240,30 +1240,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4649800927838961</v>
+        <v>0.4952608541464383</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4536819568933839</v>
+        <v>0.4951630681825896</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4210034809558854</v>
+        <v>0.4344647446767294</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1285,150 +1285,150 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3504240461465002</v>
+        <v>0.3694444232516818</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3071533664457744</v>
+        <v>0.3645646985308377</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3039844911479701</v>
+        <v>0.3307791619465381</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2998927218684486</v>
+        <v>0.3244240497502149</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2994757897360683</v>
+        <v>0.3191506227892198</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2952105133416181</v>
+        <v>0.3087997449203497</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2849253524049993</v>
+        <v>0.3061381961987419</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2762136931785131</v>
+        <v>0.2906617764725727</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2748137820840102</v>
+        <v>0.2832511151642554</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2692246254199202</v>
+        <v>0.2808204708943756</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.682747728836988</v>
+        <v>1.773318626949357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.663881866184949</v>
+        <v>1.750824636162657</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9488629366723738</v>
+        <v>0.8887632622389998</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1511,30 +1511,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8819199960688904</v>
+        <v>0.8731430134165465</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8672268929113467</v>
+        <v>0.8672110398672772</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7458429853244362</v>
+        <v>0.7299220848035262</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6634664106531614</v>
+        <v>0.6938670335836228</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1571,45 +1571,45 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6158418259569234</v>
+        <v>0.6489109520314764</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6094589828529464</v>
+        <v>0.6325460562222525</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5970630943667241</v>
+        <v>0.6256033839030164</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.573844581679068</v>
+        <v>0.6083525794441598</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.557130001051009</v>
+        <v>0.5807615336418641</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1646,45 +1646,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5220906204012083</v>
+        <v>0.5337252895016913</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5027328366101771</v>
+        <v>0.523430056074399</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4938348069032854</v>
+        <v>0.521551334258703</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.512707605180738</v>
+        <v>2.628801142092187</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.417607222895554</v>
+        <v>2.515824345855486</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.932405935244545</v>
+        <v>2.073763753411394</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.911772584709742</v>
+        <v>2.046999718976904</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.87339394020591</v>
+        <v>1.892611750801168</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.474216174288773</v>
+        <v>1.569745154406448</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.4667177000837</v>
+        <v>1.480243310310195</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1827,30 +1827,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.41480595585844</v>
+        <v>1.445236581109611</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.345117464679243</v>
+        <v>1.444676534593719</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.296374575895738</v>
+        <v>1.28890909356075</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1872,45 +1872,45 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.219584879409155</v>
+        <v>1.224420266618671</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.192414603009519</v>
+        <v>1.218765840303308</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.180119667834328</v>
+        <v>1.213617263013162</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.113983664522779</v>
+        <v>1.157935107980968</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.07469537383317</v>
+        <v>1.11208369108546</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9245931126224662</v>
+        <v>0.9856061408204522</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.917110389713419</v>
+        <v>0.977004464838209</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6378361673762845</v>
+        <v>0.6244466248207419</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5165164254319392</v>
+        <v>0.5318045038003778</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4827321998677447</v>
+        <v>0.506723636852026</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4480157312808355</v>
+        <v>0.4484403756832018</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4258143870706474</v>
+        <v>0.440116658537687</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.415160740113927</v>
+        <v>0.4322928398285544</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3967897564891103</v>
+        <v>0.4112294728956523</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3783883560345089</v>
+        <v>0.400366322733738</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3588279264633987</v>
+        <v>0.3642909858998296</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3284592289640602</v>
+        <v>0.3302051690316001</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.328241593319808</v>
+        <v>0.3289655459048488</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2173,30 +2173,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3147042398817381</v>
+        <v>0.3205185273624149</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3087591611968061</v>
+        <v>0.319451913082031</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,225 +442,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.06174056268012618</v>
+        <v>0.07344768292052373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HYPE.SW</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.06152440308800178</v>
+        <v>0.06750563717959968</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>21shares Hyperliquid ETP</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.06028455882983619</v>
+        <v>0.06046216306526864</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05376822666523151</v>
+        <v>0.04973912372695666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03482652296572475</v>
+        <v>0.0420629424224237</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0345889372461623</v>
+        <v>0.03932978816358745</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03408164132890557</v>
+        <v>0.03846935714433575</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03397648744790205</v>
+        <v>0.03784520677621495</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.03382567887390997</v>
+        <v>0.03726823346234287</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03263547029453351</v>
+        <v>0.0368977608219736</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03241395708042738</v>
+        <v>0.03438043738711993</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EJAP.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03087738812247554</v>
+        <v>0.0319227072181667</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ETFJAP.MI</t>
+          <t>LAFRI.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02895271363170804</v>
+        <v>0.02714119788870595</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Prime Japan UCITS ETF DR (D)</t>
+          <t>Amundi Pan Africa UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AUEM.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02676261390633727</v>
+        <v>0.02678450074373995</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Swap UCITS ETF USD Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PRAJ.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02671698436421943</v>
+        <v>0.02642140332218346</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Prime Japan UCITS ETF DR (C)</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5190538949220498</v>
+        <v>0.4713096918458131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -728,30 +728,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1539133614045849</v>
+        <v>0.1563709826304398</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.153438240606147</v>
+        <v>0.1532336207506486</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1151222411226231</v>
+        <v>0.1245942730774401</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -773,90 +773,90 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1021245488910758</v>
+        <v>0.1077760589492578</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.09816742439450654</v>
+        <v>0.0964479724176639</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.09698018788284313</v>
+        <v>0.08842038260332918</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.08842038260332918</v>
+        <v>0.08495356793005038</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.08654250533173991</v>
+        <v>0.08293040301229748</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0847058370017415</v>
+        <v>0.08043194275688381</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.07526008093825487</v>
+        <v>0.0798485669904867</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -878,30 +878,30 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07275686584167551</v>
+        <v>0.07858583139114872</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.06852274521625534</v>
+        <v>0.07815627551678705</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06826536116456738</v>
+        <v>0.0763172370955727</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3681338009540558</v>
+        <v>0.3846009820630434</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2281114143576572</v>
+        <v>0.2255852389530284</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2064275253980092</v>
+        <v>0.206172545616214</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,30 +1014,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>INDO.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2057030448918267</v>
+        <v>0.1970082003232065</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1863875605392815</v>
+        <v>0.1924787568072523</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.184875530115177</v>
+        <v>0.1881533377632607</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1059,30 +1059,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1643465830120914</v>
+        <v>0.1828357782529269</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1536094799606309</v>
+        <v>0.1680456353168924</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1372617564752179</v>
+        <v>0.1532153424017999</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1104,30 +1104,30 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>INDO.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1182965271213536</v>
+        <v>0.134981670683656</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SRIJ.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1130982649905548</v>
+        <v>0.1292537361152413</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Dis</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1123493072015247</v>
+        <v>0.1289697593802279</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1149,30 +1149,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1118515676021448</v>
+        <v>0.1227605181565545</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SRIJC.PA</t>
+          <t>LAFRI.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1110846761550646</v>
+        <v>0.121940950609646</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
+          <t>Amundi Pan Africa UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6459517622366897</v>
+        <v>0.614460393872903</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5128066577727348</v>
+        <v>0.477896982218202</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4952608541464383</v>
+        <v>0.4150734703888488</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4951630681825896</v>
+        <v>0.4132217941682572</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4344647446767294</v>
+        <v>0.3580277637367852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1285,90 +1285,90 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3694444232516818</v>
+        <v>0.3084810882350308</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3645646985308377</v>
+        <v>0.3071721871298396</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3307791619465381</v>
+        <v>0.2899632775407199</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3244240497502149</v>
+        <v>0.2894357191488128</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3191506227892198</v>
+        <v>0.2886836020777406</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3087997449203497</v>
+        <v>0.28329008772336</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3061381961987419</v>
+        <v>0.2794647541785262</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2906617764725727</v>
+        <v>0.262328206595001</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1405,30 +1405,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2832511151642554</v>
+        <v>0.251186435807105</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2808204708943756</v>
+        <v>0.2498522656709019</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.773318626949357</v>
+        <v>1.753231526459299</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.750824636162657</v>
+        <v>1.724948152655528</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1496,15 +1496,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8887632622389998</v>
+        <v>0.9339042524161756</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8731430134165465</v>
+        <v>0.8448979903240592</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1526,15 +1526,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8672110398672772</v>
+        <v>0.8186514660747504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7299220848035262</v>
+        <v>0.7589089099246502</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6938670335836228</v>
+        <v>0.690672136318129</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1571,30 +1571,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6489109520314764</v>
+        <v>0.6258769275645628</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6325460562222525</v>
+        <v>0.6244337533379822</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6256033839030164</v>
+        <v>0.6045905358094203</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6083525794441598</v>
+        <v>0.5965607764504692</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5807615336418641</v>
+        <v>0.567262937726263</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1646,45 +1646,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5337252895016913</v>
+        <v>0.5379219474340076</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.523430056074399</v>
+        <v>0.5368658211291626</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.521551334258703</v>
+        <v>0.5060424171909614</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.628801142092187</v>
+        <v>2.620214789826742</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.515824345855486</v>
+        <v>2.512795275135638</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.073763753411394</v>
+        <v>2.081579131656215</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.046999718976904</v>
+        <v>2.045204809886848</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.892611750801168</v>
+        <v>1.91718207136879</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.569745154406448</v>
+        <v>1.600919207774113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1812,30 +1812,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.480243310310195</v>
+        <v>1.549811867961765</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.445236581109611</v>
+        <v>1.497741425941774</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.444676534593719</v>
+        <v>1.441992252739801</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.28890909356075</v>
+        <v>1.281707932744415</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1872,30 +1872,30 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.224420266618671</v>
+        <v>1.2273646346892</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.218765840303308</v>
+        <v>1.219090983262402</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.213617263013162</v>
+        <v>1.21482728154811</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.157935107980968</v>
+        <v>1.154333419760766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.11208369108546</v>
+        <v>1.110898134704529</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9856061408204522</v>
+        <v>0.9906547601291182</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.977004464838209</v>
+        <v>0.9758398624055546</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6244466248207419</v>
+        <v>0.5961559334279489</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5318045038003778</v>
+        <v>0.5424515235096463</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4484403756832018</v>
+        <v>0.4611137931741278</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.440116658537687</v>
+        <v>0.4462621068049757</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4322928398285544</v>
+        <v>0.4430885135089162</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4112294728956523</v>
+        <v>0.4166023816910924</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.400366322733738</v>
+        <v>0.3924908590488883</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3642909858998296</v>
+        <v>0.3610628445553983</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2143,60 +2143,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3302051690316001</v>
+        <v>0.3582850042397414</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3289655459048488</v>
+        <v>0.3395897660042773</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3205185273624149</v>
+        <v>0.3354584280798143</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.319451913082031</v>
+        <v>0.3343698280863718</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,30 +442,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.07344768292052373</v>
+        <v>0.07521243435406877</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.06750563717959968</v>
+        <v>0.07122142970483236</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.06046216306526864</v>
+        <v>0.05331484719954394</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04973912372695666</v>
+        <v>0.04912110614315424</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -502,105 +502,105 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0420629424224237</v>
+        <v>0.04653307507030147</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03932978816358745</v>
+        <v>0.041156863157638</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03846935714433575</v>
+        <v>0.03297965184536134</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03784520677621495</v>
+        <v>0.03178282865874316</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.03726823346234287</v>
+        <v>0.02915885749819336</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0368977608219736</v>
+        <v>0.02909052243450061</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03438043738711993</v>
+        <v>0.02891513087800912</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0319227072181667</v>
+        <v>0.02836102240072758</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -622,45 +622,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LAFRI.MI</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02714119788870595</v>
+        <v>0.02832713589416214</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Pan Africa UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02678450074373995</v>
+        <v>0.02379965823435715</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02642140332218346</v>
+        <v>0.02354686965289643</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4713096918458131</v>
+        <v>0.532145169490271</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3514855501823135</v>
+        <v>0.2687249762388106</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -728,30 +728,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1563709826304398</v>
+        <v>0.1660784553079044</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1532336207506486</v>
+        <v>0.1628053463017032</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1245942730774401</v>
+        <v>0.1257359497452308</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -773,150 +773,150 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1077760589492578</v>
+        <v>0.09358616003176001</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0964479724176639</v>
+        <v>0.08631970701568337</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.08842038260332918</v>
+        <v>0.08204080352850185</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.08495356793005038</v>
+        <v>0.0804444207085504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.08293040301229748</v>
+        <v>0.07786777658708655</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08043194275688381</v>
+        <v>0.07394834079393608</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0798485669904867</v>
+        <v>0.07301366554923949</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>SHC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07858583139114872</v>
+        <v>0.0718983923820864</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.07815627551678705</v>
+        <v>0.07112039970595241</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0763172370955727</v>
+        <v>0.07096283233251799</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -954,30 +954,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>HODLV.AS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3846009820630434</v>
+        <v>0.3565679254910576</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>21shares Crypto Basket Equal Weight ETP</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HODLV.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3565679254910576</v>
+        <v>0.3401855214826104</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>21shares Crypto Basket Equal Weight ETP</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2255852389530284</v>
+        <v>0.207932327398328</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -999,45 +999,45 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.206172545616214</v>
+        <v>0.2046784122309806</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1970082003232065</v>
+        <v>0.1998335934500979</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1924787568072523</v>
+        <v>0.1912425957958095</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1881533377632607</v>
+        <v>0.1730991524960519</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1828357782529269</v>
+        <v>0.1563392005951887</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1680456353168924</v>
+        <v>0.1521086469456352</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1532153424017999</v>
+        <v>0.1486805272731537</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1104,15 +1104,15 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>INDO.PA</t>
+          <t>LAFRI.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.134981670683656</v>
+        <v>0.1409742411611437</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
+          <t>Amundi Pan Africa UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1292537361152413</v>
+        <v>0.1150693536364453</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1289697593802279</v>
+        <v>0.1125984878164752</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1227605181565545</v>
+        <v>0.1065602609056575</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1164,15 +1164,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LAFRI.MI</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.121940950609646</v>
+        <v>0.1024191581064176</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Pan Africa UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.614460393872903</v>
+        <v>0.6477297656970977</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.477896982218202</v>
+        <v>0.4701571396910083</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4150734703888488</v>
+        <v>0.4459930808056496</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4132217941682572</v>
+        <v>0.4456001895540345</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3580277637367852</v>
+        <v>0.3727678374883221</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3084810882350308</v>
+        <v>0.3000992589614062</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3071721871298396</v>
+        <v>0.2988870767786127</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1315,120 +1315,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2899632775407199</v>
+        <v>0.2823230256213669</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2894357191488128</v>
+        <v>0.2815457104813317</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2886836020777406</v>
+        <v>0.2768356443402422</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.28329008772336</v>
+        <v>0.2755923735308399</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2794647541785262</v>
+        <v>0.2685726687119983</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.262328206595001</v>
+        <v>0.2541144224876906</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.251186435807105</v>
+        <v>0.2491383872824664</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2498522656709019</v>
+        <v>0.2489561970796386</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.753231526459299</v>
+        <v>1.709323547581317</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.724948152655528</v>
+        <v>1.692706909264763</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9339042524161756</v>
+        <v>0.889908223737464</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1511,30 +1511,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8448979903240592</v>
+        <v>0.8445168203294522</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8186514660747504</v>
+        <v>0.8388999207145</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7589089099246502</v>
+        <v>0.7142592249539708</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.690672136318129</v>
+        <v>0.6716112253171531</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1571,30 +1571,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6258769275645628</v>
+        <v>0.6470486713912655</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6244337533379822</v>
+        <v>0.6141217315720975</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6045905358094203</v>
+        <v>0.5961732183942525</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1616,30 +1616,30 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5965607764504692</v>
+        <v>0.5893432664196399</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.567262937726263</v>
+        <v>0.5542627862773131</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5379219474340076</v>
+        <v>0.531500031495957</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5368658211291626</v>
+        <v>0.5314582553703184</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5060424171909614</v>
+        <v>0.5041653881369152</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.620214789826742</v>
+        <v>2.5746399498193</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.512795275135638</v>
+        <v>2.470389077385969</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.081579131656215</v>
+        <v>2.071269337999251</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.045204809886848</v>
+        <v>2.049820318351336</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.91718207136879</v>
+        <v>1.858247490083262</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.600919207774113</v>
+        <v>1.575821540058502</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.549811867961765</v>
+        <v>1.529609763811391</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.497741425941774</v>
+        <v>1.473732500889915</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.441992252739801</v>
+        <v>1.403519214788966</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.281707932744415</v>
+        <v>1.283671794884089</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1872,30 +1872,30 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.2273646346892</v>
+        <v>1.189247294631766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.219090983262402</v>
+        <v>1.157056118884256</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.21482728154811</v>
+        <v>1.141013196649246</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.154333419760766</v>
+        <v>1.135810339612702</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.110898134704529</v>
+        <v>1.097463135452191</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9906547601291182</v>
+        <v>0.9839947851804454</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9758398624055546</v>
+        <v>0.9788345725084013</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5961559334279489</v>
+        <v>0.5909729743868257</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5424515235096463</v>
+        <v>0.5331695363679771</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.506723636852026</v>
+        <v>0.4981662172661212</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4611137931741278</v>
+        <v>0.4753225593522479</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2068,60 +2068,60 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4462621068049757</v>
+        <v>0.4567003128750016</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4430885135089162</v>
+        <v>0.438675344358838</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4166023816910924</v>
+        <v>0.4095238321471675</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3924908590488883</v>
+        <v>0.4063602542841207</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3610628445553983</v>
+        <v>0.3439284409407288</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3582850042397414</v>
+        <v>0.3391006059357484</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2158,30 +2158,30 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3395897660042773</v>
+        <v>0.3355946614253544</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3354584280798143</v>
+        <v>0.3267132888965205</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3343698280863718</v>
+        <v>0.3237976448673543</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,225 +442,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.07521243435406877</v>
+        <v>0.04830401236009441</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07122142970483236</v>
+        <v>0.03779211480369926</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05331484719954394</v>
+        <v>0.03419943143107496</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04912110614315424</v>
+        <v>0.03236535436008947</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HYPE.SW</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04653307507030147</v>
+        <v>0.02463863387116394</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>21shares Hyperliquid ETP</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.041156863157638</v>
+        <v>0.02405569538575381</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03297965184536134</v>
+        <v>0.02223163802147354</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>SHC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03178282865874316</v>
+        <v>0.02038884444811617</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02915885749819336</v>
+        <v>0.01932920793874748</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>BSX.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02909052243450061</v>
+        <v>0.01819282626132135</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Amundi EURO STOXX 50 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02891513087800912</v>
+        <v>0.01692964604679847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02836102240072758</v>
+        <v>0.01622715293820365</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02832713589416214</v>
+        <v>0.01238161662553661</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02379965823435715</v>
+        <v>0.01179744645872316</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02354686965289643</v>
+        <v>0.01028100034678081</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.532145169490271</v>
+        <v>0.4637022223899181</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -713,30 +713,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HODLV.AS</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2687249762388106</v>
+        <v>0.1000805751758607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>21shares Crypto Basket Equal Weight ETP</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1660784553079044</v>
+        <v>0.09697769979481441</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1628053463017032</v>
+        <v>0.09308869248136475</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -758,135 +758,135 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1257359497452308</v>
+        <v>0.09185132481025171</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.09358616003176001</v>
+        <v>0.08294523887563354</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.08631970701568337</v>
+        <v>0.07974133639863346</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.08204080352850185</v>
+        <v>0.07844441731770835</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>SHC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0804444207085504</v>
+        <v>0.07645167242151873</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.07786777658708655</v>
+        <v>0.07604559489897467</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.07394834079393608</v>
+        <v>0.06567388919757056</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.07301366554923949</v>
+        <v>0.06308921145124757</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SHC.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0718983923820864</v>
+        <v>0.06105773211803256</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.07112039970595241</v>
+        <v>0.05647061357861149</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -908,15 +908,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.07096283233251799</v>
+        <v>0.05532061166914581</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -954,225 +954,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HODLV.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3565679254910576</v>
+        <v>0.3488976155402446</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21shares Crypto Basket Equal Weight ETP</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3401855214826104</v>
+        <v>0.1963908558125855</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.207932327398328</v>
+        <v>0.1944659796981401</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2046784122309806</v>
+        <v>0.1775784492934549</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1998335934500979</v>
+        <v>0.1585667513377476</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1912425957958095</v>
+        <v>0.1532142074376286</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1730991524960519</v>
+        <v>0.14711332103132</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1563392005951887</v>
+        <v>0.1377259190506559</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>LAFRI.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1521086469456352</v>
+        <v>0.1138733994973555</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi Pan Africa UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1486805272731537</v>
+        <v>0.1122951016029707</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LAFRI.MI</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1409742411611437</v>
+        <v>0.1053152263010695</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Pan Africa UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1150693536364453</v>
+        <v>0.1000131423578394</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1125984878164752</v>
+        <v>0.09939593994159734</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1065602609056575</v>
+        <v>0.09425029197272417</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1024191581064176</v>
+        <v>0.0920308070144833</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6477297656970977</v>
+        <v>0.6979592703762949</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4701571396910083</v>
+        <v>0.4848444542385628</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1240,30 +1240,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4459930808056496</v>
+        <v>0.4518042357636785</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4456001895540345</v>
+        <v>0.4509170440889509</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3727678374883221</v>
+        <v>0.3873810019431982</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3000992589614062</v>
+        <v>0.3400861719140404</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,90 +1300,90 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2988870767786127</v>
+        <v>0.309551130411478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2823230256213669</v>
+        <v>0.2989316707610474</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2815457104813317</v>
+        <v>0.2972461676402864</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2768356443402422</v>
+        <v>0.2957895653109706</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2755923735308399</v>
+        <v>0.2895524241801652</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2685726687119983</v>
+        <v>0.2737234920486968</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2541144224876906</v>
+        <v>0.2719295059114106</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1405,30 +1405,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2491383872824664</v>
+        <v>0.2574768027930363</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2489561970796386</v>
+        <v>0.2526639758979918</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.709323547581317</v>
+        <v>1.55584467615553</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.692706909264763</v>
+        <v>1.537489426072282</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1496,30 +1496,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.889908223737464</v>
+        <v>0.8118466853469417</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8445168203294522</v>
+        <v>0.7843137743777686</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8388999207145</v>
+        <v>0.7520087713393451</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7142592249539708</v>
+        <v>0.6504158512309526</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1556,120 +1556,120 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6716112253171531</v>
+        <v>0.6216274129155748</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6470486713912655</v>
+        <v>0.618117519140287</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6141217315720975</v>
+        <v>0.5687533362443049</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5961732183942525</v>
+        <v>0.5549905718248707</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5893432664196399</v>
+        <v>0.5525621857438414</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5542627862773131</v>
+        <v>0.538809205845612</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.531500031495957</v>
+        <v>0.5387271760843959</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5314582553703184</v>
+        <v>0.5265514366047837</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5041653881369152</v>
+        <v>0.5238988234023885</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.5746399498193</v>
+        <v>2.508236244514816</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.470389077385969</v>
+        <v>2.425102678174511</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.071269337999251</v>
+        <v>1.956786455211955</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.049820318351336</v>
+        <v>1.92858406220406</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.858247490083262</v>
+        <v>1.830569863049078</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.575821540058502</v>
+        <v>1.601599934895833</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1812,45 +1812,45 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.529609763811391</v>
+        <v>1.482962941322544</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.473732500889915</v>
+        <v>1.37795510809267</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.403519214788966</v>
+        <v>1.33242723779771</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.283671794884089</v>
+        <v>1.264814761598005</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.189247294631766</v>
+        <v>1.177510842635959</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1887,45 +1887,45 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.157056118884256</v>
+        <v>1.139557486306839</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.141013196649246</v>
+        <v>1.11239326791118</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.135810339612702</v>
+        <v>1.099502914854441</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.097463135452191</v>
+        <v>1.076907326922611</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9839947851804454</v>
+        <v>0.9197593735135814</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9788345725084013</v>
+        <v>0.9104554642701879</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5909729743868257</v>
+        <v>0.5721845290356304</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5331695363679771</v>
+        <v>0.5178814579995386</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2038,30 +2038,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4981662172661212</v>
+        <v>0.4695083700613985</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4753225593522479</v>
+        <v>0.4685207042919539</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4567003128750016</v>
+        <v>0.4639755429654333</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.438675344358838</v>
+        <v>0.4147747844637146</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4095238321471675</v>
+        <v>0.3979854205899478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4063602542841207</v>
+        <v>0.3836932993064908</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3439284409407288</v>
+        <v>0.3454184179114006</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2143,15 +2143,15 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3391006059357484</v>
+        <v>0.3267132888965205</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3355946614253544</v>
+        <v>0.3260967383735416</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2173,30 +2173,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3267132888965205</v>
+        <v>0.3233857290169921</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3237976448673543</v>
+        <v>0.2896920502052764</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04830401236009441</v>
+        <v>0.03832078128406491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -457,15 +457,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03779211480369926</v>
+        <v>0.03731343283582089</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03419943143107496</v>
+        <v>0.0284087536412827</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03236535436008947</v>
+        <v>0.02638195953805722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -502,60 +502,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02463863387116394</v>
+        <v>0.02269890243601469</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>TELE.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02405569538575381</v>
+        <v>0.02004580404065126</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>Amundi STOXX Europe 600 Telecommunications UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02223163802147354</v>
+        <v>0.01928671849305919</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SHC.PA</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02038884444811617</v>
+        <v>0.01792027001313068</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01932920793874748</v>
+        <v>0.01619892410736012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -577,90 +577,90 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BSX.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01819282626132135</v>
+        <v>0.01407164547855211</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.01692964604679847</v>
+        <v>0.01296130133714413</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>SHC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.01622715293820365</v>
+        <v>0.01277587303594796</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01238161662553661</v>
+        <v>0.01248996525817536</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01179744645872316</v>
+        <v>0.01232138778024661</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>XUCM.L</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01028100034678081</v>
+        <v>0.01221777277792335</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Xtrackers MSCI USA Communication Services UCITS ETF 1D</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4637022223899181</v>
+        <v>0.4104444715711806</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1000805751758607</v>
+        <v>0.1149448793737018</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -728,15 +728,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09697769979481441</v>
+        <v>0.07911114162868915</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.09308869248136475</v>
+        <v>0.0773548255976515</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -758,165 +758,165 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.09185132481025171</v>
+        <v>0.07554796999905911</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08294523887563354</v>
+        <v>0.07518178766424</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.07974133639863346</v>
+        <v>0.0707756511679023</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.07844441731770835</v>
+        <v>0.06969325527823034</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SHC.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07645167242151873</v>
+        <v>0.06923076923076921</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.07604559489897467</v>
+        <v>0.06491503936157095</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>SHC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06567388919757056</v>
+        <v>0.06376841484038631</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06308921145124757</v>
+        <v>0.06297494705199336</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06105773211803256</v>
+        <v>0.05712818379197038</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05647061357861149</v>
+        <v>0.05093257321023592</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05532061166914581</v>
+        <v>0.05005672908571435</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3488976155402446</v>
+        <v>0.319540605734423</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -969,210 +969,210 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1963908558125855</v>
+        <v>0.162301647138247</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1944659796981401</v>
+        <v>0.1553064654730978</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1775784492934549</v>
+        <v>0.1481274568729807</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1585667513377476</v>
+        <v>0.1474115481948497</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1532142074376286</v>
+        <v>0.1316870175140916</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.14711332103132</v>
+        <v>0.1238850958023381</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1377259190506559</v>
+        <v>0.1228046630151924</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LAFRI.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1138733994973555</v>
+        <v>0.1137622698617693</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Pan Africa UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1122951016029707</v>
+        <v>0.1086758497521361</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1053152263010695</v>
+        <v>0.1025912453011912</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1000131423578394</v>
+        <v>0.08680147578091013</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.09939593994159734</v>
+        <v>0.08483517394439999</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.09425029197272417</v>
+        <v>0.07862949595032798</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>JPN.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0920308070144833</v>
+        <v>0.0785932497260029</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi Japan TOPIX II UCITS ETF EUR Dist</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6979592703762949</v>
+        <v>0.6772474210357222</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4848444542385628</v>
+        <v>0.5083768612610933</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4518042357636785</v>
+        <v>0.4912954805483689</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4509170440889509</v>
+        <v>0.48582807398179</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3873810019431982</v>
+        <v>0.4303020833835212</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3400861719140404</v>
+        <v>0.3773099972820062</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.309551130411478</v>
+        <v>0.3476214664533273</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1315,120 +1315,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2989316707610474</v>
+        <v>0.3302989903802247</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2972461676402864</v>
+        <v>0.3234536077195183</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2957895653109706</v>
+        <v>0.3209116946217929</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2895524241801652</v>
+        <v>0.3198873524335386</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2737234920486968</v>
+        <v>0.2967413973388064</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2719295059114106</v>
+        <v>0.2876008193003239</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2574768027930363</v>
+        <v>0.2789506119074534</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2526639758979918</v>
+        <v>0.2766478687282095</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.55584467615553</v>
+        <v>1.585415843714573</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.537489426072282</v>
+        <v>1.563662681207206</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1496,45 +1496,45 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8118466853469417</v>
+        <v>0.7683846616377978</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7843137743777686</v>
+        <v>0.7647487630947125</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7520087713393451</v>
+        <v>0.759380986398646</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6504158512309526</v>
+        <v>0.6555295513124362</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1556,45 +1556,45 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6216274129155748</v>
+        <v>0.6356498941494806</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.618117519140287</v>
+        <v>0.6245948754684805</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5687533362443049</v>
+        <v>0.5727204309946585</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5549905718248707</v>
+        <v>0.5670279486408001</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1616,45 +1616,45 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5525621857438414</v>
+        <v>0.5636947424380803</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.538809205845612</v>
+        <v>0.5486506795053567</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5387271760843959</v>
+        <v>0.5426305900417037</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5265514366047837</v>
+        <v>0.5163087913028996</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5238988234023885</v>
+        <v>0.5129032284527903</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.508236244514816</v>
+        <v>2.578463737736245</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.425102678174511</v>
+        <v>2.457976474616103</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.956786455211955</v>
+        <v>2.077000088355379</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.92858406220406</v>
+        <v>2.043113814419916</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.830569863049078</v>
+        <v>1.865857918694148</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.601599934895833</v>
+        <v>1.613298625067221</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.482962941322544</v>
+        <v>1.545741249726172</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.37795510809267</v>
+        <v>1.387941248276654</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.33242723779771</v>
+        <v>1.353056085809162</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.264814761598005</v>
+        <v>1.278008100077423</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.177510842635959</v>
+        <v>1.223806226426214</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.139557486306839</v>
+        <v>1.178633262711191</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.11239326791118</v>
+        <v>1.161151736014856</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.099502914854441</v>
+        <v>1.151483369397445</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.076907326922611</v>
+        <v>1.096042125432263</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9197593735135814</v>
+        <v>0.979268404218667</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9104554642701879</v>
+        <v>0.9676875184448273</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5721845290356304</v>
+        <v>0.5633301142576221</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5178814579995386</v>
+        <v>0.5361724518046913</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2038,30 +2038,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4695083700613985</v>
+        <v>0.4961797067439928</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4685207042919539</v>
+        <v>0.4759432030635702</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4639755429654333</v>
+        <v>0.4679652453420586</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4147747844637146</v>
+        <v>0.4307561219978349</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2098,30 +2098,30 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3979854205899478</v>
+        <v>0.4016589751006419</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3836932993064908</v>
+        <v>0.3956043787136534</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3454184179114006</v>
+        <v>0.3779488713109476</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3267132888965205</v>
+        <v>0.3448276902743739</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2158,30 +2158,30 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3260967383735416</v>
+        <v>0.3360010340872068</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3233857290169921</v>
+        <v>0.3194632025788802</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2896920502052764</v>
+        <v>0.2958454400583692</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
